--- a/Studymaterials/中学生英作文助動詞will編.xlsx
+++ b/Studymaterials/中学生英作文助動詞will編.xlsx
@@ -3732,8 +3732,8 @@
     <mergeCell ref="A81:J81"/>
     <mergeCell ref="A38:J38"/>
     <mergeCell ref="A96:J96"/>
+    <mergeCell ref="A147:J147"/>
     <mergeCell ref="A121:J121"/>
-    <mergeCell ref="A147:J147"/>
     <mergeCell ref="A161:J161"/>
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="A44:J44"/>
@@ -3812,14 +3812,14 @@
     <mergeCell ref="A116:J116"/>
     <mergeCell ref="A85:J85"/>
     <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A17:J17"/>
     <mergeCell ref="A131:J131"/>
     <mergeCell ref="A126:J126"/>
-    <mergeCell ref="A17:J17"/>
     <mergeCell ref="A100:J100"/>
     <mergeCell ref="A140:J140"/>
     <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A109:J109"/>
     <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A109:J109"/>
     <mergeCell ref="A129:J129"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A68:J68"/>
@@ -3857,14 +3857,10 @@
   <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1" verticalDpi="0"/>
-  <rowBreaks count="8" manualBreakCount="8">
-    <brk id="20" min="0" max="16383" man="1"/>
+  <rowBreaks count="4" manualBreakCount="4">
     <brk id="38" min="0" max="16383" man="1"/>
-    <brk id="56" min="0" max="16383" man="1"/>
     <brk id="74" min="0" max="16383" man="1"/>
-    <brk id="92" min="0" max="16383" man="1"/>
     <brk id="110" min="0" max="16383" man="1"/>
-    <brk id="128" min="0" max="16383" man="1"/>
     <brk id="146" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
@@ -6531,8 +6527,8 @@
     <mergeCell ref="A81:J81"/>
     <mergeCell ref="A38:J38"/>
     <mergeCell ref="A96:J96"/>
+    <mergeCell ref="A147:J147"/>
     <mergeCell ref="A121:J121"/>
-    <mergeCell ref="A147:J147"/>
     <mergeCell ref="A161:J161"/>
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="A44:J44"/>
@@ -6611,14 +6607,14 @@
     <mergeCell ref="A116:J116"/>
     <mergeCell ref="A85:J85"/>
     <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A17:J17"/>
     <mergeCell ref="A131:J131"/>
     <mergeCell ref="A126:J126"/>
-    <mergeCell ref="A17:J17"/>
     <mergeCell ref="A100:J100"/>
     <mergeCell ref="A140:J140"/>
     <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A109:J109"/>
     <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A109:J109"/>
     <mergeCell ref="A129:J129"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A68:J68"/>
@@ -6656,14 +6652,10 @@
   <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1" verticalDpi="0"/>
-  <rowBreaks count="8" manualBreakCount="8">
-    <brk id="20" min="0" max="16383" man="1"/>
+  <rowBreaks count="4" manualBreakCount="4">
     <brk id="38" min="0" max="16383" man="1"/>
-    <brk id="56" min="0" max="16383" man="1"/>
     <brk id="74" min="0" max="16383" man="1"/>
-    <brk id="92" min="0" max="16383" man="1"/>
     <brk id="110" min="0" max="16383" man="1"/>
-    <brk id="128" min="0" max="16383" man="1"/>
     <brk id="146" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>

--- a/Studymaterials/中学生英作文助動詞will編.xlsx
+++ b/Studymaterials/中学生英作文助動詞will編.xlsx
@@ -10,8 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="解答willと書き換え" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'問題willと書き換え'!$A$1:$J$164</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'解答willと書き換え'!$A$1:$J$164</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'問題willと書き換え'!$A$1:$J$182</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'解答willと書き換え'!$A$1:$J$182</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1077,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J164"/>
+  <dimension ref="A1:J182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="13" customWidth="1" style="6" min="1" max="1"/>
@@ -1108,7 +1108,7 @@
       <c r="I1" s="25" t="n"/>
       <c r="J1" s="56" t="n"/>
     </row>
-    <row r="2" ht="6" customHeight="1" s="6">
+    <row r="2" ht="4" customHeight="1" s="6">
       <c r="A2" s="8" t="n"/>
       <c r="B2" s="27" t="n"/>
       <c r="C2" s="27" t="n"/>
@@ -1120,7 +1120,7 @@
       <c r="I2" s="27" t="n"/>
       <c r="J2" s="57" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="6">
+    <row r="3" ht="16" customHeight="1" s="6">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>1．主語は「私」で書いてください。</t>
@@ -1136,7 +1136,7 @@
       <c r="I3" s="25" t="n"/>
       <c r="J3" s="56" t="n"/>
     </row>
-    <row r="4" ht="48" customHeight="1" s="6">
+    <row r="4" ht="40" customHeight="1" s="6">
       <c r="A4" s="55" t="inlineStr">
         <is>
           <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
@@ -1154,7 +1154,7 @@
       <c r="I4" s="27" t="n"/>
       <c r="J4" s="57" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1" s="6">
+    <row r="5" ht="17" customHeight="1" s="6">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>私は来週テニスをします。</t>
@@ -1170,7 +1170,7 @@
       <c r="I5" s="27" t="n"/>
       <c r="J5" s="57" t="n"/>
     </row>
-    <row r="6" ht="26" customHeight="1" s="6">
+    <row r="6" ht="20" customHeight="1" s="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>回答（will）：</t>
@@ -1186,7 +1186,7 @@
       <c r="I6" s="27" t="n"/>
       <c r="J6" s="57" t="n"/>
     </row>
-    <row r="7" ht="26" customHeight="1" s="6">
+    <row r="7" ht="20" customHeight="1" s="6">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>回答（言いかえ）：</t>
@@ -1202,7 +1202,7 @@
       <c r="I7" s="27" t="n"/>
       <c r="J7" s="57" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1" s="6">
+    <row r="8" ht="17" customHeight="1" s="6">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>私は来週テニスをしません。</t>
@@ -1218,7 +1218,7 @@
       <c r="I8" s="27" t="n"/>
       <c r="J8" s="57" t="n"/>
     </row>
-    <row r="9" ht="26" customHeight="1" s="6">
+    <row r="9" ht="20" customHeight="1" s="6">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>回答（基本形）：</t>
@@ -1234,7 +1234,7 @@
       <c r="I9" s="27" t="n"/>
       <c r="J9" s="57" t="n"/>
     </row>
-    <row r="10" ht="26" customHeight="1" s="6">
+    <row r="10" ht="20" customHeight="1" s="6">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>回答（短縮形）：</t>
@@ -1250,7 +1250,7 @@
       <c r="I10" s="27" t="n"/>
       <c r="J10" s="57" t="n"/>
     </row>
-    <row r="11" ht="26" customHeight="1" s="6">
+    <row r="11" ht="20" customHeight="1" s="6">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>回答（言いかえ）：</t>
@@ -1266,7 +1266,7 @@
       <c r="I11" s="27" t="n"/>
       <c r="J11" s="57" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1" s="6">
+    <row r="12" ht="17" customHeight="1" s="6">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>私は来週テニスをしますか。</t>
@@ -1282,7 +1282,7 @@
       <c r="I12" s="27" t="n"/>
       <c r="J12" s="57" t="n"/>
     </row>
-    <row r="13" ht="26" customHeight="1" s="6">
+    <row r="13" ht="20" customHeight="1" s="6">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>回答（will疑問文）：</t>
@@ -1298,7 +1298,7 @@
       <c r="I13" s="27" t="n"/>
       <c r="J13" s="57" t="n"/>
     </row>
-    <row r="14" ht="26" customHeight="1" s="6">
+    <row r="14" ht="20" customHeight="1" s="6">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>回答（言いかえ疑問文）：</t>
@@ -1314,7 +1314,7 @@
       <c r="I14" s="27" t="n"/>
       <c r="J14" s="57" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1" s="6">
+    <row r="15" ht="17" customHeight="1" s="6">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>はい、します。</t>
@@ -1330,10 +1330,10 @@
       <c r="I15" s="27" t="n"/>
       <c r="J15" s="57" t="n"/>
     </row>
-    <row r="16" ht="26" customHeight="1" s="6">
+    <row r="16" ht="20" customHeight="1" s="6">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>回答（返答）：</t>
+          <t>回答（will返答）：</t>
         </is>
       </c>
       <c r="B16" s="27" t="n"/>
@@ -1349,7 +1349,7 @@
     <row r="17" ht="20" customHeight="1" s="6">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B17" s="27" t="n"/>
@@ -1362,10 +1362,10 @@
       <c r="I17" s="27" t="n"/>
       <c r="J17" s="57" t="n"/>
     </row>
-    <row r="18" ht="26" customHeight="1" s="6">
+    <row r="18" ht="17" customHeight="1" s="6">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B18" s="27" t="n"/>
@@ -1378,10 +1378,10 @@
       <c r="I18" s="27" t="n"/>
       <c r="J18" s="57" t="n"/>
     </row>
-    <row r="19" ht="26" customHeight="1" s="6">
+    <row r="19" ht="20" customHeight="1" s="6">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B19" s="27" t="n"/>
@@ -1394,8 +1394,12 @@
       <c r="I19" s="27" t="n"/>
       <c r="J19" s="57" t="n"/>
     </row>
-    <row r="20" ht="6" customHeight="1" s="6">
-      <c r="A20" s="8" t="n"/>
+    <row r="20" ht="20" customHeight="1" s="6">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="27" t="n"/>
       <c r="D20" s="27" t="n"/>
@@ -1406,29 +1410,24 @@
       <c r="I20" s="27" t="n"/>
       <c r="J20" s="57" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1" s="6">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>2．主語は「あなた」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="n"/>
-      <c r="C21" s="25" t="n"/>
-      <c r="D21" s="25" t="n"/>
-      <c r="E21" s="25" t="n"/>
-      <c r="F21" s="25" t="n"/>
-      <c r="G21" s="25" t="n"/>
-      <c r="H21" s="25" t="n"/>
-      <c r="I21" s="25" t="n"/>
-      <c r="J21" s="56" t="n"/>
-    </row>
-    <row r="22" ht="40" customHeight="1" s="6">
-      <c r="A22" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
-        </is>
-      </c>
+    <row r="21" ht="20" customHeight="1" s="6">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ返答）：</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="27" t="n"/>
+      <c r="G21" s="27" t="n"/>
+      <c r="H21" s="27" t="n"/>
+      <c r="I21" s="27" t="n"/>
+      <c r="J21" s="57" t="n"/>
+    </row>
+    <row r="22" ht="4" customHeight="1" s="6">
+      <c r="A22" s="8" t="n"/>
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="27" t="n"/>
       <c r="D22" s="27" t="n"/>
@@ -1439,26 +1438,27 @@
       <c r="I22" s="27" t="n"/>
       <c r="J22" s="57" t="n"/>
     </row>
-    <row r="23" ht="20" customHeight="1" s="6">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>あなたは来週テニスをします。</t>
-        </is>
-      </c>
-      <c r="B23" s="27" t="n"/>
-      <c r="C23" s="27" t="n"/>
-      <c r="D23" s="27" t="n"/>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="27" t="n"/>
-      <c r="H23" s="27" t="n"/>
-      <c r="I23" s="27" t="n"/>
-      <c r="J23" s="57" t="n"/>
-    </row>
-    <row r="24" ht="26" customHeight="1" s="6">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>回答（will）：</t>
+    <row r="23" ht="16" customHeight="1" s="6">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>2．主語は「あなた」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="n"/>
+      <c r="C23" s="25" t="n"/>
+      <c r="D23" s="25" t="n"/>
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="25" t="n"/>
+      <c r="G23" s="25" t="n"/>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
+      <c r="J23" s="56" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1" s="6">
+      <c r="A24" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B24" s="27" t="n"/>
@@ -1471,10 +1471,10 @@
       <c r="I24" s="27" t="n"/>
       <c r="J24" s="57" t="n"/>
     </row>
-    <row r="25" ht="26" customHeight="1" s="6">
+    <row r="25" ht="17" customHeight="1" s="6">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>あなたは来週テニスをします。</t>
         </is>
       </c>
       <c r="B25" s="27" t="n"/>
@@ -1490,7 +1490,7 @@
     <row r="26" ht="20" customHeight="1" s="6">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>あなたは来週テニスをしません。</t>
+          <t>回答（will）：</t>
         </is>
       </c>
       <c r="B26" s="27" t="n"/>
@@ -1503,10 +1503,10 @@
       <c r="I26" s="27" t="n"/>
       <c r="J26" s="57" t="n"/>
     </row>
-    <row r="27" ht="26" customHeight="1" s="6">
+    <row r="27" ht="20" customHeight="1" s="6">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B27" s="27" t="n"/>
@@ -1519,10 +1519,10 @@
       <c r="I27" s="27" t="n"/>
       <c r="J27" s="57" t="n"/>
     </row>
-    <row r="28" ht="26" customHeight="1" s="6">
+    <row r="28" ht="17" customHeight="1" s="6">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>あなたは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B28" s="27" t="n"/>
@@ -1535,10 +1535,10 @@
       <c r="I28" s="27" t="n"/>
       <c r="J28" s="57" t="n"/>
     </row>
-    <row r="29" ht="26" customHeight="1" s="6">
+    <row r="29" ht="20" customHeight="1" s="6">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B29" s="27" t="n"/>
@@ -1554,7 +1554,7 @@
     <row r="30" ht="20" customHeight="1" s="6">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>あなたは来週テニスをしますか。</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B30" s="27" t="n"/>
@@ -1567,10 +1567,10 @@
       <c r="I30" s="27" t="n"/>
       <c r="J30" s="57" t="n"/>
     </row>
-    <row r="31" ht="26" customHeight="1" s="6">
+    <row r="31" ht="20" customHeight="1" s="6">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B31" s="27" t="n"/>
@@ -1583,10 +1583,10 @@
       <c r="I31" s="27" t="n"/>
       <c r="J31" s="57" t="n"/>
     </row>
-    <row r="32" ht="26" customHeight="1" s="6">
+    <row r="32" ht="17" customHeight="1" s="6">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ疑問文）：</t>
+          <t>あなたは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B32" s="27" t="n"/>
@@ -1602,7 +1602,7 @@
     <row r="33" ht="20" customHeight="1" s="6">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>回答（will疑問文）：</t>
         </is>
       </c>
       <c r="B33" s="27" t="n"/>
@@ -1615,10 +1615,10 @@
       <c r="I33" s="27" t="n"/>
       <c r="J33" s="57" t="n"/>
     </row>
-    <row r="34" ht="26" customHeight="1" s="6">
+    <row r="34" ht="20" customHeight="1" s="6">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>回答（返答）：</t>
+          <t>回答（言いかえ疑問文）：</t>
         </is>
       </c>
       <c r="B34" s="27" t="n"/>
@@ -1631,10 +1631,10 @@
       <c r="I34" s="27" t="n"/>
       <c r="J34" s="57" t="n"/>
     </row>
-    <row r="35" ht="20" customHeight="1" s="6">
+    <row r="35" ht="17" customHeight="1" s="6">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B35" s="27" t="n"/>
@@ -1647,10 +1647,10 @@
       <c r="I35" s="27" t="n"/>
       <c r="J35" s="57" t="n"/>
     </row>
-    <row r="36" ht="26" customHeight="1" s="6">
+    <row r="36" ht="20" customHeight="1" s="6">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（will返答）：</t>
         </is>
       </c>
       <c r="B36" s="27" t="n"/>
@@ -1663,10 +1663,10 @@
       <c r="I36" s="27" t="n"/>
       <c r="J36" s="57" t="n"/>
     </row>
-    <row r="37" ht="26" customHeight="1" s="6">
+    <row r="37" ht="20" customHeight="1" s="6">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B37" s="27" t="n"/>
@@ -1679,8 +1679,12 @@
       <c r="I37" s="27" t="n"/>
       <c r="J37" s="57" t="n"/>
     </row>
-    <row r="38" ht="6" customHeight="1" s="6">
-      <c r="A38" s="8" t="n"/>
+    <row r="38" ht="17" customHeight="1" s="6">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、しません。</t>
+        </is>
+      </c>
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="27" t="n"/>
       <c r="D38" s="27" t="n"/>
@@ -1691,27 +1695,26 @@
       <c r="I38" s="27" t="n"/>
       <c r="J38" s="57" t="n"/>
     </row>
-    <row r="39" ht="18" customHeight="1" s="6">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>3．主語は「彼」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B39" s="25" t="n"/>
-      <c r="C39" s="25" t="n"/>
-      <c r="D39" s="25" t="n"/>
-      <c r="E39" s="25" t="n"/>
-      <c r="F39" s="25" t="n"/>
-      <c r="G39" s="25" t="n"/>
-      <c r="H39" s="25" t="n"/>
-      <c r="I39" s="25" t="n"/>
-      <c r="J39" s="56" t="n"/>
-    </row>
-    <row r="40" ht="40" customHeight="1" s="6">
-      <c r="A40" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="39" ht="20" customHeight="1" s="6">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="n"/>
+      <c r="C39" s="27" t="n"/>
+      <c r="D39" s="27" t="n"/>
+      <c r="E39" s="27" t="n"/>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="n"/>
+      <c r="H39" s="27" t="n"/>
+      <c r="I39" s="27" t="n"/>
+      <c r="J39" s="57" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1" s="6">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B40" s="27" t="n"/>
@@ -1727,7 +1730,7 @@
     <row r="41" ht="20" customHeight="1" s="6">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>彼は来週テニスをします。</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B41" s="27" t="n"/>
@@ -1740,12 +1743,8 @@
       <c r="I41" s="27" t="n"/>
       <c r="J41" s="57" t="n"/>
     </row>
-    <row r="42" ht="26" customHeight="1" s="6">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>回答（will）：</t>
-        </is>
-      </c>
+    <row r="42" ht="4" customHeight="1" s="6">
+      <c r="A42" s="8" t="n"/>
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="27" t="n"/>
       <c r="D42" s="27" t="n"/>
@@ -1756,26 +1755,27 @@
       <c r="I42" s="27" t="n"/>
       <c r="J42" s="57" t="n"/>
     </row>
-    <row r="43" ht="26" customHeight="1" s="6">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>回答（言いかえ）：</t>
-        </is>
-      </c>
-      <c r="B43" s="27" t="n"/>
-      <c r="C43" s="27" t="n"/>
-      <c r="D43" s="27" t="n"/>
-      <c r="E43" s="27" t="n"/>
-      <c r="F43" s="27" t="n"/>
-      <c r="G43" s="27" t="n"/>
-      <c r="H43" s="27" t="n"/>
-      <c r="I43" s="27" t="n"/>
-      <c r="J43" s="57" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1" s="6">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>彼は来週テニスをしません。</t>
+    <row r="43" ht="16" customHeight="1" s="6">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>3．主語は「彼」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="n"/>
+      <c r="C43" s="25" t="n"/>
+      <c r="D43" s="25" t="n"/>
+      <c r="E43" s="25" t="n"/>
+      <c r="F43" s="25" t="n"/>
+      <c r="G43" s="25" t="n"/>
+      <c r="H43" s="25" t="n"/>
+      <c r="I43" s="25" t="n"/>
+      <c r="J43" s="56" t="n"/>
+    </row>
+    <row r="44" ht="34" customHeight="1" s="6">
+      <c r="A44" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B44" s="27" t="n"/>
@@ -1788,10 +1788,10 @@
       <c r="I44" s="27" t="n"/>
       <c r="J44" s="57" t="n"/>
     </row>
-    <row r="45" ht="26" customHeight="1" s="6">
+    <row r="45" ht="17" customHeight="1" s="6">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>彼は来週テニスをします。</t>
         </is>
       </c>
       <c r="B45" s="27" t="n"/>
@@ -1804,10 +1804,10 @@
       <c r="I45" s="27" t="n"/>
       <c r="J45" s="57" t="n"/>
     </row>
-    <row r="46" ht="26" customHeight="1" s="6">
+    <row r="46" ht="20" customHeight="1" s="6">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（will）：</t>
         </is>
       </c>
       <c r="B46" s="27" t="n"/>
@@ -1820,7 +1820,7 @@
       <c r="I46" s="27" t="n"/>
       <c r="J46" s="57" t="n"/>
     </row>
-    <row r="47" ht="26" customHeight="1" s="6">
+    <row r="47" ht="20" customHeight="1" s="6">
       <c r="A47" s="11" t="inlineStr">
         <is>
           <t>回答（言いかえ）：</t>
@@ -1836,10 +1836,10 @@
       <c r="I47" s="27" t="n"/>
       <c r="J47" s="57" t="n"/>
     </row>
-    <row r="48" ht="20" customHeight="1" s="6">
+    <row r="48" ht="17" customHeight="1" s="6">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>彼は来週テニスをしますか。</t>
+          <t>彼は来週テニスをしません。</t>
         </is>
       </c>
       <c r="B48" s="27" t="n"/>
@@ -1852,10 +1852,10 @@
       <c r="I48" s="27" t="n"/>
       <c r="J48" s="57" t="n"/>
     </row>
-    <row r="49" ht="26" customHeight="1" s="6">
+    <row r="49" ht="20" customHeight="1" s="6">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B49" s="27" t="n"/>
@@ -1868,10 +1868,10 @@
       <c r="I49" s="27" t="n"/>
       <c r="J49" s="57" t="n"/>
     </row>
-    <row r="50" ht="26" customHeight="1" s="6">
+    <row r="50" ht="20" customHeight="1" s="6">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ疑問文）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B50" s="27" t="n"/>
@@ -1887,7 +1887,7 @@
     <row r="51" ht="20" customHeight="1" s="6">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B51" s="27" t="n"/>
@@ -1900,10 +1900,10 @@
       <c r="I51" s="27" t="n"/>
       <c r="J51" s="57" t="n"/>
     </row>
-    <row r="52" ht="26" customHeight="1" s="6">
+    <row r="52" ht="17" customHeight="1" s="6">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>回答（返答）：</t>
+          <t>彼は来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B52" s="27" t="n"/>
@@ -1919,7 +1919,7 @@
     <row r="53" ht="20" customHeight="1" s="6">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>回答（will疑問文）：</t>
         </is>
       </c>
       <c r="B53" s="27" t="n"/>
@@ -1932,10 +1932,10 @@
       <c r="I53" s="27" t="n"/>
       <c r="J53" s="57" t="n"/>
     </row>
-    <row r="54" ht="26" customHeight="1" s="6">
+    <row r="54" ht="20" customHeight="1" s="6">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（言いかえ疑問文）：</t>
         </is>
       </c>
       <c r="B54" s="27" t="n"/>
@@ -1948,10 +1948,10 @@
       <c r="I54" s="27" t="n"/>
       <c r="J54" s="57" t="n"/>
     </row>
-    <row r="55" ht="26" customHeight="1" s="6">
+    <row r="55" ht="17" customHeight="1" s="6">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B55" s="27" t="n"/>
@@ -1964,8 +1964,12 @@
       <c r="I55" s="27" t="n"/>
       <c r="J55" s="57" t="n"/>
     </row>
-    <row r="56" ht="6" customHeight="1" s="6">
-      <c r="A56" s="8" t="n"/>
+    <row r="56" ht="20" customHeight="1" s="6">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>回答（will返答）：</t>
+        </is>
+      </c>
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="27" t="n"/>
       <c r="D56" s="27" t="n"/>
@@ -1976,27 +1980,26 @@
       <c r="I56" s="27" t="n"/>
       <c r="J56" s="57" t="n"/>
     </row>
-    <row r="57" ht="18" customHeight="1" s="6">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>4．主語は「彼女」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B57" s="25" t="n"/>
-      <c r="C57" s="25" t="n"/>
-      <c r="D57" s="25" t="n"/>
-      <c r="E57" s="25" t="n"/>
-      <c r="F57" s="25" t="n"/>
-      <c r="G57" s="25" t="n"/>
-      <c r="H57" s="25" t="n"/>
-      <c r="I57" s="25" t="n"/>
-      <c r="J57" s="56" t="n"/>
-    </row>
-    <row r="58" ht="40" customHeight="1" s="6">
-      <c r="A58" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="57" ht="20" customHeight="1" s="6">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ返答）：</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="n"/>
+      <c r="C57" s="27" t="n"/>
+      <c r="D57" s="27" t="n"/>
+      <c r="E57" s="27" t="n"/>
+      <c r="F57" s="27" t="n"/>
+      <c r="G57" s="27" t="n"/>
+      <c r="H57" s="27" t="n"/>
+      <c r="I57" s="27" t="n"/>
+      <c r="J57" s="57" t="n"/>
+    </row>
+    <row r="58" ht="17" customHeight="1" s="6">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B58" s="27" t="n"/>
@@ -2012,7 +2015,7 @@
     <row r="59" ht="20" customHeight="1" s="6">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>彼女は来週テニスをします。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B59" s="27" t="n"/>
@@ -2025,10 +2028,10 @@
       <c r="I59" s="27" t="n"/>
       <c r="J59" s="57" t="n"/>
     </row>
-    <row r="60" ht="26" customHeight="1" s="6">
+    <row r="60" ht="20" customHeight="1" s="6">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>回答（will）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B60" s="27" t="n"/>
@@ -2041,10 +2044,10 @@
       <c r="I60" s="27" t="n"/>
       <c r="J60" s="57" t="n"/>
     </row>
-    <row r="61" ht="26" customHeight="1" s="6">
+    <row r="61" ht="20" customHeight="1" s="6">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B61" s="27" t="n"/>
@@ -2057,12 +2060,8 @@
       <c r="I61" s="27" t="n"/>
       <c r="J61" s="57" t="n"/>
     </row>
-    <row r="62" ht="20" customHeight="1" s="6">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>彼女は来週テニスをしません。</t>
-        </is>
-      </c>
+    <row r="62" ht="4" customHeight="1" s="6">
+      <c r="A62" s="8" t="n"/>
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="27" t="n"/>
       <c r="D62" s="27" t="n"/>
@@ -2073,26 +2072,27 @@
       <c r="I62" s="27" t="n"/>
       <c r="J62" s="57" t="n"/>
     </row>
-    <row r="63" ht="26" customHeight="1" s="6">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>回答（基本形）：</t>
-        </is>
-      </c>
-      <c r="B63" s="27" t="n"/>
-      <c r="C63" s="27" t="n"/>
-      <c r="D63" s="27" t="n"/>
-      <c r="E63" s="27" t="n"/>
-      <c r="F63" s="27" t="n"/>
-      <c r="G63" s="27" t="n"/>
-      <c r="H63" s="27" t="n"/>
-      <c r="I63" s="27" t="n"/>
-      <c r="J63" s="57" t="n"/>
-    </row>
-    <row r="64" ht="26" customHeight="1" s="6">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>回答（短縮形）：</t>
+    <row r="63" ht="16" customHeight="1" s="6">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>4．主語は「彼女」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B63" s="25" t="n"/>
+      <c r="C63" s="25" t="n"/>
+      <c r="D63" s="25" t="n"/>
+      <c r="E63" s="25" t="n"/>
+      <c r="F63" s="25" t="n"/>
+      <c r="G63" s="25" t="n"/>
+      <c r="H63" s="25" t="n"/>
+      <c r="I63" s="25" t="n"/>
+      <c r="J63" s="56" t="n"/>
+    </row>
+    <row r="64" ht="34" customHeight="1" s="6">
+      <c r="A64" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B64" s="27" t="n"/>
@@ -2105,10 +2105,10 @@
       <c r="I64" s="27" t="n"/>
       <c r="J64" s="57" t="n"/>
     </row>
-    <row r="65" ht="26" customHeight="1" s="6">
+    <row r="65" ht="17" customHeight="1" s="6">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>彼女は来週テニスをします。</t>
         </is>
       </c>
       <c r="B65" s="27" t="n"/>
@@ -2124,7 +2124,7 @@
     <row r="66" ht="20" customHeight="1" s="6">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>彼女は来週テニスをしますか。</t>
+          <t>回答（will）：</t>
         </is>
       </c>
       <c r="B66" s="27" t="n"/>
@@ -2137,10 +2137,10 @@
       <c r="I66" s="27" t="n"/>
       <c r="J66" s="57" t="n"/>
     </row>
-    <row r="67" ht="26" customHeight="1" s="6">
+    <row r="67" ht="20" customHeight="1" s="6">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B67" s="27" t="n"/>
@@ -2153,10 +2153,10 @@
       <c r="I67" s="27" t="n"/>
       <c r="J67" s="57" t="n"/>
     </row>
-    <row r="68" ht="26" customHeight="1" s="6">
+    <row r="68" ht="17" customHeight="1" s="6">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ疑問文）：</t>
+          <t>彼女は来週テニスをしません。</t>
         </is>
       </c>
       <c r="B68" s="27" t="n"/>
@@ -2172,7 +2172,7 @@
     <row r="69" ht="20" customHeight="1" s="6">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B69" s="27" t="n"/>
@@ -2185,10 +2185,10 @@
       <c r="I69" s="27" t="n"/>
       <c r="J69" s="57" t="n"/>
     </row>
-    <row r="70" ht="26" customHeight="1" s="6">
+    <row r="70" ht="20" customHeight="1" s="6">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>回答（返答）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B70" s="27" t="n"/>
@@ -2204,7 +2204,7 @@
     <row r="71" ht="20" customHeight="1" s="6">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B71" s="27" t="n"/>
@@ -2217,10 +2217,10 @@
       <c r="I71" s="27" t="n"/>
       <c r="J71" s="57" t="n"/>
     </row>
-    <row r="72" ht="26" customHeight="1" s="6">
+    <row r="72" ht="17" customHeight="1" s="6">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>彼女は来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B72" s="27" t="n"/>
@@ -2233,10 +2233,10 @@
       <c r="I72" s="27" t="n"/>
       <c r="J72" s="57" t="n"/>
     </row>
-    <row r="73" ht="26" customHeight="1" s="6">
+    <row r="73" ht="20" customHeight="1" s="6">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（will疑問文）：</t>
         </is>
       </c>
       <c r="B73" s="27" t="n"/>
@@ -2249,8 +2249,12 @@
       <c r="I73" s="27" t="n"/>
       <c r="J73" s="57" t="n"/>
     </row>
-    <row r="74" ht="6" customHeight="1" s="6">
-      <c r="A74" s="8" t="n"/>
+    <row r="74" ht="20" customHeight="1" s="6">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ疑問文）：</t>
+        </is>
+      </c>
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="27" t="n"/>
       <c r="D74" s="27" t="n"/>
@@ -2261,28 +2265,26 @@
       <c r="I74" s="27" t="n"/>
       <c r="J74" s="57" t="n"/>
     </row>
-    <row r="75" ht="18" customHeight="1" s="6">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>5．主語は「私たち」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B75" s="25" t="n"/>
-      <c r="C75" s="25" t="n"/>
-      <c r="D75" s="25" t="n"/>
-      <c r="E75" s="25" t="n"/>
-      <c r="F75" s="25" t="n"/>
-      <c r="G75" s="25" t="n"/>
-      <c r="H75" s="25" t="n"/>
-      <c r="I75" s="25" t="n"/>
-      <c r="J75" s="56" t="n"/>
-    </row>
-    <row r="76" ht="48" customHeight="1" s="6">
-      <c r="A76" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。
-※相手が答える形なので、返答では I / we ではなく you を使います。</t>
+    <row r="75" ht="17" customHeight="1" s="6">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>はい、します。</t>
+        </is>
+      </c>
+      <c r="B75" s="27" t="n"/>
+      <c r="C75" s="27" t="n"/>
+      <c r="D75" s="27" t="n"/>
+      <c r="E75" s="27" t="n"/>
+      <c r="F75" s="27" t="n"/>
+      <c r="G75" s="27" t="n"/>
+      <c r="H75" s="27" t="n"/>
+      <c r="I75" s="27" t="n"/>
+      <c r="J75" s="57" t="n"/>
+    </row>
+    <row r="76" ht="20" customHeight="1" s="6">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>回答（will返答）：</t>
         </is>
       </c>
       <c r="B76" s="27" t="n"/>
@@ -2298,7 +2300,7 @@
     <row r="77" ht="20" customHeight="1" s="6">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>私たちは来週テニスをします。</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B77" s="27" t="n"/>
@@ -2311,10 +2313,10 @@
       <c r="I77" s="27" t="n"/>
       <c r="J77" s="57" t="n"/>
     </row>
-    <row r="78" ht="26" customHeight="1" s="6">
+    <row r="78" ht="17" customHeight="1" s="6">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>回答（will）：</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B78" s="27" t="n"/>
@@ -2327,10 +2329,10 @@
       <c r="I78" s="27" t="n"/>
       <c r="J78" s="57" t="n"/>
     </row>
-    <row r="79" ht="26" customHeight="1" s="6">
+    <row r="79" ht="20" customHeight="1" s="6">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B79" s="27" t="n"/>
@@ -2346,7 +2348,7 @@
     <row r="80" ht="20" customHeight="1" s="6">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>私たちは来週テニスをしません。</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B80" s="27" t="n"/>
@@ -2359,10 +2361,10 @@
       <c r="I80" s="27" t="n"/>
       <c r="J80" s="57" t="n"/>
     </row>
-    <row r="81" ht="26" customHeight="1" s="6">
+    <row r="81" ht="20" customHeight="1" s="6">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B81" s="27" t="n"/>
@@ -2375,12 +2377,8 @@
       <c r="I81" s="27" t="n"/>
       <c r="J81" s="57" t="n"/>
     </row>
-    <row r="82" ht="26" customHeight="1" s="6">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t>回答（短縮形）：</t>
-        </is>
-      </c>
+    <row r="82" ht="4" customHeight="1" s="6">
+      <c r="A82" s="8" t="n"/>
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="27" t="n"/>
       <c r="D82" s="27" t="n"/>
@@ -2391,26 +2389,28 @@
       <c r="I82" s="27" t="n"/>
       <c r="J82" s="57" t="n"/>
     </row>
-    <row r="83" ht="26" customHeight="1" s="6">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t>回答（言いかえ）：</t>
-        </is>
-      </c>
-      <c r="B83" s="27" t="n"/>
-      <c r="C83" s="27" t="n"/>
-      <c r="D83" s="27" t="n"/>
-      <c r="E83" s="27" t="n"/>
-      <c r="F83" s="27" t="n"/>
-      <c r="G83" s="27" t="n"/>
-      <c r="H83" s="27" t="n"/>
-      <c r="I83" s="27" t="n"/>
-      <c r="J83" s="57" t="n"/>
-    </row>
-    <row r="84" ht="20" customHeight="1" s="6">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t>私たちは来週テニスをしますか。</t>
+    <row r="83" ht="16" customHeight="1" s="6">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>5．主語は「私たち」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B83" s="25" t="n"/>
+      <c r="C83" s="25" t="n"/>
+      <c r="D83" s="25" t="n"/>
+      <c r="E83" s="25" t="n"/>
+      <c r="F83" s="25" t="n"/>
+      <c r="G83" s="25" t="n"/>
+      <c r="H83" s="25" t="n"/>
+      <c r="I83" s="25" t="n"/>
+      <c r="J83" s="56" t="n"/>
+    </row>
+    <row r="84" ht="40" customHeight="1" s="6">
+      <c r="A84" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。
+※相手が答える形なので、返答では I / we ではなく you を使います。</t>
         </is>
       </c>
       <c r="B84" s="27" t="n"/>
@@ -2423,10 +2423,10 @@
       <c r="I84" s="27" t="n"/>
       <c r="J84" s="57" t="n"/>
     </row>
-    <row r="85" ht="26" customHeight="1" s="6">
+    <row r="85" ht="17" customHeight="1" s="6">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>私たちは来週テニスをします。</t>
         </is>
       </c>
       <c r="B85" s="27" t="n"/>
@@ -2439,10 +2439,10 @@
       <c r="I85" s="27" t="n"/>
       <c r="J85" s="57" t="n"/>
     </row>
-    <row r="86" ht="26" customHeight="1" s="6">
+    <row r="86" ht="20" customHeight="1" s="6">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ疑問文）：</t>
+          <t>回答（will）：</t>
         </is>
       </c>
       <c r="B86" s="27" t="n"/>
@@ -2458,7 +2458,7 @@
     <row r="87" ht="20" customHeight="1" s="6">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B87" s="27" t="n"/>
@@ -2471,10 +2471,10 @@
       <c r="I87" s="27" t="n"/>
       <c r="J87" s="57" t="n"/>
     </row>
-    <row r="88" ht="26" customHeight="1" s="6">
+    <row r="88" ht="17" customHeight="1" s="6">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>回答（返答）：</t>
+          <t>私たちは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B88" s="27" t="n"/>
@@ -2490,7 +2490,7 @@
     <row r="89" ht="20" customHeight="1" s="6">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B89" s="27" t="n"/>
@@ -2503,10 +2503,10 @@
       <c r="I89" s="27" t="n"/>
       <c r="J89" s="57" t="n"/>
     </row>
-    <row r="90" ht="26" customHeight="1" s="6">
+    <row r="90" ht="20" customHeight="1" s="6">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B90" s="27" t="n"/>
@@ -2519,10 +2519,10 @@
       <c r="I90" s="27" t="n"/>
       <c r="J90" s="57" t="n"/>
     </row>
-    <row r="91" ht="26" customHeight="1" s="6">
+    <row r="91" ht="20" customHeight="1" s="6">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B91" s="27" t="n"/>
@@ -2535,8 +2535,12 @@
       <c r="I91" s="27" t="n"/>
       <c r="J91" s="57" t="n"/>
     </row>
-    <row r="92" ht="6" customHeight="1" s="6">
-      <c r="A92" s="8" t="n"/>
+    <row r="92" ht="17" customHeight="1" s="6">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>私たちは来週テニスをしますか。</t>
+        </is>
+      </c>
       <c r="B92" s="27" t="n"/>
       <c r="C92" s="27" t="n"/>
       <c r="D92" s="27" t="n"/>
@@ -2547,27 +2551,26 @@
       <c r="I92" s="27" t="n"/>
       <c r="J92" s="57" t="n"/>
     </row>
-    <row r="93" ht="18" customHeight="1" s="6">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>6．主語は「あなたたち」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B93" s="25" t="n"/>
-      <c r="C93" s="25" t="n"/>
-      <c r="D93" s="25" t="n"/>
-      <c r="E93" s="25" t="n"/>
-      <c r="F93" s="25" t="n"/>
-      <c r="G93" s="25" t="n"/>
-      <c r="H93" s="25" t="n"/>
-      <c r="I93" s="25" t="n"/>
-      <c r="J93" s="56" t="n"/>
-    </row>
-    <row r="94" ht="40" customHeight="1" s="6">
-      <c r="A94" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="93" ht="20" customHeight="1" s="6">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>回答（will疑問文）：</t>
+        </is>
+      </c>
+      <c r="B93" s="27" t="n"/>
+      <c r="C93" s="27" t="n"/>
+      <c r="D93" s="27" t="n"/>
+      <c r="E93" s="27" t="n"/>
+      <c r="F93" s="27" t="n"/>
+      <c r="G93" s="27" t="n"/>
+      <c r="H93" s="27" t="n"/>
+      <c r="I93" s="27" t="n"/>
+      <c r="J93" s="57" t="n"/>
+    </row>
+    <row r="94" ht="20" customHeight="1" s="6">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ疑問文）：</t>
         </is>
       </c>
       <c r="B94" s="27" t="n"/>
@@ -2580,10 +2583,10 @@
       <c r="I94" s="27" t="n"/>
       <c r="J94" s="57" t="n"/>
     </row>
-    <row r="95" ht="20" customHeight="1" s="6">
+    <row r="95" ht="17" customHeight="1" s="6">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>あなたたちは来週テニスをします。</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B95" s="27" t="n"/>
@@ -2596,10 +2599,10 @@
       <c r="I95" s="27" t="n"/>
       <c r="J95" s="57" t="n"/>
     </row>
-    <row r="96" ht="26" customHeight="1" s="6">
+    <row r="96" ht="20" customHeight="1" s="6">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>回答（will）：</t>
+          <t>回答（will返答）：</t>
         </is>
       </c>
       <c r="B96" s="27" t="n"/>
@@ -2612,10 +2615,10 @@
       <c r="I96" s="27" t="n"/>
       <c r="J96" s="57" t="n"/>
     </row>
-    <row r="97" ht="26" customHeight="1" s="6">
+    <row r="97" ht="20" customHeight="1" s="6">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B97" s="27" t="n"/>
@@ -2628,10 +2631,10 @@
       <c r="I97" s="27" t="n"/>
       <c r="J97" s="57" t="n"/>
     </row>
-    <row r="98" ht="20" customHeight="1" s="6">
+    <row r="98" ht="17" customHeight="1" s="6">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>あなたたちは来週テニスをしません。</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B98" s="27" t="n"/>
@@ -2644,7 +2647,7 @@
       <c r="I98" s="27" t="n"/>
       <c r="J98" s="57" t="n"/>
     </row>
-    <row r="99" ht="26" customHeight="1" s="6">
+    <row r="99" ht="20" customHeight="1" s="6">
       <c r="A99" s="11" t="inlineStr">
         <is>
           <t>回答（基本形）：</t>
@@ -2660,7 +2663,7 @@
       <c r="I99" s="27" t="n"/>
       <c r="J99" s="57" t="n"/>
     </row>
-    <row r="100" ht="26" customHeight="1" s="6">
+    <row r="100" ht="20" customHeight="1" s="6">
       <c r="A100" s="11" t="inlineStr">
         <is>
           <t>回答（短縮形）：</t>
@@ -2676,10 +2679,10 @@
       <c r="I100" s="27" t="n"/>
       <c r="J100" s="57" t="n"/>
     </row>
-    <row r="101" ht="26" customHeight="1" s="6">
+    <row r="101" ht="20" customHeight="1" s="6">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B101" s="27" t="n"/>
@@ -2692,12 +2695,8 @@
       <c r="I101" s="27" t="n"/>
       <c r="J101" s="57" t="n"/>
     </row>
-    <row r="102" ht="20" customHeight="1" s="6">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t>あなたたちは来週テニスをしますか。</t>
-        </is>
-      </c>
+    <row r="102" ht="4" customHeight="1" s="6">
+      <c r="A102" s="8" t="n"/>
       <c r="B102" s="27" t="n"/>
       <c r="C102" s="27" t="n"/>
       <c r="D102" s="27" t="n"/>
@@ -2708,26 +2707,27 @@
       <c r="I102" s="27" t="n"/>
       <c r="J102" s="57" t="n"/>
     </row>
-    <row r="103" ht="26" customHeight="1" s="6">
-      <c r="A103" s="11" t="inlineStr">
-        <is>
-          <t>回答（will疑問文）：</t>
-        </is>
-      </c>
-      <c r="B103" s="27" t="n"/>
-      <c r="C103" s="27" t="n"/>
-      <c r="D103" s="27" t="n"/>
-      <c r="E103" s="27" t="n"/>
-      <c r="F103" s="27" t="n"/>
-      <c r="G103" s="27" t="n"/>
-      <c r="H103" s="27" t="n"/>
-      <c r="I103" s="27" t="n"/>
-      <c r="J103" s="57" t="n"/>
-    </row>
-    <row r="104" ht="26" customHeight="1" s="6">
-      <c r="A104" s="11" t="inlineStr">
-        <is>
-          <t>回答（言いかえ疑問文）：</t>
+    <row r="103" ht="16" customHeight="1" s="6">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>6．主語は「あなたたち」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B103" s="25" t="n"/>
+      <c r="C103" s="25" t="n"/>
+      <c r="D103" s="25" t="n"/>
+      <c r="E103" s="25" t="n"/>
+      <c r="F103" s="25" t="n"/>
+      <c r="G103" s="25" t="n"/>
+      <c r="H103" s="25" t="n"/>
+      <c r="I103" s="25" t="n"/>
+      <c r="J103" s="56" t="n"/>
+    </row>
+    <row r="104" ht="34" customHeight="1" s="6">
+      <c r="A104" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B104" s="27" t="n"/>
@@ -2740,10 +2740,10 @@
       <c r="I104" s="27" t="n"/>
       <c r="J104" s="57" t="n"/>
     </row>
-    <row r="105" ht="20" customHeight="1" s="6">
+    <row r="105" ht="17" customHeight="1" s="6">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>あなたたちは来週テニスをします。</t>
         </is>
       </c>
       <c r="B105" s="27" t="n"/>
@@ -2756,10 +2756,10 @@
       <c r="I105" s="27" t="n"/>
       <c r="J105" s="57" t="n"/>
     </row>
-    <row r="106" ht="26" customHeight="1" s="6">
+    <row r="106" ht="20" customHeight="1" s="6">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>回答（返答）：</t>
+          <t>回答（will）：</t>
         </is>
       </c>
       <c r="B106" s="27" t="n"/>
@@ -2775,7 +2775,7 @@
     <row r="107" ht="20" customHeight="1" s="6">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B107" s="27" t="n"/>
@@ -2788,10 +2788,10 @@
       <c r="I107" s="27" t="n"/>
       <c r="J107" s="57" t="n"/>
     </row>
-    <row r="108" ht="26" customHeight="1" s="6">
+    <row r="108" ht="17" customHeight="1" s="6">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>あなたたちは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B108" s="27" t="n"/>
@@ -2804,10 +2804,10 @@
       <c r="I108" s="27" t="n"/>
       <c r="J108" s="57" t="n"/>
     </row>
-    <row r="109" ht="26" customHeight="1" s="6">
+    <row r="109" ht="20" customHeight="1" s="6">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B109" s="27" t="n"/>
@@ -2820,8 +2820,12 @@
       <c r="I109" s="27" t="n"/>
       <c r="J109" s="57" t="n"/>
     </row>
-    <row r="110" ht="6" customHeight="1" s="6">
-      <c r="A110" s="8" t="n"/>
+    <row r="110" ht="20" customHeight="1" s="6">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
       <c r="B110" s="27" t="n"/>
       <c r="C110" s="27" t="n"/>
       <c r="D110" s="27" t="n"/>
@@ -2832,27 +2836,26 @@
       <c r="I110" s="27" t="n"/>
       <c r="J110" s="57" t="n"/>
     </row>
-    <row r="111" ht="18" customHeight="1" s="6">
-      <c r="A111" s="9" t="inlineStr">
-        <is>
-          <t>7．主語は「彼ら」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B111" s="25" t="n"/>
-      <c r="C111" s="25" t="n"/>
-      <c r="D111" s="25" t="n"/>
-      <c r="E111" s="25" t="n"/>
-      <c r="F111" s="25" t="n"/>
-      <c r="G111" s="25" t="n"/>
-      <c r="H111" s="25" t="n"/>
-      <c r="I111" s="25" t="n"/>
-      <c r="J111" s="56" t="n"/>
-    </row>
-    <row r="112" ht="40" customHeight="1" s="6">
-      <c r="A112" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="111" ht="20" customHeight="1" s="6">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B111" s="27" t="n"/>
+      <c r="C111" s="27" t="n"/>
+      <c r="D111" s="27" t="n"/>
+      <c r="E111" s="27" t="n"/>
+      <c r="F111" s="27" t="n"/>
+      <c r="G111" s="27" t="n"/>
+      <c r="H111" s="27" t="n"/>
+      <c r="I111" s="27" t="n"/>
+      <c r="J111" s="57" t="n"/>
+    </row>
+    <row r="112" ht="17" customHeight="1" s="6">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>あなたたちは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B112" s="27" t="n"/>
@@ -2868,7 +2871,7 @@
     <row r="113" ht="20" customHeight="1" s="6">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>彼らは来週テニスをします。</t>
+          <t>回答（will疑問文）：</t>
         </is>
       </c>
       <c r="B113" s="27" t="n"/>
@@ -2881,10 +2884,10 @@
       <c r="I113" s="27" t="n"/>
       <c r="J113" s="57" t="n"/>
     </row>
-    <row r="114" ht="26" customHeight="1" s="6">
+    <row r="114" ht="20" customHeight="1" s="6">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>回答（will）：</t>
+          <t>回答（言いかえ疑問文）：</t>
         </is>
       </c>
       <c r="B114" s="27" t="n"/>
@@ -2897,10 +2900,10 @@
       <c r="I114" s="27" t="n"/>
       <c r="J114" s="57" t="n"/>
     </row>
-    <row r="115" ht="26" customHeight="1" s="6">
+    <row r="115" ht="17" customHeight="1" s="6">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B115" s="27" t="n"/>
@@ -2916,7 +2919,7 @@
     <row r="116" ht="20" customHeight="1" s="6">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>彼らは来週テニスをしません。</t>
+          <t>回答（will返答）：</t>
         </is>
       </c>
       <c r="B116" s="27" t="n"/>
@@ -2929,10 +2932,10 @@
       <c r="I116" s="27" t="n"/>
       <c r="J116" s="57" t="n"/>
     </row>
-    <row r="117" ht="26" customHeight="1" s="6">
+    <row r="117" ht="20" customHeight="1" s="6">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B117" s="27" t="n"/>
@@ -2945,10 +2948,10 @@
       <c r="I117" s="27" t="n"/>
       <c r="J117" s="57" t="n"/>
     </row>
-    <row r="118" ht="26" customHeight="1" s="6">
+    <row r="118" ht="17" customHeight="1" s="6">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B118" s="27" t="n"/>
@@ -2961,10 +2964,10 @@
       <c r="I118" s="27" t="n"/>
       <c r="J118" s="57" t="n"/>
     </row>
-    <row r="119" ht="26" customHeight="1" s="6">
+    <row r="119" ht="20" customHeight="1" s="6">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B119" s="27" t="n"/>
@@ -2980,7 +2983,7 @@
     <row r="120" ht="20" customHeight="1" s="6">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>彼らは来週テニスをしますか。</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B120" s="27" t="n"/>
@@ -2993,10 +2996,10 @@
       <c r="I120" s="27" t="n"/>
       <c r="J120" s="57" t="n"/>
     </row>
-    <row r="121" ht="26" customHeight="1" s="6">
+    <row r="121" ht="20" customHeight="1" s="6">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B121" s="27" t="n"/>
@@ -3009,12 +3012,8 @@
       <c r="I121" s="27" t="n"/>
       <c r="J121" s="57" t="n"/>
     </row>
-    <row r="122" ht="26" customHeight="1" s="6">
-      <c r="A122" s="11" t="inlineStr">
-        <is>
-          <t>回答（言いかえ疑問文）：</t>
-        </is>
-      </c>
+    <row r="122" ht="4" customHeight="1" s="6">
+      <c r="A122" s="8" t="n"/>
       <c r="B122" s="27" t="n"/>
       <c r="C122" s="27" t="n"/>
       <c r="D122" s="27" t="n"/>
@@ -3025,26 +3024,27 @@
       <c r="I122" s="27" t="n"/>
       <c r="J122" s="57" t="n"/>
     </row>
-    <row r="123" ht="20" customHeight="1" s="6">
-      <c r="A123" s="11" t="inlineStr">
-        <is>
-          <t>はい、します。</t>
-        </is>
-      </c>
-      <c r="B123" s="27" t="n"/>
-      <c r="C123" s="27" t="n"/>
-      <c r="D123" s="27" t="n"/>
-      <c r="E123" s="27" t="n"/>
-      <c r="F123" s="27" t="n"/>
-      <c r="G123" s="27" t="n"/>
-      <c r="H123" s="27" t="n"/>
-      <c r="I123" s="27" t="n"/>
-      <c r="J123" s="57" t="n"/>
-    </row>
-    <row r="124" ht="26" customHeight="1" s="6">
-      <c r="A124" s="11" t="inlineStr">
-        <is>
-          <t>回答（返答）：</t>
+    <row r="123" ht="16" customHeight="1" s="6">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>7．主語は「彼ら」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B123" s="25" t="n"/>
+      <c r="C123" s="25" t="n"/>
+      <c r="D123" s="25" t="n"/>
+      <c r="E123" s="25" t="n"/>
+      <c r="F123" s="25" t="n"/>
+      <c r="G123" s="25" t="n"/>
+      <c r="H123" s="25" t="n"/>
+      <c r="I123" s="25" t="n"/>
+      <c r="J123" s="56" t="n"/>
+    </row>
+    <row r="124" ht="34" customHeight="1" s="6">
+      <c r="A124" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B124" s="27" t="n"/>
@@ -3057,10 +3057,10 @@
       <c r="I124" s="27" t="n"/>
       <c r="J124" s="57" t="n"/>
     </row>
-    <row r="125" ht="20" customHeight="1" s="6">
+    <row r="125" ht="17" customHeight="1" s="6">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>彼らは来週テニスをします。</t>
         </is>
       </c>
       <c r="B125" s="27" t="n"/>
@@ -3073,10 +3073,10 @@
       <c r="I125" s="27" t="n"/>
       <c r="J125" s="57" t="n"/>
     </row>
-    <row r="126" ht="26" customHeight="1" s="6">
+    <row r="126" ht="20" customHeight="1" s="6">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（will）：</t>
         </is>
       </c>
       <c r="B126" s="27" t="n"/>
@@ -3089,10 +3089,10 @@
       <c r="I126" s="27" t="n"/>
       <c r="J126" s="57" t="n"/>
     </row>
-    <row r="127" ht="26" customHeight="1" s="6">
+    <row r="127" ht="20" customHeight="1" s="6">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B127" s="27" t="n"/>
@@ -3105,8 +3105,12 @@
       <c r="I127" s="27" t="n"/>
       <c r="J127" s="57" t="n"/>
     </row>
-    <row r="128" ht="6" customHeight="1" s="6">
-      <c r="A128" s="8" t="n"/>
+    <row r="128" ht="17" customHeight="1" s="6">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>彼らは来週テニスをしません。</t>
+        </is>
+      </c>
       <c r="B128" s="27" t="n"/>
       <c r="C128" s="27" t="n"/>
       <c r="D128" s="27" t="n"/>
@@ -3117,27 +3121,26 @@
       <c r="I128" s="27" t="n"/>
       <c r="J128" s="57" t="n"/>
     </row>
-    <row r="129" ht="18" customHeight="1" s="6">
-      <c r="A129" s="9" t="inlineStr">
-        <is>
-          <t>8．主語は「リョウタロウ」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B129" s="25" t="n"/>
-      <c r="C129" s="25" t="n"/>
-      <c r="D129" s="25" t="n"/>
-      <c r="E129" s="25" t="n"/>
-      <c r="F129" s="25" t="n"/>
-      <c r="G129" s="25" t="n"/>
-      <c r="H129" s="25" t="n"/>
-      <c r="I129" s="25" t="n"/>
-      <c r="J129" s="56" t="n"/>
-    </row>
-    <row r="130" ht="40" customHeight="1" s="6">
-      <c r="A130" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="129" ht="20" customHeight="1" s="6">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B129" s="27" t="n"/>
+      <c r="C129" s="27" t="n"/>
+      <c r="D129" s="27" t="n"/>
+      <c r="E129" s="27" t="n"/>
+      <c r="F129" s="27" t="n"/>
+      <c r="G129" s="27" t="n"/>
+      <c r="H129" s="27" t="n"/>
+      <c r="I129" s="27" t="n"/>
+      <c r="J129" s="57" t="n"/>
+    </row>
+    <row r="130" ht="20" customHeight="1" s="6">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B130" s="27" t="n"/>
@@ -3153,7 +3156,7 @@
     <row r="131" ht="20" customHeight="1" s="6">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは来週テニスをします。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B131" s="27" t="n"/>
@@ -3166,10 +3169,10 @@
       <c r="I131" s="27" t="n"/>
       <c r="J131" s="57" t="n"/>
     </row>
-    <row r="132" ht="26" customHeight="1" s="6">
+    <row r="132" ht="17" customHeight="1" s="6">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>回答（will）：</t>
+          <t>彼らは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B132" s="27" t="n"/>
@@ -3182,10 +3185,10 @@
       <c r="I132" s="27" t="n"/>
       <c r="J132" s="57" t="n"/>
     </row>
-    <row r="133" ht="26" customHeight="1" s="6">
+    <row r="133" ht="20" customHeight="1" s="6">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（will疑問文）：</t>
         </is>
       </c>
       <c r="B133" s="27" t="n"/>
@@ -3201,7 +3204,7 @@
     <row r="134" ht="20" customHeight="1" s="6">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは来週テニスをしません。</t>
+          <t>回答（言いかえ疑問文）：</t>
         </is>
       </c>
       <c r="B134" s="27" t="n"/>
@@ -3214,10 +3217,10 @@
       <c r="I134" s="27" t="n"/>
       <c r="J134" s="57" t="n"/>
     </row>
-    <row r="135" ht="26" customHeight="1" s="6">
+    <row r="135" ht="17" customHeight="1" s="6">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B135" s="27" t="n"/>
@@ -3230,10 +3233,10 @@
       <c r="I135" s="27" t="n"/>
       <c r="J135" s="57" t="n"/>
     </row>
-    <row r="136" ht="26" customHeight="1" s="6">
+    <row r="136" ht="20" customHeight="1" s="6">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（will返答）：</t>
         </is>
       </c>
       <c r="B136" s="27" t="n"/>
@@ -3246,10 +3249,10 @@
       <c r="I136" s="27" t="n"/>
       <c r="J136" s="57" t="n"/>
     </row>
-    <row r="137" ht="26" customHeight="1" s="6">
+    <row r="137" ht="20" customHeight="1" s="6">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B137" s="27" t="n"/>
@@ -3262,10 +3265,10 @@
       <c r="I137" s="27" t="n"/>
       <c r="J137" s="57" t="n"/>
     </row>
-    <row r="138" ht="20" customHeight="1" s="6">
+    <row r="138" ht="17" customHeight="1" s="6">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは来週テニスをしますか。</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B138" s="27" t="n"/>
@@ -3278,10 +3281,10 @@
       <c r="I138" s="27" t="n"/>
       <c r="J138" s="57" t="n"/>
     </row>
-    <row r="139" ht="26" customHeight="1" s="6">
+    <row r="139" ht="20" customHeight="1" s="6">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B139" s="27" t="n"/>
@@ -3294,10 +3297,10 @@
       <c r="I139" s="27" t="n"/>
       <c r="J139" s="57" t="n"/>
     </row>
-    <row r="140" ht="26" customHeight="1" s="6">
+    <row r="140" ht="20" customHeight="1" s="6">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ疑問文）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B140" s="27" t="n"/>
@@ -3313,7 +3316,7 @@
     <row r="141" ht="20" customHeight="1" s="6">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B141" s="27" t="n"/>
@@ -3326,12 +3329,8 @@
       <c r="I141" s="27" t="n"/>
       <c r="J141" s="57" t="n"/>
     </row>
-    <row r="142" ht="26" customHeight="1" s="6">
-      <c r="A142" s="11" t="inlineStr">
-        <is>
-          <t>回答（返答）：</t>
-        </is>
-      </c>
+    <row r="142" ht="4" customHeight="1" s="6">
+      <c r="A142" s="8" t="n"/>
       <c r="B142" s="27" t="n"/>
       <c r="C142" s="27" t="n"/>
       <c r="D142" s="27" t="n"/>
@@ -3342,26 +3341,27 @@
       <c r="I142" s="27" t="n"/>
       <c r="J142" s="57" t="n"/>
     </row>
-    <row r="143" ht="20" customHeight="1" s="6">
-      <c r="A143" s="11" t="inlineStr">
-        <is>
-          <t>いいえ、しません。</t>
-        </is>
-      </c>
-      <c r="B143" s="27" t="n"/>
-      <c r="C143" s="27" t="n"/>
-      <c r="D143" s="27" t="n"/>
-      <c r="E143" s="27" t="n"/>
-      <c r="F143" s="27" t="n"/>
-      <c r="G143" s="27" t="n"/>
-      <c r="H143" s="27" t="n"/>
-      <c r="I143" s="27" t="n"/>
-      <c r="J143" s="57" t="n"/>
-    </row>
-    <row r="144" ht="26" customHeight="1" s="6">
-      <c r="A144" s="11" t="inlineStr">
-        <is>
-          <t>回答（基本形）：</t>
+    <row r="143" ht="16" customHeight="1" s="6">
+      <c r="A143" s="9" t="inlineStr">
+        <is>
+          <t>8．主語は「リョウタロウ」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B143" s="25" t="n"/>
+      <c r="C143" s="25" t="n"/>
+      <c r="D143" s="25" t="n"/>
+      <c r="E143" s="25" t="n"/>
+      <c r="F143" s="25" t="n"/>
+      <c r="G143" s="25" t="n"/>
+      <c r="H143" s="25" t="n"/>
+      <c r="I143" s="25" t="n"/>
+      <c r="J143" s="56" t="n"/>
+    </row>
+    <row r="144" ht="34" customHeight="1" s="6">
+      <c r="A144" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B144" s="27" t="n"/>
@@ -3374,10 +3374,10 @@
       <c r="I144" s="27" t="n"/>
       <c r="J144" s="57" t="n"/>
     </row>
-    <row r="145" ht="26" customHeight="1" s="6">
+    <row r="145" ht="17" customHeight="1" s="6">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>リョウタロウは来週テニスをします。</t>
         </is>
       </c>
       <c r="B145" s="27" t="n"/>
@@ -3390,8 +3390,12 @@
       <c r="I145" s="27" t="n"/>
       <c r="J145" s="57" t="n"/>
     </row>
-    <row r="146" ht="6" customHeight="1" s="6">
-      <c r="A146" s="8" t="n"/>
+    <row r="146" ht="20" customHeight="1" s="6">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>回答（will）：</t>
+        </is>
+      </c>
       <c r="B146" s="27" t="n"/>
       <c r="C146" s="27" t="n"/>
       <c r="D146" s="27" t="n"/>
@@ -3402,27 +3406,26 @@
       <c r="I146" s="27" t="n"/>
       <c r="J146" s="57" t="n"/>
     </row>
-    <row r="147" ht="18" customHeight="1" s="6">
-      <c r="A147" s="9" t="inlineStr">
-        <is>
-          <t>9．主語は「チサコ」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B147" s="25" t="n"/>
-      <c r="C147" s="25" t="n"/>
-      <c r="D147" s="25" t="n"/>
-      <c r="E147" s="25" t="n"/>
-      <c r="F147" s="25" t="n"/>
-      <c r="G147" s="25" t="n"/>
-      <c r="H147" s="25" t="n"/>
-      <c r="I147" s="25" t="n"/>
-      <c r="J147" s="56" t="n"/>
-    </row>
-    <row r="148" ht="40" customHeight="1" s="6">
-      <c r="A148" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="147" ht="20" customHeight="1" s="6">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B147" s="27" t="n"/>
+      <c r="C147" s="27" t="n"/>
+      <c r="D147" s="27" t="n"/>
+      <c r="E147" s="27" t="n"/>
+      <c r="F147" s="27" t="n"/>
+      <c r="G147" s="27" t="n"/>
+      <c r="H147" s="27" t="n"/>
+      <c r="I147" s="27" t="n"/>
+      <c r="J147" s="57" t="n"/>
+    </row>
+    <row r="148" ht="17" customHeight="1" s="6">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>リョウタロウは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B148" s="27" t="n"/>
@@ -3438,7 +3441,7 @@
     <row r="149" ht="20" customHeight="1" s="6">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>チサコは来週テニスをします。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B149" s="27" t="n"/>
@@ -3451,10 +3454,10 @@
       <c r="I149" s="27" t="n"/>
       <c r="J149" s="57" t="n"/>
     </row>
-    <row r="150" ht="26" customHeight="1" s="6">
+    <row r="150" ht="20" customHeight="1" s="6">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>回答（will）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B150" s="27" t="n"/>
@@ -3467,7 +3470,7 @@
       <c r="I150" s="27" t="n"/>
       <c r="J150" s="57" t="n"/>
     </row>
-    <row r="151" ht="26" customHeight="1" s="6">
+    <row r="151" ht="20" customHeight="1" s="6">
       <c r="A151" s="11" t="inlineStr">
         <is>
           <t>回答（言いかえ）：</t>
@@ -3483,10 +3486,10 @@
       <c r="I151" s="27" t="n"/>
       <c r="J151" s="57" t="n"/>
     </row>
-    <row r="152" ht="20" customHeight="1" s="6">
+    <row r="152" ht="17" customHeight="1" s="6">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>チサコは来週テニスをしません。</t>
+          <t>リョウタロウは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B152" s="27" t="n"/>
@@ -3499,10 +3502,10 @@
       <c r="I152" s="27" t="n"/>
       <c r="J152" s="57" t="n"/>
     </row>
-    <row r="153" ht="26" customHeight="1" s="6">
+    <row r="153" ht="20" customHeight="1" s="6">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（will疑問文）：</t>
         </is>
       </c>
       <c r="B153" s="27" t="n"/>
@@ -3515,10 +3518,10 @@
       <c r="I153" s="27" t="n"/>
       <c r="J153" s="57" t="n"/>
     </row>
-    <row r="154" ht="26" customHeight="1" s="6">
+    <row r="154" ht="20" customHeight="1" s="6">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（言いかえ疑問文）：</t>
         </is>
       </c>
       <c r="B154" s="27" t="n"/>
@@ -3531,10 +3534,10 @@
       <c r="I154" s="27" t="n"/>
       <c r="J154" s="57" t="n"/>
     </row>
-    <row r="155" ht="26" customHeight="1" s="6">
+    <row r="155" ht="17" customHeight="1" s="6">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B155" s="27" t="n"/>
@@ -3550,7 +3553,7 @@
     <row r="156" ht="20" customHeight="1" s="6">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>チサコは来週テニスをしますか。</t>
+          <t>回答（will返答）：</t>
         </is>
       </c>
       <c r="B156" s="27" t="n"/>
@@ -3563,10 +3566,10 @@
       <c r="I156" s="27" t="n"/>
       <c r="J156" s="57" t="n"/>
     </row>
-    <row r="157" ht="26" customHeight="1" s="6">
+    <row r="157" ht="20" customHeight="1" s="6">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B157" s="27" t="n"/>
@@ -3579,10 +3582,10 @@
       <c r="I157" s="27" t="n"/>
       <c r="J157" s="57" t="n"/>
     </row>
-    <row r="158" ht="26" customHeight="1" s="6">
+    <row r="158" ht="17" customHeight="1" s="6">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ疑問文）：</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B158" s="27" t="n"/>
@@ -3598,7 +3601,7 @@
     <row r="159" ht="20" customHeight="1" s="6">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B159" s="27" t="n"/>
@@ -3611,10 +3614,10 @@
       <c r="I159" s="27" t="n"/>
       <c r="J159" s="57" t="n"/>
     </row>
-    <row r="160" ht="26" customHeight="1" s="6">
+    <row r="160" ht="20" customHeight="1" s="6">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>回答（返答）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B160" s="27" t="n"/>
@@ -3630,7 +3633,7 @@
     <row r="161" ht="20" customHeight="1" s="6">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B161" s="27" t="n"/>
@@ -3643,12 +3646,8 @@
       <c r="I161" s="27" t="n"/>
       <c r="J161" s="57" t="n"/>
     </row>
-    <row r="162" ht="26" customHeight="1" s="6">
-      <c r="A162" s="11" t="inlineStr">
-        <is>
-          <t>回答（基本形）：</t>
-        </is>
-      </c>
+    <row r="162" ht="4" customHeight="1" s="6">
+      <c r="A162" s="8" t="n"/>
       <c r="B162" s="27" t="n"/>
       <c r="C162" s="27" t="n"/>
       <c r="D162" s="27" t="n"/>
@@ -3659,24 +3658,29 @@
       <c r="I162" s="27" t="n"/>
       <c r="J162" s="57" t="n"/>
     </row>
-    <row r="163" ht="26" customHeight="1" s="6">
-      <c r="A163" s="11" t="inlineStr">
-        <is>
-          <t>回答（短縮形）：</t>
-        </is>
-      </c>
-      <c r="B163" s="27" t="n"/>
-      <c r="C163" s="27" t="n"/>
-      <c r="D163" s="27" t="n"/>
-      <c r="E163" s="27" t="n"/>
-      <c r="F163" s="27" t="n"/>
-      <c r="G163" s="27" t="n"/>
-      <c r="H163" s="27" t="n"/>
-      <c r="I163" s="27" t="n"/>
-      <c r="J163" s="57" t="n"/>
-    </row>
-    <row r="164" ht="6" customHeight="1" s="6">
-      <c r="A164" s="8" t="n"/>
+    <row r="163" ht="16" customHeight="1" s="6">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>9．主語は「チサコ」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B163" s="25" t="n"/>
+      <c r="C163" s="25" t="n"/>
+      <c r="D163" s="25" t="n"/>
+      <c r="E163" s="25" t="n"/>
+      <c r="F163" s="25" t="n"/>
+      <c r="G163" s="25" t="n"/>
+      <c r="H163" s="25" t="n"/>
+      <c r="I163" s="25" t="n"/>
+      <c r="J163" s="56" t="n"/>
+    </row>
+    <row r="164" ht="34" customHeight="1" s="6">
+      <c r="A164" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
+        </is>
+      </c>
       <c r="B164" s="27" t="n"/>
       <c r="C164" s="27" t="n"/>
       <c r="D164" s="27" t="n"/>
@@ -3687,30 +3691,319 @@
       <c r="I164" s="27" t="n"/>
       <c r="J164" s="57" t="n"/>
     </row>
+    <row r="165" ht="17" customHeight="1" s="6">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t>チサコは来週テニスをします。</t>
+        </is>
+      </c>
+      <c r="B165" s="27" t="n"/>
+      <c r="C165" s="27" t="n"/>
+      <c r="D165" s="27" t="n"/>
+      <c r="E165" s="27" t="n"/>
+      <c r="F165" s="27" t="n"/>
+      <c r="G165" s="27" t="n"/>
+      <c r="H165" s="27" t="n"/>
+      <c r="I165" s="27" t="n"/>
+      <c r="J165" s="57" t="n"/>
+    </row>
+    <row r="166" ht="20" customHeight="1" s="6">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>回答（will）：</t>
+        </is>
+      </c>
+      <c r="B166" s="27" t="n"/>
+      <c r="C166" s="27" t="n"/>
+      <c r="D166" s="27" t="n"/>
+      <c r="E166" s="27" t="n"/>
+      <c r="F166" s="27" t="n"/>
+      <c r="G166" s="27" t="n"/>
+      <c r="H166" s="27" t="n"/>
+      <c r="I166" s="27" t="n"/>
+      <c r="J166" s="57" t="n"/>
+    </row>
+    <row r="167" ht="20" customHeight="1" s="6">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B167" s="27" t="n"/>
+      <c r="C167" s="27" t="n"/>
+      <c r="D167" s="27" t="n"/>
+      <c r="E167" s="27" t="n"/>
+      <c r="F167" s="27" t="n"/>
+      <c r="G167" s="27" t="n"/>
+      <c r="H167" s="27" t="n"/>
+      <c r="I167" s="27" t="n"/>
+      <c r="J167" s="57" t="n"/>
+    </row>
+    <row r="168" ht="17" customHeight="1" s="6">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>チサコは来週テニスをしません。</t>
+        </is>
+      </c>
+      <c r="B168" s="27" t="n"/>
+      <c r="C168" s="27" t="n"/>
+      <c r="D168" s="27" t="n"/>
+      <c r="E168" s="27" t="n"/>
+      <c r="F168" s="27" t="n"/>
+      <c r="G168" s="27" t="n"/>
+      <c r="H168" s="27" t="n"/>
+      <c r="I168" s="27" t="n"/>
+      <c r="J168" s="57" t="n"/>
+    </row>
+    <row r="169" ht="20" customHeight="1" s="6">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B169" s="27" t="n"/>
+      <c r="C169" s="27" t="n"/>
+      <c r="D169" s="27" t="n"/>
+      <c r="E169" s="27" t="n"/>
+      <c r="F169" s="27" t="n"/>
+      <c r="G169" s="27" t="n"/>
+      <c r="H169" s="27" t="n"/>
+      <c r="I169" s="27" t="n"/>
+      <c r="J169" s="57" t="n"/>
+    </row>
+    <row r="170" ht="20" customHeight="1" s="6">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B170" s="27" t="n"/>
+      <c r="C170" s="27" t="n"/>
+      <c r="D170" s="27" t="n"/>
+      <c r="E170" s="27" t="n"/>
+      <c r="F170" s="27" t="n"/>
+      <c r="G170" s="27" t="n"/>
+      <c r="H170" s="27" t="n"/>
+      <c r="I170" s="27" t="n"/>
+      <c r="J170" s="57" t="n"/>
+    </row>
+    <row r="171" ht="20" customHeight="1" s="6">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ）：</t>
+        </is>
+      </c>
+      <c r="B171" s="27" t="n"/>
+      <c r="C171" s="27" t="n"/>
+      <c r="D171" s="27" t="n"/>
+      <c r="E171" s="27" t="n"/>
+      <c r="F171" s="27" t="n"/>
+      <c r="G171" s="27" t="n"/>
+      <c r="H171" s="27" t="n"/>
+      <c r="I171" s="27" t="n"/>
+      <c r="J171" s="57" t="n"/>
+    </row>
+    <row r="172" ht="17" customHeight="1" s="6">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>チサコは来週テニスをしますか。</t>
+        </is>
+      </c>
+      <c r="B172" s="27" t="n"/>
+      <c r="C172" s="27" t="n"/>
+      <c r="D172" s="27" t="n"/>
+      <c r="E172" s="27" t="n"/>
+      <c r="F172" s="27" t="n"/>
+      <c r="G172" s="27" t="n"/>
+      <c r="H172" s="27" t="n"/>
+      <c r="I172" s="27" t="n"/>
+      <c r="J172" s="57" t="n"/>
+    </row>
+    <row r="173" ht="20" customHeight="1" s="6">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>回答（will疑問文）：</t>
+        </is>
+      </c>
+      <c r="B173" s="27" t="n"/>
+      <c r="C173" s="27" t="n"/>
+      <c r="D173" s="27" t="n"/>
+      <c r="E173" s="27" t="n"/>
+      <c r="F173" s="27" t="n"/>
+      <c r="G173" s="27" t="n"/>
+      <c r="H173" s="27" t="n"/>
+      <c r="I173" s="27" t="n"/>
+      <c r="J173" s="57" t="n"/>
+    </row>
+    <row r="174" ht="20" customHeight="1" s="6">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ疑問文）：</t>
+        </is>
+      </c>
+      <c r="B174" s="27" t="n"/>
+      <c r="C174" s="27" t="n"/>
+      <c r="D174" s="27" t="n"/>
+      <c r="E174" s="27" t="n"/>
+      <c r="F174" s="27" t="n"/>
+      <c r="G174" s="27" t="n"/>
+      <c r="H174" s="27" t="n"/>
+      <c r="I174" s="27" t="n"/>
+      <c r="J174" s="57" t="n"/>
+    </row>
+    <row r="175" ht="17" customHeight="1" s="6">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>はい、します。</t>
+        </is>
+      </c>
+      <c r="B175" s="27" t="n"/>
+      <c r="C175" s="27" t="n"/>
+      <c r="D175" s="27" t="n"/>
+      <c r="E175" s="27" t="n"/>
+      <c r="F175" s="27" t="n"/>
+      <c r="G175" s="27" t="n"/>
+      <c r="H175" s="27" t="n"/>
+      <c r="I175" s="27" t="n"/>
+      <c r="J175" s="57" t="n"/>
+    </row>
+    <row r="176" ht="20" customHeight="1" s="6">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t>回答（will返答）：</t>
+        </is>
+      </c>
+      <c r="B176" s="27" t="n"/>
+      <c r="C176" s="27" t="n"/>
+      <c r="D176" s="27" t="n"/>
+      <c r="E176" s="27" t="n"/>
+      <c r="F176" s="27" t="n"/>
+      <c r="G176" s="27" t="n"/>
+      <c r="H176" s="27" t="n"/>
+      <c r="I176" s="27" t="n"/>
+      <c r="J176" s="57" t="n"/>
+    </row>
+    <row r="177" ht="20" customHeight="1" s="6">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ返答）：</t>
+        </is>
+      </c>
+      <c r="B177" s="27" t="n"/>
+      <c r="C177" s="27" t="n"/>
+      <c r="D177" s="27" t="n"/>
+      <c r="E177" s="27" t="n"/>
+      <c r="F177" s="27" t="n"/>
+      <c r="G177" s="27" t="n"/>
+      <c r="H177" s="27" t="n"/>
+      <c r="I177" s="27" t="n"/>
+      <c r="J177" s="57" t="n"/>
+    </row>
+    <row r="178" ht="17" customHeight="1" s="6">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、しません。</t>
+        </is>
+      </c>
+      <c r="B178" s="27" t="n"/>
+      <c r="C178" s="27" t="n"/>
+      <c r="D178" s="27" t="n"/>
+      <c r="E178" s="27" t="n"/>
+      <c r="F178" s="27" t="n"/>
+      <c r="G178" s="27" t="n"/>
+      <c r="H178" s="27" t="n"/>
+      <c r="I178" s="27" t="n"/>
+      <c r="J178" s="57" t="n"/>
+    </row>
+    <row r="179" ht="20" customHeight="1" s="6">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B179" s="27" t="n"/>
+      <c r="C179" s="27" t="n"/>
+      <c r="D179" s="27" t="n"/>
+      <c r="E179" s="27" t="n"/>
+      <c r="F179" s="27" t="n"/>
+      <c r="G179" s="27" t="n"/>
+      <c r="H179" s="27" t="n"/>
+      <c r="I179" s="27" t="n"/>
+      <c r="J179" s="57" t="n"/>
+    </row>
+    <row r="180" ht="20" customHeight="1" s="6">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B180" s="27" t="n"/>
+      <c r="C180" s="27" t="n"/>
+      <c r="D180" s="27" t="n"/>
+      <c r="E180" s="27" t="n"/>
+      <c r="F180" s="27" t="n"/>
+      <c r="G180" s="27" t="n"/>
+      <c r="H180" s="27" t="n"/>
+      <c r="I180" s="27" t="n"/>
+      <c r="J180" s="57" t="n"/>
+    </row>
+    <row r="181" ht="20" customHeight="1" s="6">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ返答）：</t>
+        </is>
+      </c>
+      <c r="B181" s="27" t="n"/>
+      <c r="C181" s="27" t="n"/>
+      <c r="D181" s="27" t="n"/>
+      <c r="E181" s="27" t="n"/>
+      <c r="F181" s="27" t="n"/>
+      <c r="G181" s="27" t="n"/>
+      <c r="H181" s="27" t="n"/>
+      <c r="I181" s="27" t="n"/>
+      <c r="J181" s="57" t="n"/>
+    </row>
+    <row r="182" ht="4" customHeight="1" s="6">
+      <c r="A182" s="8" t="n"/>
+      <c r="B182" s="27" t="n"/>
+      <c r="C182" s="27" t="n"/>
+      <c r="D182" s="27" t="n"/>
+      <c r="E182" s="27" t="n"/>
+      <c r="F182" s="27" t="n"/>
+      <c r="G182" s="27" t="n"/>
+      <c r="H182" s="27" t="n"/>
+      <c r="I182" s="27" t="n"/>
+      <c r="J182" s="57" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="164">
+  <mergeCells count="182">
     <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A181:J181"/>
     <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A156:J156"/>
     <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A156:J156"/>
+    <mergeCell ref="A171:J171"/>
+    <mergeCell ref="A165:J165"/>
     <mergeCell ref="A52:J52"/>
     <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A155:J155"/>
     <mergeCell ref="A115:J115"/>
-    <mergeCell ref="A155:J155"/>
     <mergeCell ref="A93:J93"/>
+    <mergeCell ref="A173:J173"/>
     <mergeCell ref="A130:J130"/>
     <mergeCell ref="A77:J77"/>
+    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A148:J148"/>
     <mergeCell ref="A157:J157"/>
+    <mergeCell ref="A138:J138"/>
     <mergeCell ref="A49:J49"/>
-    <mergeCell ref="A138:J138"/>
     <mergeCell ref="A132:J132"/>
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="A119:J119"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A69:J69"/>
+    <mergeCell ref="A174:J174"/>
     <mergeCell ref="A66:J66"/>
     <mergeCell ref="A118:J118"/>
     <mergeCell ref="A75:J75"/>
@@ -3721,6 +4014,7 @@
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A95:J95"/>
     <mergeCell ref="A104:J104"/>
+    <mergeCell ref="A175:J175"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="A14:J14"/>
@@ -3730,12 +4024,13 @@
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A81:J81"/>
+    <mergeCell ref="A96:J96"/>
     <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A96:J96"/>
     <mergeCell ref="A147:J147"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A161:J161"/>
     <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A170:J170"/>
     <mergeCell ref="A44:J44"/>
     <mergeCell ref="A31:J31"/>
     <mergeCell ref="A58:J58"/>
@@ -3751,6 +4046,7 @@
     <mergeCell ref="A146:J146"/>
     <mergeCell ref="A124:J124"/>
     <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A172:J172"/>
     <mergeCell ref="A16:J16"/>
     <mergeCell ref="A25:J25"/>
     <mergeCell ref="A108:J108"/>
@@ -3763,14 +4059,14 @@
     <mergeCell ref="A86:J86"/>
     <mergeCell ref="A42:J42"/>
     <mergeCell ref="A151:J151"/>
+    <mergeCell ref="A160:J160"/>
     <mergeCell ref="A47:J47"/>
-    <mergeCell ref="A160:J160"/>
     <mergeCell ref="A141:J141"/>
     <mergeCell ref="A135:J135"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A150:J150"/>
+    <mergeCell ref="A144:J144"/>
     <mergeCell ref="A62:J62"/>
-    <mergeCell ref="A144:J144"/>
     <mergeCell ref="A122:J122"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A125:J125"/>
@@ -3780,29 +4076,35 @@
     <mergeCell ref="A112:J112"/>
     <mergeCell ref="A152:J152"/>
     <mergeCell ref="A127:J127"/>
+    <mergeCell ref="A167:J167"/>
+    <mergeCell ref="A176:J176"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A114:J114"/>
     <mergeCell ref="A59:J59"/>
+    <mergeCell ref="A182:J182"/>
     <mergeCell ref="A64:J64"/>
     <mergeCell ref="A98:J98"/>
+    <mergeCell ref="A169:J169"/>
     <mergeCell ref="A51:J51"/>
     <mergeCell ref="A107:J107"/>
+    <mergeCell ref="A178:J178"/>
     <mergeCell ref="A79:J79"/>
     <mergeCell ref="A61:J61"/>
     <mergeCell ref="A88:J88"/>
     <mergeCell ref="A70:J70"/>
+    <mergeCell ref="A162:J162"/>
     <mergeCell ref="A153:J153"/>
-    <mergeCell ref="A162:J162"/>
     <mergeCell ref="A54:J54"/>
     <mergeCell ref="A137:J137"/>
+    <mergeCell ref="A177:J177"/>
     <mergeCell ref="A90:J90"/>
     <mergeCell ref="A41:J41"/>
     <mergeCell ref="A99:J99"/>
     <mergeCell ref="A164:J164"/>
     <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A145:J145"/>
     <mergeCell ref="A56:J56"/>
     <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A145:J145"/>
     <mergeCell ref="A139:J139"/>
     <mergeCell ref="A154:J154"/>
     <mergeCell ref="A163:J163"/>
@@ -3820,6 +4122,7 @@
     <mergeCell ref="A53:J53"/>
     <mergeCell ref="A109:J109"/>
     <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A180:J180"/>
     <mergeCell ref="A129:J129"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A68:J68"/>
@@ -3831,6 +4134,7 @@
     <mergeCell ref="A143:J143"/>
     <mergeCell ref="A92:J92"/>
     <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A166:J166"/>
     <mergeCell ref="A48:J48"/>
     <mergeCell ref="A142:J142"/>
     <mergeCell ref="A11:J11"/>
@@ -3838,6 +4142,7 @@
     <mergeCell ref="A94:J94"/>
     <mergeCell ref="A45:J45"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A168:J168"/>
     <mergeCell ref="A78:J78"/>
     <mergeCell ref="A87:J87"/>
     <mergeCell ref="A65:J65"/>
@@ -3852,16 +4157,17 @@
     <mergeCell ref="A57:J57"/>
     <mergeCell ref="A26:J26"/>
     <mergeCell ref="A113:J113"/>
+    <mergeCell ref="A179:J179"/>
     <mergeCell ref="A71:J71"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1" verticalDpi="0"/>
   <rowBreaks count="4" manualBreakCount="4">
-    <brk id="38" min="0" max="16383" man="1"/>
-    <brk id="74" min="0" max="16383" man="1"/>
-    <brk id="110" min="0" max="16383" man="1"/>
-    <brk id="146" min="0" max="16383" man="1"/>
+    <brk id="42" min="0" max="16383" man="1"/>
+    <brk id="82" min="0" max="16383" man="1"/>
+    <brk id="122" min="0" max="16383" man="1"/>
+    <brk id="162" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -3872,7 +4178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J164"/>
+  <dimension ref="A1:J182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="13" customWidth="1" style="6" min="1" max="1"/>
@@ -3903,7 +4209,7 @@
       <c r="I1" s="25" t="n"/>
       <c r="J1" s="56" t="n"/>
     </row>
-    <row r="2" ht="6" customHeight="1" s="6">
+    <row r="2" ht="4" customHeight="1" s="6">
       <c r="A2" s="8" t="n"/>
       <c r="B2" s="27" t="n"/>
       <c r="C2" s="27" t="n"/>
@@ -3915,7 +4221,7 @@
       <c r="I2" s="27" t="n"/>
       <c r="J2" s="57" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="6">
+    <row r="3" ht="16" customHeight="1" s="6">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>1．主語は「私」で書いてください。</t>
@@ -3931,7 +4237,7 @@
       <c r="I3" s="25" t="n"/>
       <c r="J3" s="56" t="n"/>
     </row>
-    <row r="4" ht="48" customHeight="1" s="6">
+    <row r="4" ht="40" customHeight="1" s="6">
       <c r="A4" s="55" t="inlineStr">
         <is>
           <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
@@ -3949,7 +4255,7 @@
       <c r="I4" s="27" t="n"/>
       <c r="J4" s="57" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1" s="6">
+    <row r="5" ht="17" customHeight="1" s="6">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>私は来週テニスをします。</t>
@@ -3965,7 +4271,7 @@
       <c r="I5" s="27" t="n"/>
       <c r="J5" s="57" t="n"/>
     </row>
-    <row r="6" ht="26" customHeight="1" s="6">
+    <row r="6" ht="20" customHeight="1" s="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>正解（will）：I will play tennis next week.</t>
@@ -3981,7 +4287,7 @@
       <c r="I6" s="27" t="n"/>
       <c r="J6" s="57" t="n"/>
     </row>
-    <row r="7" ht="26" customHeight="1" s="6">
+    <row r="7" ht="20" customHeight="1" s="6">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>正解（言いかえ）：I am going to play tennis next week.</t>
@@ -3997,7 +4303,7 @@
       <c r="I7" s="27" t="n"/>
       <c r="J7" s="57" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1" s="6">
+    <row r="8" ht="17" customHeight="1" s="6">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>私は来週テニスをしません。</t>
@@ -4013,7 +4319,7 @@
       <c r="I8" s="27" t="n"/>
       <c r="J8" s="57" t="n"/>
     </row>
-    <row r="9" ht="26" customHeight="1" s="6">
+    <row r="9" ht="20" customHeight="1" s="6">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>正解（基本形）：I will not play tennis next week.</t>
@@ -4029,7 +4335,7 @@
       <c r="I9" s="27" t="n"/>
       <c r="J9" s="57" t="n"/>
     </row>
-    <row r="10" ht="26" customHeight="1" s="6">
+    <row r="10" ht="20" customHeight="1" s="6">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>正解（短縮形）：I won't play tennis next week.</t>
@@ -4045,7 +4351,7 @@
       <c r="I10" s="27" t="n"/>
       <c r="J10" s="57" t="n"/>
     </row>
-    <row r="11" ht="26" customHeight="1" s="6">
+    <row r="11" ht="20" customHeight="1" s="6">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>正解（言いかえ）：I am not going to play tennis next week.</t>
@@ -4061,7 +4367,7 @@
       <c r="I11" s="27" t="n"/>
       <c r="J11" s="57" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1" s="6">
+    <row r="12" ht="17" customHeight="1" s="6">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>私は来週テニスをしますか。</t>
@@ -4077,7 +4383,7 @@
       <c r="I12" s="27" t="n"/>
       <c r="J12" s="57" t="n"/>
     </row>
-    <row r="13" ht="26" customHeight="1" s="6">
+    <row r="13" ht="20" customHeight="1" s="6">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>正解（will疑問文）：Will I play tennis next week?</t>
@@ -4093,7 +4399,7 @@
       <c r="I13" s="27" t="n"/>
       <c r="J13" s="57" t="n"/>
     </row>
-    <row r="14" ht="26" customHeight="1" s="6">
+    <row r="14" ht="20" customHeight="1" s="6">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>正解（言いかえ疑問文）：Am I going to play tennis next week?</t>
@@ -4109,7 +4415,7 @@
       <c r="I14" s="27" t="n"/>
       <c r="J14" s="57" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1" s="6">
+    <row r="15" ht="17" customHeight="1" s="6">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>はい、します。</t>
@@ -4125,10 +4431,10 @@
       <c r="I15" s="27" t="n"/>
       <c r="J15" s="57" t="n"/>
     </row>
-    <row r="16" ht="26" customHeight="1" s="6">
+    <row r="16" ht="20" customHeight="1" s="6">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>正解（返答）：Yes, you will.</t>
+          <t>正解（will返答）：Yes, you will.</t>
         </is>
       </c>
       <c r="B16" s="27" t="n"/>
@@ -4144,7 +4450,7 @@
     <row r="17" ht="20" customHeight="1" s="6">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>正解（言いかえ返答）：Yes, you are.</t>
         </is>
       </c>
       <c r="B17" s="27" t="n"/>
@@ -4157,10 +4463,10 @@
       <c r="I17" s="27" t="n"/>
       <c r="J17" s="57" t="n"/>
     </row>
-    <row r="18" ht="26" customHeight="1" s="6">
+    <row r="18" ht="17" customHeight="1" s="6">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, you will not.</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B18" s="27" t="n"/>
@@ -4173,10 +4479,10 @@
       <c r="I18" s="27" t="n"/>
       <c r="J18" s="57" t="n"/>
     </row>
-    <row r="19" ht="26" customHeight="1" s="6">
+    <row r="19" ht="20" customHeight="1" s="6">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, you won't.</t>
+          <t>正解（基本形）：No, you will not.</t>
         </is>
       </c>
       <c r="B19" s="27" t="n"/>
@@ -4189,8 +4495,12 @@
       <c r="I19" s="27" t="n"/>
       <c r="J19" s="57" t="n"/>
     </row>
-    <row r="20" ht="6" customHeight="1" s="6">
-      <c r="A20" s="8" t="n"/>
+    <row r="20" ht="20" customHeight="1" s="6">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：No, you won't.</t>
+        </is>
+      </c>
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="27" t="n"/>
       <c r="D20" s="27" t="n"/>
@@ -4201,29 +4511,24 @@
       <c r="I20" s="27" t="n"/>
       <c r="J20" s="57" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1" s="6">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>2．主語は「あなた」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="n"/>
-      <c r="C21" s="25" t="n"/>
-      <c r="D21" s="25" t="n"/>
-      <c r="E21" s="25" t="n"/>
-      <c r="F21" s="25" t="n"/>
-      <c r="G21" s="25" t="n"/>
-      <c r="H21" s="25" t="n"/>
-      <c r="I21" s="25" t="n"/>
-      <c r="J21" s="56" t="n"/>
-    </row>
-    <row r="22" ht="40" customHeight="1" s="6">
-      <c r="A22" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
-        </is>
-      </c>
+    <row r="21" ht="20" customHeight="1" s="6">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ返答）：No, you are not.</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="27" t="n"/>
+      <c r="G21" s="27" t="n"/>
+      <c r="H21" s="27" t="n"/>
+      <c r="I21" s="27" t="n"/>
+      <c r="J21" s="57" t="n"/>
+    </row>
+    <row r="22" ht="4" customHeight="1" s="6">
+      <c r="A22" s="8" t="n"/>
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="27" t="n"/>
       <c r="D22" s="27" t="n"/>
@@ -4234,26 +4539,27 @@
       <c r="I22" s="27" t="n"/>
       <c r="J22" s="57" t="n"/>
     </row>
-    <row r="23" ht="20" customHeight="1" s="6">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>あなたは来週テニスをします。</t>
-        </is>
-      </c>
-      <c r="B23" s="27" t="n"/>
-      <c r="C23" s="27" t="n"/>
-      <c r="D23" s="27" t="n"/>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="27" t="n"/>
-      <c r="H23" s="27" t="n"/>
-      <c r="I23" s="27" t="n"/>
-      <c r="J23" s="57" t="n"/>
-    </row>
-    <row r="24" ht="26" customHeight="1" s="6">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>正解（will）：You will play tennis next week.</t>
+    <row r="23" ht="16" customHeight="1" s="6">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>2．主語は「あなた」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="n"/>
+      <c r="C23" s="25" t="n"/>
+      <c r="D23" s="25" t="n"/>
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="25" t="n"/>
+      <c r="G23" s="25" t="n"/>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
+      <c r="J23" s="56" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1" s="6">
+      <c r="A24" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B24" s="27" t="n"/>
@@ -4266,10 +4572,10 @@
       <c r="I24" s="27" t="n"/>
       <c r="J24" s="57" t="n"/>
     </row>
-    <row r="25" ht="26" customHeight="1" s="6">
+    <row r="25" ht="17" customHeight="1" s="6">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：You are going to play tennis next week.</t>
+          <t>あなたは来週テニスをします。</t>
         </is>
       </c>
       <c r="B25" s="27" t="n"/>
@@ -4285,7 +4591,7 @@
     <row r="26" ht="20" customHeight="1" s="6">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>あなたは来週テニスをしません。</t>
+          <t>正解（will）：You will play tennis next week.</t>
         </is>
       </c>
       <c r="B26" s="27" t="n"/>
@@ -4298,10 +4604,10 @@
       <c r="I26" s="27" t="n"/>
       <c r="J26" s="57" t="n"/>
     </row>
-    <row r="27" ht="26" customHeight="1" s="6">
+    <row r="27" ht="20" customHeight="1" s="6">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：You will not play tennis next week.</t>
+          <t>正解（言いかえ）：You are going to play tennis next week.</t>
         </is>
       </c>
       <c r="B27" s="27" t="n"/>
@@ -4314,10 +4620,10 @@
       <c r="I27" s="27" t="n"/>
       <c r="J27" s="57" t="n"/>
     </row>
-    <row r="28" ht="26" customHeight="1" s="6">
+    <row r="28" ht="17" customHeight="1" s="6">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：You won't play tennis next week.</t>
+          <t>あなたは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B28" s="27" t="n"/>
@@ -4330,10 +4636,10 @@
       <c r="I28" s="27" t="n"/>
       <c r="J28" s="57" t="n"/>
     </row>
-    <row r="29" ht="26" customHeight="1" s="6">
+    <row r="29" ht="20" customHeight="1" s="6">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：You are not going to play tennis next week.</t>
+          <t>正解（基本形）：You will not play tennis next week.</t>
         </is>
       </c>
       <c r="B29" s="27" t="n"/>
@@ -4349,7 +4655,7 @@
     <row r="30" ht="20" customHeight="1" s="6">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>あなたは来週テニスをしますか。</t>
+          <t>正解（短縮形）：You won't play tennis next week.</t>
         </is>
       </c>
       <c r="B30" s="27" t="n"/>
@@ -4362,10 +4668,10 @@
       <c r="I30" s="27" t="n"/>
       <c r="J30" s="57" t="n"/>
     </row>
-    <row r="31" ht="26" customHeight="1" s="6">
+    <row r="31" ht="20" customHeight="1" s="6">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will you play tennis next week?</t>
+          <t>正解（言いかえ）：You are not going to play tennis next week.</t>
         </is>
       </c>
       <c r="B31" s="27" t="n"/>
@@ -4378,10 +4684,10 @@
       <c r="I31" s="27" t="n"/>
       <c r="J31" s="57" t="n"/>
     </row>
-    <row r="32" ht="26" customHeight="1" s="6">
+    <row r="32" ht="17" customHeight="1" s="6">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ疑問文）：Are you going to play tennis next week?</t>
+          <t>あなたは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B32" s="27" t="n"/>
@@ -4397,7 +4703,7 @@
     <row r="33" ht="20" customHeight="1" s="6">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>正解（will疑問文）：Will you play tennis next week?</t>
         </is>
       </c>
       <c r="B33" s="27" t="n"/>
@@ -4410,10 +4716,10 @@
       <c r="I33" s="27" t="n"/>
       <c r="J33" s="57" t="n"/>
     </row>
-    <row r="34" ht="26" customHeight="1" s="6">
+    <row r="34" ht="20" customHeight="1" s="6">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>正解（返答）：Yes, I will.</t>
+          <t>正解（言いかえ疑問文）：Are you going to play tennis next week?</t>
         </is>
       </c>
       <c r="B34" s="27" t="n"/>
@@ -4426,10 +4732,10 @@
       <c r="I34" s="27" t="n"/>
       <c r="J34" s="57" t="n"/>
     </row>
-    <row r="35" ht="20" customHeight="1" s="6">
+    <row r="35" ht="17" customHeight="1" s="6">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B35" s="27" t="n"/>
@@ -4442,10 +4748,10 @@
       <c r="I35" s="27" t="n"/>
       <c r="J35" s="57" t="n"/>
     </row>
-    <row r="36" ht="26" customHeight="1" s="6">
+    <row r="36" ht="20" customHeight="1" s="6">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, I will not.</t>
+          <t>正解（will返答）：Yes, I will.</t>
         </is>
       </c>
       <c r="B36" s="27" t="n"/>
@@ -4458,10 +4764,10 @@
       <c r="I36" s="27" t="n"/>
       <c r="J36" s="57" t="n"/>
     </row>
-    <row r="37" ht="26" customHeight="1" s="6">
+    <row r="37" ht="20" customHeight="1" s="6">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, I won't.</t>
+          <t>正解（言いかえ返答）：Yes, I am.</t>
         </is>
       </c>
       <c r="B37" s="27" t="n"/>
@@ -4474,8 +4780,12 @@
       <c r="I37" s="27" t="n"/>
       <c r="J37" s="57" t="n"/>
     </row>
-    <row r="38" ht="6" customHeight="1" s="6">
-      <c r="A38" s="8" t="n"/>
+    <row r="38" ht="17" customHeight="1" s="6">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、しません。</t>
+        </is>
+      </c>
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="27" t="n"/>
       <c r="D38" s="27" t="n"/>
@@ -4486,27 +4796,26 @@
       <c r="I38" s="27" t="n"/>
       <c r="J38" s="57" t="n"/>
     </row>
-    <row r="39" ht="18" customHeight="1" s="6">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>3．主語は「彼」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B39" s="25" t="n"/>
-      <c r="C39" s="25" t="n"/>
-      <c r="D39" s="25" t="n"/>
-      <c r="E39" s="25" t="n"/>
-      <c r="F39" s="25" t="n"/>
-      <c r="G39" s="25" t="n"/>
-      <c r="H39" s="25" t="n"/>
-      <c r="I39" s="25" t="n"/>
-      <c r="J39" s="56" t="n"/>
-    </row>
-    <row r="40" ht="40" customHeight="1" s="6">
-      <c r="A40" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="39" ht="20" customHeight="1" s="6">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：No, I will not.</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="n"/>
+      <c r="C39" s="27" t="n"/>
+      <c r="D39" s="27" t="n"/>
+      <c r="E39" s="27" t="n"/>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="n"/>
+      <c r="H39" s="27" t="n"/>
+      <c r="I39" s="27" t="n"/>
+      <c r="J39" s="57" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1" s="6">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：No, I won't.</t>
         </is>
       </c>
       <c r="B40" s="27" t="n"/>
@@ -4522,7 +4831,7 @@
     <row r="41" ht="20" customHeight="1" s="6">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>彼は来週テニスをします。</t>
+          <t>正解（言いかえ返答）：No, I am not.</t>
         </is>
       </c>
       <c r="B41" s="27" t="n"/>
@@ -4535,12 +4844,8 @@
       <c r="I41" s="27" t="n"/>
       <c r="J41" s="57" t="n"/>
     </row>
-    <row r="42" ht="26" customHeight="1" s="6">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>正解（will）：He will play tennis next week.</t>
-        </is>
-      </c>
+    <row r="42" ht="4" customHeight="1" s="6">
+      <c r="A42" s="8" t="n"/>
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="27" t="n"/>
       <c r="D42" s="27" t="n"/>
@@ -4551,26 +4856,27 @@
       <c r="I42" s="27" t="n"/>
       <c r="J42" s="57" t="n"/>
     </row>
-    <row r="43" ht="26" customHeight="1" s="6">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>正解（言いかえ）：He is going to play tennis next week.</t>
-        </is>
-      </c>
-      <c r="B43" s="27" t="n"/>
-      <c r="C43" s="27" t="n"/>
-      <c r="D43" s="27" t="n"/>
-      <c r="E43" s="27" t="n"/>
-      <c r="F43" s="27" t="n"/>
-      <c r="G43" s="27" t="n"/>
-      <c r="H43" s="27" t="n"/>
-      <c r="I43" s="27" t="n"/>
-      <c r="J43" s="57" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1" s="6">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>彼は来週テニスをしません。</t>
+    <row r="43" ht="16" customHeight="1" s="6">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>3．主語は「彼」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="n"/>
+      <c r="C43" s="25" t="n"/>
+      <c r="D43" s="25" t="n"/>
+      <c r="E43" s="25" t="n"/>
+      <c r="F43" s="25" t="n"/>
+      <c r="G43" s="25" t="n"/>
+      <c r="H43" s="25" t="n"/>
+      <c r="I43" s="25" t="n"/>
+      <c r="J43" s="56" t="n"/>
+    </row>
+    <row r="44" ht="34" customHeight="1" s="6">
+      <c r="A44" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B44" s="27" t="n"/>
@@ -4583,10 +4889,10 @@
       <c r="I44" s="27" t="n"/>
       <c r="J44" s="57" t="n"/>
     </row>
-    <row r="45" ht="26" customHeight="1" s="6">
+    <row r="45" ht="17" customHeight="1" s="6">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：He will not play tennis next week.</t>
+          <t>彼は来週テニスをします。</t>
         </is>
       </c>
       <c r="B45" s="27" t="n"/>
@@ -4599,10 +4905,10 @@
       <c r="I45" s="27" t="n"/>
       <c r="J45" s="57" t="n"/>
     </row>
-    <row r="46" ht="26" customHeight="1" s="6">
+    <row r="46" ht="20" customHeight="1" s="6">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：He won't play tennis next week.</t>
+          <t>正解（will）：He will play tennis next week.</t>
         </is>
       </c>
       <c r="B46" s="27" t="n"/>
@@ -4615,10 +4921,10 @@
       <c r="I46" s="27" t="n"/>
       <c r="J46" s="57" t="n"/>
     </row>
-    <row r="47" ht="26" customHeight="1" s="6">
+    <row r="47" ht="20" customHeight="1" s="6">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：He is not going to play tennis next week.</t>
+          <t>正解（言いかえ）：He is going to play tennis next week.</t>
         </is>
       </c>
       <c r="B47" s="27" t="n"/>
@@ -4631,10 +4937,10 @@
       <c r="I47" s="27" t="n"/>
       <c r="J47" s="57" t="n"/>
     </row>
-    <row r="48" ht="20" customHeight="1" s="6">
+    <row r="48" ht="17" customHeight="1" s="6">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>彼は来週テニスをしますか。</t>
+          <t>彼は来週テニスをしません。</t>
         </is>
       </c>
       <c r="B48" s="27" t="n"/>
@@ -4647,10 +4953,10 @@
       <c r="I48" s="27" t="n"/>
       <c r="J48" s="57" t="n"/>
     </row>
-    <row r="49" ht="26" customHeight="1" s="6">
+    <row r="49" ht="20" customHeight="1" s="6">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will he play tennis next week?</t>
+          <t>正解（基本形）：He will not play tennis next week.</t>
         </is>
       </c>
       <c r="B49" s="27" t="n"/>
@@ -4663,10 +4969,10 @@
       <c r="I49" s="27" t="n"/>
       <c r="J49" s="57" t="n"/>
     </row>
-    <row r="50" ht="26" customHeight="1" s="6">
+    <row r="50" ht="20" customHeight="1" s="6">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ疑問文）：Is he going to play tennis next week?</t>
+          <t>正解（短縮形）：He won't play tennis next week.</t>
         </is>
       </c>
       <c r="B50" s="27" t="n"/>
@@ -4682,7 +4988,7 @@
     <row r="51" ht="20" customHeight="1" s="6">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>正解（言いかえ）：He is not going to play tennis next week.</t>
         </is>
       </c>
       <c r="B51" s="27" t="n"/>
@@ -4695,10 +5001,10 @@
       <c r="I51" s="27" t="n"/>
       <c r="J51" s="57" t="n"/>
     </row>
-    <row r="52" ht="26" customHeight="1" s="6">
+    <row r="52" ht="17" customHeight="1" s="6">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>正解（返答）：Yes, he will.</t>
+          <t>彼は来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B52" s="27" t="n"/>
@@ -4714,7 +5020,7 @@
     <row r="53" ht="20" customHeight="1" s="6">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>正解（will疑問文）：Will he play tennis next week?</t>
         </is>
       </c>
       <c r="B53" s="27" t="n"/>
@@ -4727,10 +5033,10 @@
       <c r="I53" s="27" t="n"/>
       <c r="J53" s="57" t="n"/>
     </row>
-    <row r="54" ht="26" customHeight="1" s="6">
+    <row r="54" ht="20" customHeight="1" s="6">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, he will not.</t>
+          <t>正解（言いかえ疑問文）：Is he going to play tennis next week?</t>
         </is>
       </c>
       <c r="B54" s="27" t="n"/>
@@ -4743,10 +5049,10 @@
       <c r="I54" s="27" t="n"/>
       <c r="J54" s="57" t="n"/>
     </row>
-    <row r="55" ht="26" customHeight="1" s="6">
+    <row r="55" ht="17" customHeight="1" s="6">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, he won't.</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B55" s="27" t="n"/>
@@ -4759,8 +5065,12 @@
       <c r="I55" s="27" t="n"/>
       <c r="J55" s="57" t="n"/>
     </row>
-    <row r="56" ht="6" customHeight="1" s="6">
-      <c r="A56" s="8" t="n"/>
+    <row r="56" ht="20" customHeight="1" s="6">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>正解（will返答）：Yes, he will.</t>
+        </is>
+      </c>
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="27" t="n"/>
       <c r="D56" s="27" t="n"/>
@@ -4771,27 +5081,26 @@
       <c r="I56" s="27" t="n"/>
       <c r="J56" s="57" t="n"/>
     </row>
-    <row r="57" ht="18" customHeight="1" s="6">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>4．主語は「彼女」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B57" s="25" t="n"/>
-      <c r="C57" s="25" t="n"/>
-      <c r="D57" s="25" t="n"/>
-      <c r="E57" s="25" t="n"/>
-      <c r="F57" s="25" t="n"/>
-      <c r="G57" s="25" t="n"/>
-      <c r="H57" s="25" t="n"/>
-      <c r="I57" s="25" t="n"/>
-      <c r="J57" s="56" t="n"/>
-    </row>
-    <row r="58" ht="40" customHeight="1" s="6">
-      <c r="A58" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="57" ht="20" customHeight="1" s="6">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ返答）：Yes, he is.</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="n"/>
+      <c r="C57" s="27" t="n"/>
+      <c r="D57" s="27" t="n"/>
+      <c r="E57" s="27" t="n"/>
+      <c r="F57" s="27" t="n"/>
+      <c r="G57" s="27" t="n"/>
+      <c r="H57" s="27" t="n"/>
+      <c r="I57" s="27" t="n"/>
+      <c r="J57" s="57" t="n"/>
+    </row>
+    <row r="58" ht="17" customHeight="1" s="6">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B58" s="27" t="n"/>
@@ -4807,7 +5116,7 @@
     <row r="59" ht="20" customHeight="1" s="6">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>彼女は来週テニスをします。</t>
+          <t>正解（基本形）：No, he will not.</t>
         </is>
       </c>
       <c r="B59" s="27" t="n"/>
@@ -4820,10 +5129,10 @@
       <c r="I59" s="27" t="n"/>
       <c r="J59" s="57" t="n"/>
     </row>
-    <row r="60" ht="26" customHeight="1" s="6">
+    <row r="60" ht="20" customHeight="1" s="6">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>正解（will）：She will play tennis next week.</t>
+          <t>正解（短縮形）：No, he won't.</t>
         </is>
       </c>
       <c r="B60" s="27" t="n"/>
@@ -4836,10 +5145,10 @@
       <c r="I60" s="27" t="n"/>
       <c r="J60" s="57" t="n"/>
     </row>
-    <row r="61" ht="26" customHeight="1" s="6">
+    <row r="61" ht="20" customHeight="1" s="6">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：She is going to play tennis next week.</t>
+          <t>正解（言いかえ返答）：No, he is not.</t>
         </is>
       </c>
       <c r="B61" s="27" t="n"/>
@@ -4852,12 +5161,8 @@
       <c r="I61" s="27" t="n"/>
       <c r="J61" s="57" t="n"/>
     </row>
-    <row r="62" ht="20" customHeight="1" s="6">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>彼女は来週テニスをしません。</t>
-        </is>
-      </c>
+    <row r="62" ht="4" customHeight="1" s="6">
+      <c r="A62" s="8" t="n"/>
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="27" t="n"/>
       <c r="D62" s="27" t="n"/>
@@ -4868,26 +5173,27 @@
       <c r="I62" s="27" t="n"/>
       <c r="J62" s="57" t="n"/>
     </row>
-    <row r="63" ht="26" customHeight="1" s="6">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>正解（基本形）：She will not play tennis next week.</t>
-        </is>
-      </c>
-      <c r="B63" s="27" t="n"/>
-      <c r="C63" s="27" t="n"/>
-      <c r="D63" s="27" t="n"/>
-      <c r="E63" s="27" t="n"/>
-      <c r="F63" s="27" t="n"/>
-      <c r="G63" s="27" t="n"/>
-      <c r="H63" s="27" t="n"/>
-      <c r="I63" s="27" t="n"/>
-      <c r="J63" s="57" t="n"/>
-    </row>
-    <row r="64" ht="26" customHeight="1" s="6">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>正解（短縮形）：She won't play tennis next week.</t>
+    <row r="63" ht="16" customHeight="1" s="6">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>4．主語は「彼女」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B63" s="25" t="n"/>
+      <c r="C63" s="25" t="n"/>
+      <c r="D63" s="25" t="n"/>
+      <c r="E63" s="25" t="n"/>
+      <c r="F63" s="25" t="n"/>
+      <c r="G63" s="25" t="n"/>
+      <c r="H63" s="25" t="n"/>
+      <c r="I63" s="25" t="n"/>
+      <c r="J63" s="56" t="n"/>
+    </row>
+    <row r="64" ht="34" customHeight="1" s="6">
+      <c r="A64" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B64" s="27" t="n"/>
@@ -4900,10 +5206,10 @@
       <c r="I64" s="27" t="n"/>
       <c r="J64" s="57" t="n"/>
     </row>
-    <row r="65" ht="26" customHeight="1" s="6">
+    <row r="65" ht="17" customHeight="1" s="6">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：She is not going to play tennis next week.</t>
+          <t>彼女は来週テニスをします。</t>
         </is>
       </c>
       <c r="B65" s="27" t="n"/>
@@ -4919,7 +5225,7 @@
     <row r="66" ht="20" customHeight="1" s="6">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>彼女は来週テニスをしますか。</t>
+          <t>正解（will）：She will play tennis next week.</t>
         </is>
       </c>
       <c r="B66" s="27" t="n"/>
@@ -4932,10 +5238,10 @@
       <c r="I66" s="27" t="n"/>
       <c r="J66" s="57" t="n"/>
     </row>
-    <row r="67" ht="26" customHeight="1" s="6">
+    <row r="67" ht="20" customHeight="1" s="6">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will she play tennis next week?</t>
+          <t>正解（言いかえ）：She is going to play tennis next week.</t>
         </is>
       </c>
       <c r="B67" s="27" t="n"/>
@@ -4948,10 +5254,10 @@
       <c r="I67" s="27" t="n"/>
       <c r="J67" s="57" t="n"/>
     </row>
-    <row r="68" ht="26" customHeight="1" s="6">
+    <row r="68" ht="17" customHeight="1" s="6">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ疑問文）：Is she going to play tennis next week?</t>
+          <t>彼女は来週テニスをしません。</t>
         </is>
       </c>
       <c r="B68" s="27" t="n"/>
@@ -4967,7 +5273,7 @@
     <row r="69" ht="20" customHeight="1" s="6">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>正解（基本形）：She will not play tennis next week.</t>
         </is>
       </c>
       <c r="B69" s="27" t="n"/>
@@ -4980,10 +5286,10 @@
       <c r="I69" s="27" t="n"/>
       <c r="J69" s="57" t="n"/>
     </row>
-    <row r="70" ht="26" customHeight="1" s="6">
+    <row r="70" ht="20" customHeight="1" s="6">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>正解（返答）：Yes, she will.</t>
+          <t>正解（短縮形）：She won't play tennis next week.</t>
         </is>
       </c>
       <c r="B70" s="27" t="n"/>
@@ -4999,7 +5305,7 @@
     <row r="71" ht="20" customHeight="1" s="6">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>正解（言いかえ）：She is not going to play tennis next week.</t>
         </is>
       </c>
       <c r="B71" s="27" t="n"/>
@@ -5012,10 +5318,10 @@
       <c r="I71" s="27" t="n"/>
       <c r="J71" s="57" t="n"/>
     </row>
-    <row r="72" ht="26" customHeight="1" s="6">
+    <row r="72" ht="17" customHeight="1" s="6">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, she will not.</t>
+          <t>彼女は来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B72" s="27" t="n"/>
@@ -5028,10 +5334,10 @@
       <c r="I72" s="27" t="n"/>
       <c r="J72" s="57" t="n"/>
     </row>
-    <row r="73" ht="26" customHeight="1" s="6">
+    <row r="73" ht="20" customHeight="1" s="6">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, she won't.</t>
+          <t>正解（will疑問文）：Will she play tennis next week?</t>
         </is>
       </c>
       <c r="B73" s="27" t="n"/>
@@ -5044,8 +5350,12 @@
       <c r="I73" s="27" t="n"/>
       <c r="J73" s="57" t="n"/>
     </row>
-    <row r="74" ht="6" customHeight="1" s="6">
-      <c r="A74" s="8" t="n"/>
+    <row r="74" ht="20" customHeight="1" s="6">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ疑問文）：Is she going to play tennis next week?</t>
+        </is>
+      </c>
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="27" t="n"/>
       <c r="D74" s="27" t="n"/>
@@ -5056,28 +5366,26 @@
       <c r="I74" s="27" t="n"/>
       <c r="J74" s="57" t="n"/>
     </row>
-    <row r="75" ht="18" customHeight="1" s="6">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>5．主語は「私たち」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B75" s="25" t="n"/>
-      <c r="C75" s="25" t="n"/>
-      <c r="D75" s="25" t="n"/>
-      <c r="E75" s="25" t="n"/>
-      <c r="F75" s="25" t="n"/>
-      <c r="G75" s="25" t="n"/>
-      <c r="H75" s="25" t="n"/>
-      <c r="I75" s="25" t="n"/>
-      <c r="J75" s="56" t="n"/>
-    </row>
-    <row r="76" ht="48" customHeight="1" s="6">
-      <c r="A76" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。
-※相手が答える形なので、返答では I / we ではなく you を使います。</t>
+    <row r="75" ht="17" customHeight="1" s="6">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>はい、します。</t>
+        </is>
+      </c>
+      <c r="B75" s="27" t="n"/>
+      <c r="C75" s="27" t="n"/>
+      <c r="D75" s="27" t="n"/>
+      <c r="E75" s="27" t="n"/>
+      <c r="F75" s="27" t="n"/>
+      <c r="G75" s="27" t="n"/>
+      <c r="H75" s="27" t="n"/>
+      <c r="I75" s="27" t="n"/>
+      <c r="J75" s="57" t="n"/>
+    </row>
+    <row r="76" ht="20" customHeight="1" s="6">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>正解（will返答）：Yes, she will.</t>
         </is>
       </c>
       <c r="B76" s="27" t="n"/>
@@ -5093,7 +5401,7 @@
     <row r="77" ht="20" customHeight="1" s="6">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>私たちは来週テニスをします。</t>
+          <t>正解（言いかえ返答）：Yes, she is.</t>
         </is>
       </c>
       <c r="B77" s="27" t="n"/>
@@ -5106,10 +5414,10 @@
       <c r="I77" s="27" t="n"/>
       <c r="J77" s="57" t="n"/>
     </row>
-    <row r="78" ht="26" customHeight="1" s="6">
+    <row r="78" ht="17" customHeight="1" s="6">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>正解（will）：We will play tennis next week.</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B78" s="27" t="n"/>
@@ -5122,10 +5430,10 @@
       <c r="I78" s="27" t="n"/>
       <c r="J78" s="57" t="n"/>
     </row>
-    <row r="79" ht="26" customHeight="1" s="6">
+    <row r="79" ht="20" customHeight="1" s="6">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：We are going to play tennis next week.</t>
+          <t>正解（基本形）：No, she will not.</t>
         </is>
       </c>
       <c r="B79" s="27" t="n"/>
@@ -5141,7 +5449,7 @@
     <row r="80" ht="20" customHeight="1" s="6">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>私たちは来週テニスをしません。</t>
+          <t>正解（短縮形）：No, she won't.</t>
         </is>
       </c>
       <c r="B80" s="27" t="n"/>
@@ -5154,10 +5462,10 @@
       <c r="I80" s="27" t="n"/>
       <c r="J80" s="57" t="n"/>
     </row>
-    <row r="81" ht="26" customHeight="1" s="6">
+    <row r="81" ht="20" customHeight="1" s="6">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：We will not play tennis next week.</t>
+          <t>正解（言いかえ返答）：No, she is not.</t>
         </is>
       </c>
       <c r="B81" s="27" t="n"/>
@@ -5170,12 +5478,8 @@
       <c r="I81" s="27" t="n"/>
       <c r="J81" s="57" t="n"/>
     </row>
-    <row r="82" ht="26" customHeight="1" s="6">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t>正解（短縮形）：We won't play tennis next week.</t>
-        </is>
-      </c>
+    <row r="82" ht="4" customHeight="1" s="6">
+      <c r="A82" s="8" t="n"/>
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="27" t="n"/>
       <c r="D82" s="27" t="n"/>
@@ -5186,26 +5490,28 @@
       <c r="I82" s="27" t="n"/>
       <c r="J82" s="57" t="n"/>
     </row>
-    <row r="83" ht="26" customHeight="1" s="6">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t>正解（言いかえ）：We are not going to play tennis next week.</t>
-        </is>
-      </c>
-      <c r="B83" s="27" t="n"/>
-      <c r="C83" s="27" t="n"/>
-      <c r="D83" s="27" t="n"/>
-      <c r="E83" s="27" t="n"/>
-      <c r="F83" s="27" t="n"/>
-      <c r="G83" s="27" t="n"/>
-      <c r="H83" s="27" t="n"/>
-      <c r="I83" s="27" t="n"/>
-      <c r="J83" s="57" t="n"/>
-    </row>
-    <row r="84" ht="20" customHeight="1" s="6">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t>私たちは来週テニスをしますか。</t>
+    <row r="83" ht="16" customHeight="1" s="6">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>5．主語は「私たち」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B83" s="25" t="n"/>
+      <c r="C83" s="25" t="n"/>
+      <c r="D83" s="25" t="n"/>
+      <c r="E83" s="25" t="n"/>
+      <c r="F83" s="25" t="n"/>
+      <c r="G83" s="25" t="n"/>
+      <c r="H83" s="25" t="n"/>
+      <c r="I83" s="25" t="n"/>
+      <c r="J83" s="56" t="n"/>
+    </row>
+    <row r="84" ht="40" customHeight="1" s="6">
+      <c r="A84" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。
+※相手が答える形なので、返答では I / we ではなく you を使います。</t>
         </is>
       </c>
       <c r="B84" s="27" t="n"/>
@@ -5218,10 +5524,10 @@
       <c r="I84" s="27" t="n"/>
       <c r="J84" s="57" t="n"/>
     </row>
-    <row r="85" ht="26" customHeight="1" s="6">
+    <row r="85" ht="17" customHeight="1" s="6">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will we play tennis next week?</t>
+          <t>私たちは来週テニスをします。</t>
         </is>
       </c>
       <c r="B85" s="27" t="n"/>
@@ -5234,10 +5540,10 @@
       <c r="I85" s="27" t="n"/>
       <c r="J85" s="57" t="n"/>
     </row>
-    <row r="86" ht="26" customHeight="1" s="6">
+    <row r="86" ht="20" customHeight="1" s="6">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ疑問文）：Are we going to play tennis next week?</t>
+          <t>正解（will）：We will play tennis next week.</t>
         </is>
       </c>
       <c r="B86" s="27" t="n"/>
@@ -5253,7 +5559,7 @@
     <row r="87" ht="20" customHeight="1" s="6">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>正解（言いかえ）：We are going to play tennis next week.</t>
         </is>
       </c>
       <c r="B87" s="27" t="n"/>
@@ -5266,10 +5572,10 @@
       <c r="I87" s="27" t="n"/>
       <c r="J87" s="57" t="n"/>
     </row>
-    <row r="88" ht="26" customHeight="1" s="6">
+    <row r="88" ht="17" customHeight="1" s="6">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>正解（返答）：Yes, you will.</t>
+          <t>私たちは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B88" s="27" t="n"/>
@@ -5285,7 +5591,7 @@
     <row r="89" ht="20" customHeight="1" s="6">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>正解（基本形）：We will not play tennis next week.</t>
         </is>
       </c>
       <c r="B89" s="27" t="n"/>
@@ -5298,10 +5604,10 @@
       <c r="I89" s="27" t="n"/>
       <c r="J89" s="57" t="n"/>
     </row>
-    <row r="90" ht="26" customHeight="1" s="6">
+    <row r="90" ht="20" customHeight="1" s="6">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, you will not.</t>
+          <t>正解（短縮形）：We won't play tennis next week.</t>
         </is>
       </c>
       <c r="B90" s="27" t="n"/>
@@ -5314,10 +5620,10 @@
       <c r="I90" s="27" t="n"/>
       <c r="J90" s="57" t="n"/>
     </row>
-    <row r="91" ht="26" customHeight="1" s="6">
+    <row r="91" ht="20" customHeight="1" s="6">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, you won't.</t>
+          <t>正解（言いかえ）：We are not going to play tennis next week.</t>
         </is>
       </c>
       <c r="B91" s="27" t="n"/>
@@ -5330,8 +5636,12 @@
       <c r="I91" s="27" t="n"/>
       <c r="J91" s="57" t="n"/>
     </row>
-    <row r="92" ht="6" customHeight="1" s="6">
-      <c r="A92" s="8" t="n"/>
+    <row r="92" ht="17" customHeight="1" s="6">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>私たちは来週テニスをしますか。</t>
+        </is>
+      </c>
       <c r="B92" s="27" t="n"/>
       <c r="C92" s="27" t="n"/>
       <c r="D92" s="27" t="n"/>
@@ -5342,27 +5652,26 @@
       <c r="I92" s="27" t="n"/>
       <c r="J92" s="57" t="n"/>
     </row>
-    <row r="93" ht="18" customHeight="1" s="6">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>6．主語は「あなたたち」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B93" s="25" t="n"/>
-      <c r="C93" s="25" t="n"/>
-      <c r="D93" s="25" t="n"/>
-      <c r="E93" s="25" t="n"/>
-      <c r="F93" s="25" t="n"/>
-      <c r="G93" s="25" t="n"/>
-      <c r="H93" s="25" t="n"/>
-      <c r="I93" s="25" t="n"/>
-      <c r="J93" s="56" t="n"/>
-    </row>
-    <row r="94" ht="40" customHeight="1" s="6">
-      <c r="A94" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="93" ht="20" customHeight="1" s="6">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>正解（will疑問文）：Will we play tennis next week?</t>
+        </is>
+      </c>
+      <c r="B93" s="27" t="n"/>
+      <c r="C93" s="27" t="n"/>
+      <c r="D93" s="27" t="n"/>
+      <c r="E93" s="27" t="n"/>
+      <c r="F93" s="27" t="n"/>
+      <c r="G93" s="27" t="n"/>
+      <c r="H93" s="27" t="n"/>
+      <c r="I93" s="27" t="n"/>
+      <c r="J93" s="57" t="n"/>
+    </row>
+    <row r="94" ht="20" customHeight="1" s="6">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ疑問文）：Are we going to play tennis next week?</t>
         </is>
       </c>
       <c r="B94" s="27" t="n"/>
@@ -5375,10 +5684,10 @@
       <c r="I94" s="27" t="n"/>
       <c r="J94" s="57" t="n"/>
     </row>
-    <row r="95" ht="20" customHeight="1" s="6">
+    <row r="95" ht="17" customHeight="1" s="6">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>あなたたちは来週テニスをします。</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B95" s="27" t="n"/>
@@ -5391,10 +5700,10 @@
       <c r="I95" s="27" t="n"/>
       <c r="J95" s="57" t="n"/>
     </row>
-    <row r="96" ht="26" customHeight="1" s="6">
+    <row r="96" ht="20" customHeight="1" s="6">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>正解（will）：You will play tennis next week.</t>
+          <t>正解（will返答）：Yes, you will.</t>
         </is>
       </c>
       <c r="B96" s="27" t="n"/>
@@ -5407,10 +5716,10 @@
       <c r="I96" s="27" t="n"/>
       <c r="J96" s="57" t="n"/>
     </row>
-    <row r="97" ht="26" customHeight="1" s="6">
+    <row r="97" ht="20" customHeight="1" s="6">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：You are going to play tennis next week.</t>
+          <t>正解（言いかえ返答）：Yes, you are.</t>
         </is>
       </c>
       <c r="B97" s="27" t="n"/>
@@ -5423,10 +5732,10 @@
       <c r="I97" s="27" t="n"/>
       <c r="J97" s="57" t="n"/>
     </row>
-    <row r="98" ht="20" customHeight="1" s="6">
+    <row r="98" ht="17" customHeight="1" s="6">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>あなたたちは来週テニスをしません。</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B98" s="27" t="n"/>
@@ -5439,10 +5748,10 @@
       <c r="I98" s="27" t="n"/>
       <c r="J98" s="57" t="n"/>
     </row>
-    <row r="99" ht="26" customHeight="1" s="6">
+    <row r="99" ht="20" customHeight="1" s="6">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：You will not play tennis next week.</t>
+          <t>正解（基本形）：No, you will not.</t>
         </is>
       </c>
       <c r="B99" s="27" t="n"/>
@@ -5455,10 +5764,10 @@
       <c r="I99" s="27" t="n"/>
       <c r="J99" s="57" t="n"/>
     </row>
-    <row r="100" ht="26" customHeight="1" s="6">
+    <row r="100" ht="20" customHeight="1" s="6">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：You won't play tennis next week.</t>
+          <t>正解（短縮形）：No, you won't.</t>
         </is>
       </c>
       <c r="B100" s="27" t="n"/>
@@ -5471,10 +5780,10 @@
       <c r="I100" s="27" t="n"/>
       <c r="J100" s="57" t="n"/>
     </row>
-    <row r="101" ht="26" customHeight="1" s="6">
+    <row r="101" ht="20" customHeight="1" s="6">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：You are not going to play tennis next week.</t>
+          <t>正解（言いかえ返答）：No, you are not.</t>
         </is>
       </c>
       <c r="B101" s="27" t="n"/>
@@ -5487,12 +5796,8 @@
       <c r="I101" s="27" t="n"/>
       <c r="J101" s="57" t="n"/>
     </row>
-    <row r="102" ht="20" customHeight="1" s="6">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t>あなたたちは来週テニスをしますか。</t>
-        </is>
-      </c>
+    <row r="102" ht="4" customHeight="1" s="6">
+      <c r="A102" s="8" t="n"/>
       <c r="B102" s="27" t="n"/>
       <c r="C102" s="27" t="n"/>
       <c r="D102" s="27" t="n"/>
@@ -5503,26 +5808,27 @@
       <c r="I102" s="27" t="n"/>
       <c r="J102" s="57" t="n"/>
     </row>
-    <row r="103" ht="26" customHeight="1" s="6">
-      <c r="A103" s="11" t="inlineStr">
-        <is>
-          <t>正解（will疑問文）：Will you play tennis next week?</t>
-        </is>
-      </c>
-      <c r="B103" s="27" t="n"/>
-      <c r="C103" s="27" t="n"/>
-      <c r="D103" s="27" t="n"/>
-      <c r="E103" s="27" t="n"/>
-      <c r="F103" s="27" t="n"/>
-      <c r="G103" s="27" t="n"/>
-      <c r="H103" s="27" t="n"/>
-      <c r="I103" s="27" t="n"/>
-      <c r="J103" s="57" t="n"/>
-    </row>
-    <row r="104" ht="26" customHeight="1" s="6">
-      <c r="A104" s="11" t="inlineStr">
-        <is>
-          <t>正解（言いかえ疑問文）：Are you going to play tennis next week?</t>
+    <row r="103" ht="16" customHeight="1" s="6">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>6．主語は「あなたたち」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B103" s="25" t="n"/>
+      <c r="C103" s="25" t="n"/>
+      <c r="D103" s="25" t="n"/>
+      <c r="E103" s="25" t="n"/>
+      <c r="F103" s="25" t="n"/>
+      <c r="G103" s="25" t="n"/>
+      <c r="H103" s="25" t="n"/>
+      <c r="I103" s="25" t="n"/>
+      <c r="J103" s="56" t="n"/>
+    </row>
+    <row r="104" ht="34" customHeight="1" s="6">
+      <c r="A104" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B104" s="27" t="n"/>
@@ -5535,10 +5841,10 @@
       <c r="I104" s="27" t="n"/>
       <c r="J104" s="57" t="n"/>
     </row>
-    <row r="105" ht="20" customHeight="1" s="6">
+    <row r="105" ht="17" customHeight="1" s="6">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>あなたたちは来週テニスをします。</t>
         </is>
       </c>
       <c r="B105" s="27" t="n"/>
@@ -5551,10 +5857,10 @@
       <c r="I105" s="27" t="n"/>
       <c r="J105" s="57" t="n"/>
     </row>
-    <row r="106" ht="26" customHeight="1" s="6">
+    <row r="106" ht="20" customHeight="1" s="6">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>正解（返答）：Yes, we will.</t>
+          <t>正解（will）：You will play tennis next week.</t>
         </is>
       </c>
       <c r="B106" s="27" t="n"/>
@@ -5570,7 +5876,7 @@
     <row r="107" ht="20" customHeight="1" s="6">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>正解（言いかえ）：You are going to play tennis next week.</t>
         </is>
       </c>
       <c r="B107" s="27" t="n"/>
@@ -5583,10 +5889,10 @@
       <c r="I107" s="27" t="n"/>
       <c r="J107" s="57" t="n"/>
     </row>
-    <row r="108" ht="26" customHeight="1" s="6">
+    <row r="108" ht="17" customHeight="1" s="6">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, we will not.</t>
+          <t>あなたたちは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B108" s="27" t="n"/>
@@ -5599,10 +5905,10 @@
       <c r="I108" s="27" t="n"/>
       <c r="J108" s="57" t="n"/>
     </row>
-    <row r="109" ht="26" customHeight="1" s="6">
+    <row r="109" ht="20" customHeight="1" s="6">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, we won't.</t>
+          <t>正解（基本形）：You will not play tennis next week.</t>
         </is>
       </c>
       <c r="B109" s="27" t="n"/>
@@ -5615,8 +5921,12 @@
       <c r="I109" s="27" t="n"/>
       <c r="J109" s="57" t="n"/>
     </row>
-    <row r="110" ht="6" customHeight="1" s="6">
-      <c r="A110" s="8" t="n"/>
+    <row r="110" ht="20" customHeight="1" s="6">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：You won't play tennis next week.</t>
+        </is>
+      </c>
       <c r="B110" s="27" t="n"/>
       <c r="C110" s="27" t="n"/>
       <c r="D110" s="27" t="n"/>
@@ -5627,27 +5937,26 @@
       <c r="I110" s="27" t="n"/>
       <c r="J110" s="57" t="n"/>
     </row>
-    <row r="111" ht="18" customHeight="1" s="6">
-      <c r="A111" s="9" t="inlineStr">
-        <is>
-          <t>7．主語は「彼ら」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B111" s="25" t="n"/>
-      <c r="C111" s="25" t="n"/>
-      <c r="D111" s="25" t="n"/>
-      <c r="E111" s="25" t="n"/>
-      <c r="F111" s="25" t="n"/>
-      <c r="G111" s="25" t="n"/>
-      <c r="H111" s="25" t="n"/>
-      <c r="I111" s="25" t="n"/>
-      <c r="J111" s="56" t="n"/>
-    </row>
-    <row r="112" ht="40" customHeight="1" s="6">
-      <c r="A112" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="111" ht="20" customHeight="1" s="6">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：You are not going to play tennis next week.</t>
+        </is>
+      </c>
+      <c r="B111" s="27" t="n"/>
+      <c r="C111" s="27" t="n"/>
+      <c r="D111" s="27" t="n"/>
+      <c r="E111" s="27" t="n"/>
+      <c r="F111" s="27" t="n"/>
+      <c r="G111" s="27" t="n"/>
+      <c r="H111" s="27" t="n"/>
+      <c r="I111" s="27" t="n"/>
+      <c r="J111" s="57" t="n"/>
+    </row>
+    <row r="112" ht="17" customHeight="1" s="6">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>あなたたちは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B112" s="27" t="n"/>
@@ -5663,7 +5972,7 @@
     <row r="113" ht="20" customHeight="1" s="6">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>彼らは来週テニスをします。</t>
+          <t>正解（will疑問文）：Will you play tennis next week?</t>
         </is>
       </c>
       <c r="B113" s="27" t="n"/>
@@ -5676,10 +5985,10 @@
       <c r="I113" s="27" t="n"/>
       <c r="J113" s="57" t="n"/>
     </row>
-    <row r="114" ht="26" customHeight="1" s="6">
+    <row r="114" ht="20" customHeight="1" s="6">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>正解（will）：They will play tennis next week.</t>
+          <t>正解（言いかえ疑問文）：Are you going to play tennis next week?</t>
         </is>
       </c>
       <c r="B114" s="27" t="n"/>
@@ -5692,10 +6001,10 @@
       <c r="I114" s="27" t="n"/>
       <c r="J114" s="57" t="n"/>
     </row>
-    <row r="115" ht="26" customHeight="1" s="6">
+    <row r="115" ht="17" customHeight="1" s="6">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：They are going to play tennis next week.</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B115" s="27" t="n"/>
@@ -5711,7 +6020,7 @@
     <row r="116" ht="20" customHeight="1" s="6">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>彼らは来週テニスをしません。</t>
+          <t>正解（will返答）：Yes, we will.</t>
         </is>
       </c>
       <c r="B116" s="27" t="n"/>
@@ -5724,10 +6033,10 @@
       <c r="I116" s="27" t="n"/>
       <c r="J116" s="57" t="n"/>
     </row>
-    <row r="117" ht="26" customHeight="1" s="6">
+    <row r="117" ht="20" customHeight="1" s="6">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：They will not play tennis next week.</t>
+          <t>正解（言いかえ返答）：Yes, we are.</t>
         </is>
       </c>
       <c r="B117" s="27" t="n"/>
@@ -5740,10 +6049,10 @@
       <c r="I117" s="27" t="n"/>
       <c r="J117" s="57" t="n"/>
     </row>
-    <row r="118" ht="26" customHeight="1" s="6">
+    <row r="118" ht="17" customHeight="1" s="6">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：They won't play tennis next week.</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B118" s="27" t="n"/>
@@ -5756,10 +6065,10 @@
       <c r="I118" s="27" t="n"/>
       <c r="J118" s="57" t="n"/>
     </row>
-    <row r="119" ht="26" customHeight="1" s="6">
+    <row r="119" ht="20" customHeight="1" s="6">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：They are not going to play tennis next week.</t>
+          <t>正解（基本形）：No, we will not.</t>
         </is>
       </c>
       <c r="B119" s="27" t="n"/>
@@ -5775,7 +6084,7 @@
     <row r="120" ht="20" customHeight="1" s="6">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>彼らは来週テニスをしますか。</t>
+          <t>正解（短縮形）：No, we won't.</t>
         </is>
       </c>
       <c r="B120" s="27" t="n"/>
@@ -5788,10 +6097,10 @@
       <c r="I120" s="27" t="n"/>
       <c r="J120" s="57" t="n"/>
     </row>
-    <row r="121" ht="26" customHeight="1" s="6">
+    <row r="121" ht="20" customHeight="1" s="6">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will they play tennis next week?</t>
+          <t>正解（言いかえ返答）：No, we are not.</t>
         </is>
       </c>
       <c r="B121" s="27" t="n"/>
@@ -5804,12 +6113,8 @@
       <c r="I121" s="27" t="n"/>
       <c r="J121" s="57" t="n"/>
     </row>
-    <row r="122" ht="26" customHeight="1" s="6">
-      <c r="A122" s="11" t="inlineStr">
-        <is>
-          <t>正解（言いかえ疑問文）：Are they going to play tennis next week?</t>
-        </is>
-      </c>
+    <row r="122" ht="4" customHeight="1" s="6">
+      <c r="A122" s="8" t="n"/>
       <c r="B122" s="27" t="n"/>
       <c r="C122" s="27" t="n"/>
       <c r="D122" s="27" t="n"/>
@@ -5820,26 +6125,27 @@
       <c r="I122" s="27" t="n"/>
       <c r="J122" s="57" t="n"/>
     </row>
-    <row r="123" ht="20" customHeight="1" s="6">
-      <c r="A123" s="11" t="inlineStr">
-        <is>
-          <t>はい、します。</t>
-        </is>
-      </c>
-      <c r="B123" s="27" t="n"/>
-      <c r="C123" s="27" t="n"/>
-      <c r="D123" s="27" t="n"/>
-      <c r="E123" s="27" t="n"/>
-      <c r="F123" s="27" t="n"/>
-      <c r="G123" s="27" t="n"/>
-      <c r="H123" s="27" t="n"/>
-      <c r="I123" s="27" t="n"/>
-      <c r="J123" s="57" t="n"/>
-    </row>
-    <row r="124" ht="26" customHeight="1" s="6">
-      <c r="A124" s="11" t="inlineStr">
-        <is>
-          <t>正解（返答）：Yes, they will.</t>
+    <row r="123" ht="16" customHeight="1" s="6">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>7．主語は「彼ら」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B123" s="25" t="n"/>
+      <c r="C123" s="25" t="n"/>
+      <c r="D123" s="25" t="n"/>
+      <c r="E123" s="25" t="n"/>
+      <c r="F123" s="25" t="n"/>
+      <c r="G123" s="25" t="n"/>
+      <c r="H123" s="25" t="n"/>
+      <c r="I123" s="25" t="n"/>
+      <c r="J123" s="56" t="n"/>
+    </row>
+    <row r="124" ht="34" customHeight="1" s="6">
+      <c r="A124" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B124" s="27" t="n"/>
@@ -5852,10 +6158,10 @@
       <c r="I124" s="27" t="n"/>
       <c r="J124" s="57" t="n"/>
     </row>
-    <row r="125" ht="20" customHeight="1" s="6">
+    <row r="125" ht="17" customHeight="1" s="6">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>彼らは来週テニスをします。</t>
         </is>
       </c>
       <c r="B125" s="27" t="n"/>
@@ -5868,10 +6174,10 @@
       <c r="I125" s="27" t="n"/>
       <c r="J125" s="57" t="n"/>
     </row>
-    <row r="126" ht="26" customHeight="1" s="6">
+    <row r="126" ht="20" customHeight="1" s="6">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, they will not.</t>
+          <t>正解（will）：They will play tennis next week.</t>
         </is>
       </c>
       <c r="B126" s="27" t="n"/>
@@ -5884,10 +6190,10 @@
       <c r="I126" s="27" t="n"/>
       <c r="J126" s="57" t="n"/>
     </row>
-    <row r="127" ht="26" customHeight="1" s="6">
+    <row r="127" ht="20" customHeight="1" s="6">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, they won't.</t>
+          <t>正解（言いかえ）：They are going to play tennis next week.</t>
         </is>
       </c>
       <c r="B127" s="27" t="n"/>
@@ -5900,8 +6206,12 @@
       <c r="I127" s="27" t="n"/>
       <c r="J127" s="57" t="n"/>
     </row>
-    <row r="128" ht="6" customHeight="1" s="6">
-      <c r="A128" s="8" t="n"/>
+    <row r="128" ht="17" customHeight="1" s="6">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>彼らは来週テニスをしません。</t>
+        </is>
+      </c>
       <c r="B128" s="27" t="n"/>
       <c r="C128" s="27" t="n"/>
       <c r="D128" s="27" t="n"/>
@@ -5912,27 +6222,26 @@
       <c r="I128" s="27" t="n"/>
       <c r="J128" s="57" t="n"/>
     </row>
-    <row r="129" ht="18" customHeight="1" s="6">
-      <c r="A129" s="9" t="inlineStr">
-        <is>
-          <t>8．主語は「リョウタロウ」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B129" s="25" t="n"/>
-      <c r="C129" s="25" t="n"/>
-      <c r="D129" s="25" t="n"/>
-      <c r="E129" s="25" t="n"/>
-      <c r="F129" s="25" t="n"/>
-      <c r="G129" s="25" t="n"/>
-      <c r="H129" s="25" t="n"/>
-      <c r="I129" s="25" t="n"/>
-      <c r="J129" s="56" t="n"/>
-    </row>
-    <row r="130" ht="40" customHeight="1" s="6">
-      <c r="A130" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="129" ht="20" customHeight="1" s="6">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：They will not play tennis next week.</t>
+        </is>
+      </c>
+      <c r="B129" s="27" t="n"/>
+      <c r="C129" s="27" t="n"/>
+      <c r="D129" s="27" t="n"/>
+      <c r="E129" s="27" t="n"/>
+      <c r="F129" s="27" t="n"/>
+      <c r="G129" s="27" t="n"/>
+      <c r="H129" s="27" t="n"/>
+      <c r="I129" s="27" t="n"/>
+      <c r="J129" s="57" t="n"/>
+    </row>
+    <row r="130" ht="20" customHeight="1" s="6">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：They won't play tennis next week.</t>
         </is>
       </c>
       <c r="B130" s="27" t="n"/>
@@ -5948,7 +6257,7 @@
     <row r="131" ht="20" customHeight="1" s="6">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは来週テニスをします。</t>
+          <t>正解（言いかえ）：They are not going to play tennis next week.</t>
         </is>
       </c>
       <c r="B131" s="27" t="n"/>
@@ -5961,10 +6270,10 @@
       <c r="I131" s="27" t="n"/>
       <c r="J131" s="57" t="n"/>
     </row>
-    <row r="132" ht="26" customHeight="1" s="6">
+    <row r="132" ht="17" customHeight="1" s="6">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>正解（will）：Ryoutarou will play tennis next week.</t>
+          <t>彼らは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B132" s="27" t="n"/>
@@ -5977,10 +6286,10 @@
       <c r="I132" s="27" t="n"/>
       <c r="J132" s="57" t="n"/>
     </row>
-    <row r="133" ht="26" customHeight="1" s="6">
+    <row r="133" ht="20" customHeight="1" s="6">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：Ryoutarou is going to play tennis next week.</t>
+          <t>正解（will疑問文）：Will they play tennis next week?</t>
         </is>
       </c>
       <c r="B133" s="27" t="n"/>
@@ -5996,7 +6305,7 @@
     <row r="134" ht="20" customHeight="1" s="6">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは来週テニスをしません。</t>
+          <t>正解（言いかえ疑問文）：Are they going to play tennis next week?</t>
         </is>
       </c>
       <c r="B134" s="27" t="n"/>
@@ -6009,10 +6318,10 @@
       <c r="I134" s="27" t="n"/>
       <c r="J134" s="57" t="n"/>
     </row>
-    <row r="135" ht="26" customHeight="1" s="6">
+    <row r="135" ht="17" customHeight="1" s="6">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：Ryoutarou will not play tennis next week.</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B135" s="27" t="n"/>
@@ -6025,10 +6334,10 @@
       <c r="I135" s="27" t="n"/>
       <c r="J135" s="57" t="n"/>
     </row>
-    <row r="136" ht="26" customHeight="1" s="6">
+    <row r="136" ht="20" customHeight="1" s="6">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：Ryoutarou won't play tennis next week.</t>
+          <t>正解（will返答）：Yes, they will.</t>
         </is>
       </c>
       <c r="B136" s="27" t="n"/>
@@ -6041,10 +6350,10 @@
       <c r="I136" s="27" t="n"/>
       <c r="J136" s="57" t="n"/>
     </row>
-    <row r="137" ht="26" customHeight="1" s="6">
+    <row r="137" ht="20" customHeight="1" s="6">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：Ryoutarou is not going to play tennis next week.</t>
+          <t>正解（言いかえ返答）：Yes, they are.</t>
         </is>
       </c>
       <c r="B137" s="27" t="n"/>
@@ -6057,10 +6366,10 @@
       <c r="I137" s="27" t="n"/>
       <c r="J137" s="57" t="n"/>
     </row>
-    <row r="138" ht="20" customHeight="1" s="6">
+    <row r="138" ht="17" customHeight="1" s="6">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは来週テニスをしますか。</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B138" s="27" t="n"/>
@@ -6073,10 +6382,10 @@
       <c r="I138" s="27" t="n"/>
       <c r="J138" s="57" t="n"/>
     </row>
-    <row r="139" ht="26" customHeight="1" s="6">
+    <row r="139" ht="20" customHeight="1" s="6">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will Ryoutarou play tennis next week?</t>
+          <t>正解（基本形）：No, they will not.</t>
         </is>
       </c>
       <c r="B139" s="27" t="n"/>
@@ -6089,10 +6398,10 @@
       <c r="I139" s="27" t="n"/>
       <c r="J139" s="57" t="n"/>
     </row>
-    <row r="140" ht="26" customHeight="1" s="6">
+    <row r="140" ht="20" customHeight="1" s="6">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ疑問文）：Is Ryoutarou going to play tennis next week?</t>
+          <t>正解（短縮形）：No, they won't.</t>
         </is>
       </c>
       <c r="B140" s="27" t="n"/>
@@ -6108,7 +6417,7 @@
     <row r="141" ht="20" customHeight="1" s="6">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>正解（言いかえ返答）：No, they are not.</t>
         </is>
       </c>
       <c r="B141" s="27" t="n"/>
@@ -6121,12 +6430,8 @@
       <c r="I141" s="27" t="n"/>
       <c r="J141" s="57" t="n"/>
     </row>
-    <row r="142" ht="26" customHeight="1" s="6">
-      <c r="A142" s="11" t="inlineStr">
-        <is>
-          <t>正解（返答）：Yes, he will.</t>
-        </is>
-      </c>
+    <row r="142" ht="4" customHeight="1" s="6">
+      <c r="A142" s="8" t="n"/>
       <c r="B142" s="27" t="n"/>
       <c r="C142" s="27" t="n"/>
       <c r="D142" s="27" t="n"/>
@@ -6137,26 +6442,27 @@
       <c r="I142" s="27" t="n"/>
       <c r="J142" s="57" t="n"/>
     </row>
-    <row r="143" ht="20" customHeight="1" s="6">
-      <c r="A143" s="11" t="inlineStr">
-        <is>
-          <t>いいえ、しません。</t>
-        </is>
-      </c>
-      <c r="B143" s="27" t="n"/>
-      <c r="C143" s="27" t="n"/>
-      <c r="D143" s="27" t="n"/>
-      <c r="E143" s="27" t="n"/>
-      <c r="F143" s="27" t="n"/>
-      <c r="G143" s="27" t="n"/>
-      <c r="H143" s="27" t="n"/>
-      <c r="I143" s="27" t="n"/>
-      <c r="J143" s="57" t="n"/>
-    </row>
-    <row r="144" ht="26" customHeight="1" s="6">
-      <c r="A144" s="11" t="inlineStr">
-        <is>
-          <t>正解（基本形）：No, he will not.</t>
+    <row r="143" ht="16" customHeight="1" s="6">
+      <c r="A143" s="9" t="inlineStr">
+        <is>
+          <t>8．主語は「リョウタロウ」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B143" s="25" t="n"/>
+      <c r="C143" s="25" t="n"/>
+      <c r="D143" s="25" t="n"/>
+      <c r="E143" s="25" t="n"/>
+      <c r="F143" s="25" t="n"/>
+      <c r="G143" s="25" t="n"/>
+      <c r="H143" s="25" t="n"/>
+      <c r="I143" s="25" t="n"/>
+      <c r="J143" s="56" t="n"/>
+    </row>
+    <row r="144" ht="34" customHeight="1" s="6">
+      <c r="A144" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B144" s="27" t="n"/>
@@ -6169,10 +6475,10 @@
       <c r="I144" s="27" t="n"/>
       <c r="J144" s="57" t="n"/>
     </row>
-    <row r="145" ht="26" customHeight="1" s="6">
+    <row r="145" ht="17" customHeight="1" s="6">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, he won't.</t>
+          <t>リョウタロウは来週テニスをします。</t>
         </is>
       </c>
       <c r="B145" s="27" t="n"/>
@@ -6185,8 +6491,12 @@
       <c r="I145" s="27" t="n"/>
       <c r="J145" s="57" t="n"/>
     </row>
-    <row r="146" ht="6" customHeight="1" s="6">
-      <c r="A146" s="8" t="n"/>
+    <row r="146" ht="20" customHeight="1" s="6">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>正解（will）：Ryoutarou will play tennis next week.</t>
+        </is>
+      </c>
       <c r="B146" s="27" t="n"/>
       <c r="C146" s="27" t="n"/>
       <c r="D146" s="27" t="n"/>
@@ -6197,27 +6507,26 @@
       <c r="I146" s="27" t="n"/>
       <c r="J146" s="57" t="n"/>
     </row>
-    <row r="147" ht="18" customHeight="1" s="6">
-      <c r="A147" s="9" t="inlineStr">
-        <is>
-          <t>9．主語は「チサコ」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B147" s="25" t="n"/>
-      <c r="C147" s="25" t="n"/>
-      <c r="D147" s="25" t="n"/>
-      <c r="E147" s="25" t="n"/>
-      <c r="F147" s="25" t="n"/>
-      <c r="G147" s="25" t="n"/>
-      <c r="H147" s="25" t="n"/>
-      <c r="I147" s="25" t="n"/>
-      <c r="J147" s="56" t="n"/>
-    </row>
-    <row r="148" ht="40" customHeight="1" s="6">
-      <c r="A148" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="147" ht="20" customHeight="1" s="6">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：Ryoutarou is going to play tennis next week.</t>
+        </is>
+      </c>
+      <c r="B147" s="27" t="n"/>
+      <c r="C147" s="27" t="n"/>
+      <c r="D147" s="27" t="n"/>
+      <c r="E147" s="27" t="n"/>
+      <c r="F147" s="27" t="n"/>
+      <c r="G147" s="27" t="n"/>
+      <c r="H147" s="27" t="n"/>
+      <c r="I147" s="27" t="n"/>
+      <c r="J147" s="57" t="n"/>
+    </row>
+    <row r="148" ht="17" customHeight="1" s="6">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>リョウタロウは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B148" s="27" t="n"/>
@@ -6233,7 +6542,7 @@
     <row r="149" ht="20" customHeight="1" s="6">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>チサコは来週テニスをします。</t>
+          <t>正解（基本形）：Ryoutarou will not play tennis next week.</t>
         </is>
       </c>
       <c r="B149" s="27" t="n"/>
@@ -6246,10 +6555,10 @@
       <c r="I149" s="27" t="n"/>
       <c r="J149" s="57" t="n"/>
     </row>
-    <row r="150" ht="26" customHeight="1" s="6">
+    <row r="150" ht="20" customHeight="1" s="6">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>正解（will）：Chisako will play tennis next week.</t>
+          <t>正解（短縮形）：Ryoutarou won't play tennis next week.</t>
         </is>
       </c>
       <c r="B150" s="27" t="n"/>
@@ -6262,10 +6571,10 @@
       <c r="I150" s="27" t="n"/>
       <c r="J150" s="57" t="n"/>
     </row>
-    <row r="151" ht="26" customHeight="1" s="6">
+    <row r="151" ht="20" customHeight="1" s="6">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：Chisako is going to play tennis next week.</t>
+          <t>正解（言いかえ）：Ryoutarou is not going to play tennis next week.</t>
         </is>
       </c>
       <c r="B151" s="27" t="n"/>
@@ -6278,10 +6587,10 @@
       <c r="I151" s="27" t="n"/>
       <c r="J151" s="57" t="n"/>
     </row>
-    <row r="152" ht="20" customHeight="1" s="6">
+    <row r="152" ht="17" customHeight="1" s="6">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>チサコは来週テニスをしません。</t>
+          <t>リョウタロウは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B152" s="27" t="n"/>
@@ -6294,10 +6603,10 @@
       <c r="I152" s="27" t="n"/>
       <c r="J152" s="57" t="n"/>
     </row>
-    <row r="153" ht="26" customHeight="1" s="6">
+    <row r="153" ht="20" customHeight="1" s="6">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：Chisako will not play tennis next week.</t>
+          <t>正解（will疑問文）：Will Ryoutarou play tennis next week?</t>
         </is>
       </c>
       <c r="B153" s="27" t="n"/>
@@ -6310,10 +6619,10 @@
       <c r="I153" s="27" t="n"/>
       <c r="J153" s="57" t="n"/>
     </row>
-    <row r="154" ht="26" customHeight="1" s="6">
+    <row r="154" ht="20" customHeight="1" s="6">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：Chisako won't play tennis next week.</t>
+          <t>正解（言いかえ疑問文）：Is Ryoutarou going to play tennis next week?</t>
         </is>
       </c>
       <c r="B154" s="27" t="n"/>
@@ -6326,10 +6635,10 @@
       <c r="I154" s="27" t="n"/>
       <c r="J154" s="57" t="n"/>
     </row>
-    <row r="155" ht="26" customHeight="1" s="6">
+    <row r="155" ht="17" customHeight="1" s="6">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：Chisako is not going to play tennis next week.</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B155" s="27" t="n"/>
@@ -6345,7 +6654,7 @@
     <row r="156" ht="20" customHeight="1" s="6">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>チサコは来週テニスをしますか。</t>
+          <t>正解（will返答）：Yes, he will.</t>
         </is>
       </c>
       <c r="B156" s="27" t="n"/>
@@ -6358,10 +6667,10 @@
       <c r="I156" s="27" t="n"/>
       <c r="J156" s="57" t="n"/>
     </row>
-    <row r="157" ht="26" customHeight="1" s="6">
+    <row r="157" ht="20" customHeight="1" s="6">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will Chisako play tennis next week?</t>
+          <t>正解（言いかえ返答）：Yes, he is.</t>
         </is>
       </c>
       <c r="B157" s="27" t="n"/>
@@ -6374,10 +6683,10 @@
       <c r="I157" s="27" t="n"/>
       <c r="J157" s="57" t="n"/>
     </row>
-    <row r="158" ht="26" customHeight="1" s="6">
+    <row r="158" ht="17" customHeight="1" s="6">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ疑問文）：Is Chisako going to play tennis next week?</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B158" s="27" t="n"/>
@@ -6393,7 +6702,7 @@
     <row r="159" ht="20" customHeight="1" s="6">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>正解（基本形）：No, he will not.</t>
         </is>
       </c>
       <c r="B159" s="27" t="n"/>
@@ -6406,10 +6715,10 @@
       <c r="I159" s="27" t="n"/>
       <c r="J159" s="57" t="n"/>
     </row>
-    <row r="160" ht="26" customHeight="1" s="6">
+    <row r="160" ht="20" customHeight="1" s="6">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>正解（返答）：Yes, she will.</t>
+          <t>正解（短縮形）：No, he won't.</t>
         </is>
       </c>
       <c r="B160" s="27" t="n"/>
@@ -6425,7 +6734,7 @@
     <row r="161" ht="20" customHeight="1" s="6">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>正解（言いかえ返答）：No, he is not.</t>
         </is>
       </c>
       <c r="B161" s="27" t="n"/>
@@ -6438,12 +6747,8 @@
       <c r="I161" s="27" t="n"/>
       <c r="J161" s="57" t="n"/>
     </row>
-    <row r="162" ht="26" customHeight="1" s="6">
-      <c r="A162" s="11" t="inlineStr">
-        <is>
-          <t>正解（基本形）：No, she will not.</t>
-        </is>
-      </c>
+    <row r="162" ht="4" customHeight="1" s="6">
+      <c r="A162" s="8" t="n"/>
       <c r="B162" s="27" t="n"/>
       <c r="C162" s="27" t="n"/>
       <c r="D162" s="27" t="n"/>
@@ -6454,24 +6759,29 @@
       <c r="I162" s="27" t="n"/>
       <c r="J162" s="57" t="n"/>
     </row>
-    <row r="163" ht="26" customHeight="1" s="6">
-      <c r="A163" s="11" t="inlineStr">
-        <is>
-          <t>正解（短縮形）：No, she won't.</t>
-        </is>
-      </c>
-      <c r="B163" s="27" t="n"/>
-      <c r="C163" s="27" t="n"/>
-      <c r="D163" s="27" t="n"/>
-      <c r="E163" s="27" t="n"/>
-      <c r="F163" s="27" t="n"/>
-      <c r="G163" s="27" t="n"/>
-      <c r="H163" s="27" t="n"/>
-      <c r="I163" s="27" t="n"/>
-      <c r="J163" s="57" t="n"/>
-    </row>
-    <row r="164" ht="6" customHeight="1" s="6">
-      <c r="A164" s="8" t="n"/>
+    <row r="163" ht="16" customHeight="1" s="6">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>9．主語は「チサコ」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B163" s="25" t="n"/>
+      <c r="C163" s="25" t="n"/>
+      <c r="D163" s="25" t="n"/>
+      <c r="E163" s="25" t="n"/>
+      <c r="F163" s="25" t="n"/>
+      <c r="G163" s="25" t="n"/>
+      <c r="H163" s="25" t="n"/>
+      <c r="I163" s="25" t="n"/>
+      <c r="J163" s="56" t="n"/>
+    </row>
+    <row r="164" ht="34" customHeight="1" s="6">
+      <c r="A164" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
+        </is>
+      </c>
       <c r="B164" s="27" t="n"/>
       <c r="C164" s="27" t="n"/>
       <c r="D164" s="27" t="n"/>
@@ -6482,30 +6792,319 @@
       <c r="I164" s="27" t="n"/>
       <c r="J164" s="57" t="n"/>
     </row>
+    <row r="165" ht="17" customHeight="1" s="6">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t>チサコは来週テニスをします。</t>
+        </is>
+      </c>
+      <c r="B165" s="27" t="n"/>
+      <c r="C165" s="27" t="n"/>
+      <c r="D165" s="27" t="n"/>
+      <c r="E165" s="27" t="n"/>
+      <c r="F165" s="27" t="n"/>
+      <c r="G165" s="27" t="n"/>
+      <c r="H165" s="27" t="n"/>
+      <c r="I165" s="27" t="n"/>
+      <c r="J165" s="57" t="n"/>
+    </row>
+    <row r="166" ht="20" customHeight="1" s="6">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>正解（will）：Chisako will play tennis next week.</t>
+        </is>
+      </c>
+      <c r="B166" s="27" t="n"/>
+      <c r="C166" s="27" t="n"/>
+      <c r="D166" s="27" t="n"/>
+      <c r="E166" s="27" t="n"/>
+      <c r="F166" s="27" t="n"/>
+      <c r="G166" s="27" t="n"/>
+      <c r="H166" s="27" t="n"/>
+      <c r="I166" s="27" t="n"/>
+      <c r="J166" s="57" t="n"/>
+    </row>
+    <row r="167" ht="20" customHeight="1" s="6">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：Chisako is going to play tennis next week.</t>
+        </is>
+      </c>
+      <c r="B167" s="27" t="n"/>
+      <c r="C167" s="27" t="n"/>
+      <c r="D167" s="27" t="n"/>
+      <c r="E167" s="27" t="n"/>
+      <c r="F167" s="27" t="n"/>
+      <c r="G167" s="27" t="n"/>
+      <c r="H167" s="27" t="n"/>
+      <c r="I167" s="27" t="n"/>
+      <c r="J167" s="57" t="n"/>
+    </row>
+    <row r="168" ht="17" customHeight="1" s="6">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>チサコは来週テニスをしません。</t>
+        </is>
+      </c>
+      <c r="B168" s="27" t="n"/>
+      <c r="C168" s="27" t="n"/>
+      <c r="D168" s="27" t="n"/>
+      <c r="E168" s="27" t="n"/>
+      <c r="F168" s="27" t="n"/>
+      <c r="G168" s="27" t="n"/>
+      <c r="H168" s="27" t="n"/>
+      <c r="I168" s="27" t="n"/>
+      <c r="J168" s="57" t="n"/>
+    </row>
+    <row r="169" ht="20" customHeight="1" s="6">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：Chisako will not play tennis next week.</t>
+        </is>
+      </c>
+      <c r="B169" s="27" t="n"/>
+      <c r="C169" s="27" t="n"/>
+      <c r="D169" s="27" t="n"/>
+      <c r="E169" s="27" t="n"/>
+      <c r="F169" s="27" t="n"/>
+      <c r="G169" s="27" t="n"/>
+      <c r="H169" s="27" t="n"/>
+      <c r="I169" s="27" t="n"/>
+      <c r="J169" s="57" t="n"/>
+    </row>
+    <row r="170" ht="20" customHeight="1" s="6">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：Chisako won't play tennis next week.</t>
+        </is>
+      </c>
+      <c r="B170" s="27" t="n"/>
+      <c r="C170" s="27" t="n"/>
+      <c r="D170" s="27" t="n"/>
+      <c r="E170" s="27" t="n"/>
+      <c r="F170" s="27" t="n"/>
+      <c r="G170" s="27" t="n"/>
+      <c r="H170" s="27" t="n"/>
+      <c r="I170" s="27" t="n"/>
+      <c r="J170" s="57" t="n"/>
+    </row>
+    <row r="171" ht="20" customHeight="1" s="6">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ）：Chisako is not going to play tennis next week.</t>
+        </is>
+      </c>
+      <c r="B171" s="27" t="n"/>
+      <c r="C171" s="27" t="n"/>
+      <c r="D171" s="27" t="n"/>
+      <c r="E171" s="27" t="n"/>
+      <c r="F171" s="27" t="n"/>
+      <c r="G171" s="27" t="n"/>
+      <c r="H171" s="27" t="n"/>
+      <c r="I171" s="27" t="n"/>
+      <c r="J171" s="57" t="n"/>
+    </row>
+    <row r="172" ht="17" customHeight="1" s="6">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>チサコは来週テニスをしますか。</t>
+        </is>
+      </c>
+      <c r="B172" s="27" t="n"/>
+      <c r="C172" s="27" t="n"/>
+      <c r="D172" s="27" t="n"/>
+      <c r="E172" s="27" t="n"/>
+      <c r="F172" s="27" t="n"/>
+      <c r="G172" s="27" t="n"/>
+      <c r="H172" s="27" t="n"/>
+      <c r="I172" s="27" t="n"/>
+      <c r="J172" s="57" t="n"/>
+    </row>
+    <row r="173" ht="20" customHeight="1" s="6">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>正解（will疑問文）：Will Chisako play tennis next week?</t>
+        </is>
+      </c>
+      <c r="B173" s="27" t="n"/>
+      <c r="C173" s="27" t="n"/>
+      <c r="D173" s="27" t="n"/>
+      <c r="E173" s="27" t="n"/>
+      <c r="F173" s="27" t="n"/>
+      <c r="G173" s="27" t="n"/>
+      <c r="H173" s="27" t="n"/>
+      <c r="I173" s="27" t="n"/>
+      <c r="J173" s="57" t="n"/>
+    </row>
+    <row r="174" ht="20" customHeight="1" s="6">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ疑問文）：Is Chisako going to play tennis next week?</t>
+        </is>
+      </c>
+      <c r="B174" s="27" t="n"/>
+      <c r="C174" s="27" t="n"/>
+      <c r="D174" s="27" t="n"/>
+      <c r="E174" s="27" t="n"/>
+      <c r="F174" s="27" t="n"/>
+      <c r="G174" s="27" t="n"/>
+      <c r="H174" s="27" t="n"/>
+      <c r="I174" s="27" t="n"/>
+      <c r="J174" s="57" t="n"/>
+    </row>
+    <row r="175" ht="17" customHeight="1" s="6">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>はい、します。</t>
+        </is>
+      </c>
+      <c r="B175" s="27" t="n"/>
+      <c r="C175" s="27" t="n"/>
+      <c r="D175" s="27" t="n"/>
+      <c r="E175" s="27" t="n"/>
+      <c r="F175" s="27" t="n"/>
+      <c r="G175" s="27" t="n"/>
+      <c r="H175" s="27" t="n"/>
+      <c r="I175" s="27" t="n"/>
+      <c r="J175" s="57" t="n"/>
+    </row>
+    <row r="176" ht="20" customHeight="1" s="6">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t>正解（will返答）：Yes, she will.</t>
+        </is>
+      </c>
+      <c r="B176" s="27" t="n"/>
+      <c r="C176" s="27" t="n"/>
+      <c r="D176" s="27" t="n"/>
+      <c r="E176" s="27" t="n"/>
+      <c r="F176" s="27" t="n"/>
+      <c r="G176" s="27" t="n"/>
+      <c r="H176" s="27" t="n"/>
+      <c r="I176" s="27" t="n"/>
+      <c r="J176" s="57" t="n"/>
+    </row>
+    <row r="177" ht="20" customHeight="1" s="6">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ返答）：Yes, she is.</t>
+        </is>
+      </c>
+      <c r="B177" s="27" t="n"/>
+      <c r="C177" s="27" t="n"/>
+      <c r="D177" s="27" t="n"/>
+      <c r="E177" s="27" t="n"/>
+      <c r="F177" s="27" t="n"/>
+      <c r="G177" s="27" t="n"/>
+      <c r="H177" s="27" t="n"/>
+      <c r="I177" s="27" t="n"/>
+      <c r="J177" s="57" t="n"/>
+    </row>
+    <row r="178" ht="17" customHeight="1" s="6">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、しません。</t>
+        </is>
+      </c>
+      <c r="B178" s="27" t="n"/>
+      <c r="C178" s="27" t="n"/>
+      <c r="D178" s="27" t="n"/>
+      <c r="E178" s="27" t="n"/>
+      <c r="F178" s="27" t="n"/>
+      <c r="G178" s="27" t="n"/>
+      <c r="H178" s="27" t="n"/>
+      <c r="I178" s="27" t="n"/>
+      <c r="J178" s="57" t="n"/>
+    </row>
+    <row r="179" ht="20" customHeight="1" s="6">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：No, she will not.</t>
+        </is>
+      </c>
+      <c r="B179" s="27" t="n"/>
+      <c r="C179" s="27" t="n"/>
+      <c r="D179" s="27" t="n"/>
+      <c r="E179" s="27" t="n"/>
+      <c r="F179" s="27" t="n"/>
+      <c r="G179" s="27" t="n"/>
+      <c r="H179" s="27" t="n"/>
+      <c r="I179" s="27" t="n"/>
+      <c r="J179" s="57" t="n"/>
+    </row>
+    <row r="180" ht="20" customHeight="1" s="6">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：No, she won't.</t>
+        </is>
+      </c>
+      <c r="B180" s="27" t="n"/>
+      <c r="C180" s="27" t="n"/>
+      <c r="D180" s="27" t="n"/>
+      <c r="E180" s="27" t="n"/>
+      <c r="F180" s="27" t="n"/>
+      <c r="G180" s="27" t="n"/>
+      <c r="H180" s="27" t="n"/>
+      <c r="I180" s="27" t="n"/>
+      <c r="J180" s="57" t="n"/>
+    </row>
+    <row r="181" ht="20" customHeight="1" s="6">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ返答）：No, she is not.</t>
+        </is>
+      </c>
+      <c r="B181" s="27" t="n"/>
+      <c r="C181" s="27" t="n"/>
+      <c r="D181" s="27" t="n"/>
+      <c r="E181" s="27" t="n"/>
+      <c r="F181" s="27" t="n"/>
+      <c r="G181" s="27" t="n"/>
+      <c r="H181" s="27" t="n"/>
+      <c r="I181" s="27" t="n"/>
+      <c r="J181" s="57" t="n"/>
+    </row>
+    <row r="182" ht="4" customHeight="1" s="6">
+      <c r="A182" s="8" t="n"/>
+      <c r="B182" s="27" t="n"/>
+      <c r="C182" s="27" t="n"/>
+      <c r="D182" s="27" t="n"/>
+      <c r="E182" s="27" t="n"/>
+      <c r="F182" s="27" t="n"/>
+      <c r="G182" s="27" t="n"/>
+      <c r="H182" s="27" t="n"/>
+      <c r="I182" s="27" t="n"/>
+      <c r="J182" s="57" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="164">
+  <mergeCells count="182">
     <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A181:J181"/>
     <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A156:J156"/>
     <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A156:J156"/>
+    <mergeCell ref="A171:J171"/>
+    <mergeCell ref="A165:J165"/>
     <mergeCell ref="A52:J52"/>
     <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A155:J155"/>
     <mergeCell ref="A115:J115"/>
-    <mergeCell ref="A155:J155"/>
     <mergeCell ref="A93:J93"/>
+    <mergeCell ref="A173:J173"/>
     <mergeCell ref="A130:J130"/>
     <mergeCell ref="A77:J77"/>
+    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A148:J148"/>
     <mergeCell ref="A157:J157"/>
+    <mergeCell ref="A138:J138"/>
     <mergeCell ref="A49:J49"/>
-    <mergeCell ref="A138:J138"/>
     <mergeCell ref="A132:J132"/>
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="A119:J119"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A69:J69"/>
+    <mergeCell ref="A174:J174"/>
     <mergeCell ref="A66:J66"/>
     <mergeCell ref="A118:J118"/>
     <mergeCell ref="A75:J75"/>
@@ -6516,6 +7115,7 @@
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A95:J95"/>
     <mergeCell ref="A104:J104"/>
+    <mergeCell ref="A175:J175"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="A14:J14"/>
@@ -6525,12 +7125,13 @@
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A81:J81"/>
+    <mergeCell ref="A96:J96"/>
     <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A96:J96"/>
     <mergeCell ref="A147:J147"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A161:J161"/>
     <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A170:J170"/>
     <mergeCell ref="A44:J44"/>
     <mergeCell ref="A31:J31"/>
     <mergeCell ref="A58:J58"/>
@@ -6546,6 +7147,7 @@
     <mergeCell ref="A146:J146"/>
     <mergeCell ref="A124:J124"/>
     <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A172:J172"/>
     <mergeCell ref="A16:J16"/>
     <mergeCell ref="A25:J25"/>
     <mergeCell ref="A108:J108"/>
@@ -6558,14 +7160,14 @@
     <mergeCell ref="A86:J86"/>
     <mergeCell ref="A42:J42"/>
     <mergeCell ref="A151:J151"/>
+    <mergeCell ref="A160:J160"/>
     <mergeCell ref="A47:J47"/>
-    <mergeCell ref="A160:J160"/>
     <mergeCell ref="A141:J141"/>
     <mergeCell ref="A135:J135"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A150:J150"/>
+    <mergeCell ref="A144:J144"/>
     <mergeCell ref="A62:J62"/>
-    <mergeCell ref="A144:J144"/>
     <mergeCell ref="A122:J122"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A125:J125"/>
@@ -6575,29 +7177,35 @@
     <mergeCell ref="A112:J112"/>
     <mergeCell ref="A152:J152"/>
     <mergeCell ref="A127:J127"/>
+    <mergeCell ref="A167:J167"/>
+    <mergeCell ref="A176:J176"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A114:J114"/>
     <mergeCell ref="A59:J59"/>
+    <mergeCell ref="A182:J182"/>
     <mergeCell ref="A64:J64"/>
     <mergeCell ref="A98:J98"/>
+    <mergeCell ref="A169:J169"/>
     <mergeCell ref="A51:J51"/>
     <mergeCell ref="A107:J107"/>
+    <mergeCell ref="A178:J178"/>
     <mergeCell ref="A79:J79"/>
     <mergeCell ref="A61:J61"/>
     <mergeCell ref="A88:J88"/>
     <mergeCell ref="A70:J70"/>
+    <mergeCell ref="A162:J162"/>
     <mergeCell ref="A153:J153"/>
-    <mergeCell ref="A162:J162"/>
     <mergeCell ref="A54:J54"/>
     <mergeCell ref="A137:J137"/>
+    <mergeCell ref="A177:J177"/>
     <mergeCell ref="A90:J90"/>
     <mergeCell ref="A41:J41"/>
     <mergeCell ref="A99:J99"/>
     <mergeCell ref="A164:J164"/>
     <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A145:J145"/>
     <mergeCell ref="A56:J56"/>
     <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A145:J145"/>
     <mergeCell ref="A139:J139"/>
     <mergeCell ref="A154:J154"/>
     <mergeCell ref="A163:J163"/>
@@ -6615,6 +7223,7 @@
     <mergeCell ref="A53:J53"/>
     <mergeCell ref="A109:J109"/>
     <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A180:J180"/>
     <mergeCell ref="A129:J129"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A68:J68"/>
@@ -6626,6 +7235,7 @@
     <mergeCell ref="A143:J143"/>
     <mergeCell ref="A92:J92"/>
     <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A166:J166"/>
     <mergeCell ref="A48:J48"/>
     <mergeCell ref="A142:J142"/>
     <mergeCell ref="A11:J11"/>
@@ -6633,6 +7243,7 @@
     <mergeCell ref="A94:J94"/>
     <mergeCell ref="A45:J45"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A168:J168"/>
     <mergeCell ref="A78:J78"/>
     <mergeCell ref="A87:J87"/>
     <mergeCell ref="A65:J65"/>
@@ -6647,16 +7258,17 @@
     <mergeCell ref="A57:J57"/>
     <mergeCell ref="A26:J26"/>
     <mergeCell ref="A113:J113"/>
+    <mergeCell ref="A179:J179"/>
     <mergeCell ref="A71:J71"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1" verticalDpi="0"/>
   <rowBreaks count="4" manualBreakCount="4">
-    <brk id="38" min="0" max="16383" man="1"/>
-    <brk id="74" min="0" max="16383" man="1"/>
-    <brk id="110" min="0" max="16383" man="1"/>
-    <brk id="146" min="0" max="16383" man="1"/>
+    <brk id="42" min="0" max="16383" man="1"/>
+    <brk id="82" min="0" max="16383" man="1"/>
+    <brk id="122" min="0" max="16383" man="1"/>
+    <brk id="162" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Studymaterials/中学生英作文助動詞will編.xlsx
+++ b/Studymaterials/中学生英作文助動詞will編.xlsx
@@ -10,8 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="解答willと書き換え" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'問題willと書き換え'!$A$1:$J$182</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'解答willと書き換え'!$A$1:$J$182</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'問題willと書き換え'!$A$1:$J$191</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'解答willと書き換え'!$A$1:$J$191</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1077,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J182"/>
+  <dimension ref="A1:J191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="13" customWidth="1" style="6" min="1" max="1"/>
@@ -1108,7 +1108,7 @@
       <c r="I1" s="25" t="n"/>
       <c r="J1" s="56" t="n"/>
     </row>
-    <row r="2" ht="4" customHeight="1" s="6">
+    <row r="2" ht="6" customHeight="1" s="6">
       <c r="A2" s="8" t="n"/>
       <c r="B2" s="27" t="n"/>
       <c r="C2" s="27" t="n"/>
@@ -1120,7 +1120,7 @@
       <c r="I2" s="27" t="n"/>
       <c r="J2" s="57" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1" s="6">
+    <row r="3" ht="18" customHeight="1" s="6">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>1．主語は「私」で書いてください。</t>
@@ -1136,7 +1136,7 @@
       <c r="I3" s="25" t="n"/>
       <c r="J3" s="56" t="n"/>
     </row>
-    <row r="4" ht="40" customHeight="1" s="6">
+    <row r="4" ht="42" customHeight="1" s="6">
       <c r="A4" s="55" t="inlineStr">
         <is>
           <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
@@ -1154,7 +1154,7 @@
       <c r="I4" s="27" t="n"/>
       <c r="J4" s="57" t="n"/>
     </row>
-    <row r="5" ht="17" customHeight="1" s="6">
+    <row r="5" ht="18" customHeight="1" s="6">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>私は来週テニスをします。</t>
@@ -1202,7 +1202,7 @@
       <c r="I7" s="27" t="n"/>
       <c r="J7" s="57" t="n"/>
     </row>
-    <row r="8" ht="17" customHeight="1" s="6">
+    <row r="8" ht="18" customHeight="1" s="6">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>私は来週テニスをしません。</t>
@@ -1266,7 +1266,7 @@
       <c r="I11" s="27" t="n"/>
       <c r="J11" s="57" t="n"/>
     </row>
-    <row r="12" ht="17" customHeight="1" s="6">
+    <row r="12" ht="18" customHeight="1" s="6">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>私は来週テニスをしますか。</t>
@@ -1314,7 +1314,7 @@
       <c r="I14" s="27" t="n"/>
       <c r="J14" s="57" t="n"/>
     </row>
-    <row r="15" ht="17" customHeight="1" s="6">
+    <row r="15" ht="18" customHeight="1" s="6">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>はい、します。</t>
@@ -1362,7 +1362,7 @@
       <c r="I17" s="27" t="n"/>
       <c r="J17" s="57" t="n"/>
     </row>
-    <row r="18" ht="17" customHeight="1" s="6">
+    <row r="18" ht="18" customHeight="1" s="6">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>いいえ、しません。</t>
@@ -1413,7 +1413,7 @@
     <row r="21" ht="20" customHeight="1" s="6">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>回答（言いかえ基本形）：</t>
         </is>
       </c>
       <c r="B21" s="27" t="n"/>
@@ -1426,8 +1426,12 @@
       <c r="I21" s="27" t="n"/>
       <c r="J21" s="57" t="n"/>
     </row>
-    <row r="22" ht="4" customHeight="1" s="6">
-      <c r="A22" s="8" t="n"/>
+    <row r="22" ht="20" customHeight="1" s="6">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ短縮形）：</t>
+        </is>
+      </c>
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="27" t="n"/>
       <c r="D22" s="27" t="n"/>
@@ -1438,43 +1442,39 @@
       <c r="I22" s="27" t="n"/>
       <c r="J22" s="57" t="n"/>
     </row>
-    <row r="23" ht="16" customHeight="1" s="6">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="23" ht="6" customHeight="1" s="6">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="27" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="27" t="n"/>
+      <c r="G23" s="27" t="n"/>
+      <c r="H23" s="27" t="n"/>
+      <c r="I23" s="27" t="n"/>
+      <c r="J23" s="57" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="6">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>2．主語は「あなた」で書いてください。</t>
         </is>
       </c>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="25" t="n"/>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="25" t="n"/>
-      <c r="G23" s="25" t="n"/>
-      <c r="H23" s="25" t="n"/>
-      <c r="I23" s="25" t="n"/>
-      <c r="J23" s="56" t="n"/>
-    </row>
-    <row r="24" ht="34" customHeight="1" s="6">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
+      <c r="J24" s="56" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1" s="6">
+      <c r="A25" s="55" t="inlineStr">
         <is>
           <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
 ※否定の短縮形は will not → won't を使います。</t>
-        </is>
-      </c>
-      <c r="B24" s="27" t="n"/>
-      <c r="C24" s="27" t="n"/>
-      <c r="D24" s="27" t="n"/>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="27" t="n"/>
-      <c r="H24" s="27" t="n"/>
-      <c r="I24" s="27" t="n"/>
-      <c r="J24" s="57" t="n"/>
-    </row>
-    <row r="25" ht="17" customHeight="1" s="6">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>あなたは来週テニスをします。</t>
         </is>
       </c>
       <c r="B25" s="27" t="n"/>
@@ -1487,10 +1487,10 @@
       <c r="I25" s="27" t="n"/>
       <c r="J25" s="57" t="n"/>
     </row>
-    <row r="26" ht="20" customHeight="1" s="6">
+    <row r="26" ht="18" customHeight="1" s="6">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>回答（will）：</t>
+          <t>あなたは来週テニスをします。</t>
         </is>
       </c>
       <c r="B26" s="27" t="n"/>
@@ -1506,7 +1506,7 @@
     <row r="27" ht="20" customHeight="1" s="6">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（will）：</t>
         </is>
       </c>
       <c r="B27" s="27" t="n"/>
@@ -1519,10 +1519,10 @@
       <c r="I27" s="27" t="n"/>
       <c r="J27" s="57" t="n"/>
     </row>
-    <row r="28" ht="17" customHeight="1" s="6">
+    <row r="28" ht="20" customHeight="1" s="6">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>あなたは来週テニスをしません。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B28" s="27" t="n"/>
@@ -1535,10 +1535,10 @@
       <c r="I28" s="27" t="n"/>
       <c r="J28" s="57" t="n"/>
     </row>
-    <row r="29" ht="20" customHeight="1" s="6">
+    <row r="29" ht="18" customHeight="1" s="6">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>あなたは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B29" s="27" t="n"/>
@@ -1554,7 +1554,7 @@
     <row r="30" ht="20" customHeight="1" s="6">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B30" s="27" t="n"/>
@@ -1570,7 +1570,7 @@
     <row r="31" ht="20" customHeight="1" s="6">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B31" s="27" t="n"/>
@@ -1583,10 +1583,10 @@
       <c r="I31" s="27" t="n"/>
       <c r="J31" s="57" t="n"/>
     </row>
-    <row r="32" ht="17" customHeight="1" s="6">
+    <row r="32" ht="20" customHeight="1" s="6">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>あなたは来週テニスをしますか。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B32" s="27" t="n"/>
@@ -1599,10 +1599,10 @@
       <c r="I32" s="27" t="n"/>
       <c r="J32" s="57" t="n"/>
     </row>
-    <row r="33" ht="20" customHeight="1" s="6">
+    <row r="33" ht="18" customHeight="1" s="6">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>あなたは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B33" s="27" t="n"/>
@@ -1618,7 +1618,7 @@
     <row r="34" ht="20" customHeight="1" s="6">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ疑問文）：</t>
+          <t>回答（will疑問文）：</t>
         </is>
       </c>
       <c r="B34" s="27" t="n"/>
@@ -1631,10 +1631,10 @@
       <c r="I34" s="27" t="n"/>
       <c r="J34" s="57" t="n"/>
     </row>
-    <row r="35" ht="17" customHeight="1" s="6">
+    <row r="35" ht="20" customHeight="1" s="6">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>回答（言いかえ疑問文）：</t>
         </is>
       </c>
       <c r="B35" s="27" t="n"/>
@@ -1647,10 +1647,10 @@
       <c r="I35" s="27" t="n"/>
       <c r="J35" s="57" t="n"/>
     </row>
-    <row r="36" ht="20" customHeight="1" s="6">
+    <row r="36" ht="18" customHeight="1" s="6">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>回答（will返答）：</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B36" s="27" t="n"/>
@@ -1666,7 +1666,7 @@
     <row r="37" ht="20" customHeight="1" s="6">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>回答（will返答）：</t>
         </is>
       </c>
       <c r="B37" s="27" t="n"/>
@@ -1679,10 +1679,10 @@
       <c r="I37" s="27" t="n"/>
       <c r="J37" s="57" t="n"/>
     </row>
-    <row r="38" ht="17" customHeight="1" s="6">
+    <row r="38" ht="20" customHeight="1" s="6">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B38" s="27" t="n"/>
@@ -1695,10 +1695,10 @@
       <c r="I38" s="27" t="n"/>
       <c r="J38" s="57" t="n"/>
     </row>
-    <row r="39" ht="20" customHeight="1" s="6">
+    <row r="39" ht="18" customHeight="1" s="6">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B39" s="27" t="n"/>
@@ -1714,7 +1714,7 @@
     <row r="40" ht="20" customHeight="1" s="6">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B40" s="27" t="n"/>
@@ -1730,7 +1730,7 @@
     <row r="41" ht="20" customHeight="1" s="6">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B41" s="27" t="n"/>
@@ -1743,8 +1743,12 @@
       <c r="I41" s="27" t="n"/>
       <c r="J41" s="57" t="n"/>
     </row>
-    <row r="42" ht="4" customHeight="1" s="6">
-      <c r="A42" s="8" t="n"/>
+    <row r="42" ht="20" customHeight="1" s="6">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ基本形）：</t>
+        </is>
+      </c>
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="27" t="n"/>
       <c r="D42" s="27" t="n"/>
@@ -1755,29 +1759,24 @@
       <c r="I42" s="27" t="n"/>
       <c r="J42" s="57" t="n"/>
     </row>
-    <row r="43" ht="16" customHeight="1" s="6">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>3．主語は「彼」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="n"/>
-      <c r="C43" s="25" t="n"/>
-      <c r="D43" s="25" t="n"/>
-      <c r="E43" s="25" t="n"/>
-      <c r="F43" s="25" t="n"/>
-      <c r="G43" s="25" t="n"/>
-      <c r="H43" s="25" t="n"/>
-      <c r="I43" s="25" t="n"/>
-      <c r="J43" s="56" t="n"/>
-    </row>
-    <row r="44" ht="34" customHeight="1" s="6">
-      <c r="A44" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
-        </is>
-      </c>
+    <row r="43" ht="20" customHeight="1" s="6">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ短縮形）：</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="n"/>
+      <c r="C43" s="27" t="n"/>
+      <c r="D43" s="27" t="n"/>
+      <c r="E43" s="27" t="n"/>
+      <c r="F43" s="27" t="n"/>
+      <c r="G43" s="27" t="n"/>
+      <c r="H43" s="27" t="n"/>
+      <c r="I43" s="27" t="n"/>
+      <c r="J43" s="57" t="n"/>
+    </row>
+    <row r="44" ht="6" customHeight="1" s="6">
+      <c r="A44" s="8" t="n"/>
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="27" t="n"/>
       <c r="D44" s="27" t="n"/>
@@ -1788,26 +1787,27 @@
       <c r="I44" s="27" t="n"/>
       <c r="J44" s="57" t="n"/>
     </row>
-    <row r="45" ht="17" customHeight="1" s="6">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>彼は来週テニスをします。</t>
-        </is>
-      </c>
-      <c r="B45" s="27" t="n"/>
-      <c r="C45" s="27" t="n"/>
-      <c r="D45" s="27" t="n"/>
-      <c r="E45" s="27" t="n"/>
-      <c r="F45" s="27" t="n"/>
-      <c r="G45" s="27" t="n"/>
-      <c r="H45" s="27" t="n"/>
-      <c r="I45" s="27" t="n"/>
-      <c r="J45" s="57" t="n"/>
-    </row>
-    <row r="46" ht="20" customHeight="1" s="6">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>回答（will）：</t>
+    <row r="45" ht="18" customHeight="1" s="6">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>3．主語は「彼」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="n"/>
+      <c r="C45" s="25" t="n"/>
+      <c r="D45" s="25" t="n"/>
+      <c r="E45" s="25" t="n"/>
+      <c r="F45" s="25" t="n"/>
+      <c r="G45" s="25" t="n"/>
+      <c r="H45" s="25" t="n"/>
+      <c r="I45" s="25" t="n"/>
+      <c r="J45" s="56" t="n"/>
+    </row>
+    <row r="46" ht="36" customHeight="1" s="6">
+      <c r="A46" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B46" s="27" t="n"/>
@@ -1820,10 +1820,10 @@
       <c r="I46" s="27" t="n"/>
       <c r="J46" s="57" t="n"/>
     </row>
-    <row r="47" ht="20" customHeight="1" s="6">
+    <row r="47" ht="18" customHeight="1" s="6">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>彼は来週テニスをします。</t>
         </is>
       </c>
       <c r="B47" s="27" t="n"/>
@@ -1836,10 +1836,10 @@
       <c r="I47" s="27" t="n"/>
       <c r="J47" s="57" t="n"/>
     </row>
-    <row r="48" ht="17" customHeight="1" s="6">
+    <row r="48" ht="20" customHeight="1" s="6">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>彼は来週テニスをしません。</t>
+          <t>回答（will）：</t>
         </is>
       </c>
       <c r="B48" s="27" t="n"/>
@@ -1855,7 +1855,7 @@
     <row r="49" ht="20" customHeight="1" s="6">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B49" s="27" t="n"/>
@@ -1868,10 +1868,10 @@
       <c r="I49" s="27" t="n"/>
       <c r="J49" s="57" t="n"/>
     </row>
-    <row r="50" ht="20" customHeight="1" s="6">
+    <row r="50" ht="18" customHeight="1" s="6">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>彼は来週テニスをしません。</t>
         </is>
       </c>
       <c r="B50" s="27" t="n"/>
@@ -1887,7 +1887,7 @@
     <row r="51" ht="20" customHeight="1" s="6">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B51" s="27" t="n"/>
@@ -1900,10 +1900,10 @@
       <c r="I51" s="27" t="n"/>
       <c r="J51" s="57" t="n"/>
     </row>
-    <row r="52" ht="17" customHeight="1" s="6">
+    <row r="52" ht="20" customHeight="1" s="6">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>彼は来週テニスをしますか。</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B52" s="27" t="n"/>
@@ -1919,7 +1919,7 @@
     <row r="53" ht="20" customHeight="1" s="6">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B53" s="27" t="n"/>
@@ -1932,10 +1932,10 @@
       <c r="I53" s="27" t="n"/>
       <c r="J53" s="57" t="n"/>
     </row>
-    <row r="54" ht="20" customHeight="1" s="6">
+    <row r="54" ht="18" customHeight="1" s="6">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ疑問文）：</t>
+          <t>彼は来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B54" s="27" t="n"/>
@@ -1948,10 +1948,10 @@
       <c r="I54" s="27" t="n"/>
       <c r="J54" s="57" t="n"/>
     </row>
-    <row r="55" ht="17" customHeight="1" s="6">
+    <row r="55" ht="20" customHeight="1" s="6">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>回答（will疑問文）：</t>
         </is>
       </c>
       <c r="B55" s="27" t="n"/>
@@ -1967,7 +1967,7 @@
     <row r="56" ht="20" customHeight="1" s="6">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>回答（will返答）：</t>
+          <t>回答（言いかえ疑問文）：</t>
         </is>
       </c>
       <c r="B56" s="27" t="n"/>
@@ -1980,10 +1980,10 @@
       <c r="I56" s="27" t="n"/>
       <c r="J56" s="57" t="n"/>
     </row>
-    <row r="57" ht="20" customHeight="1" s="6">
+    <row r="57" ht="18" customHeight="1" s="6">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B57" s="27" t="n"/>
@@ -1996,10 +1996,10 @@
       <c r="I57" s="27" t="n"/>
       <c r="J57" s="57" t="n"/>
     </row>
-    <row r="58" ht="17" customHeight="1" s="6">
+    <row r="58" ht="20" customHeight="1" s="6">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>回答（will返答）：</t>
         </is>
       </c>
       <c r="B58" s="27" t="n"/>
@@ -2015,7 +2015,7 @@
     <row r="59" ht="20" customHeight="1" s="6">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B59" s="27" t="n"/>
@@ -2028,10 +2028,10 @@
       <c r="I59" s="27" t="n"/>
       <c r="J59" s="57" t="n"/>
     </row>
-    <row r="60" ht="20" customHeight="1" s="6">
+    <row r="60" ht="18" customHeight="1" s="6">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B60" s="27" t="n"/>
@@ -2047,7 +2047,7 @@
     <row r="61" ht="20" customHeight="1" s="6">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B61" s="27" t="n"/>
@@ -2060,8 +2060,12 @@
       <c r="I61" s="27" t="n"/>
       <c r="J61" s="57" t="n"/>
     </row>
-    <row r="62" ht="4" customHeight="1" s="6">
-      <c r="A62" s="8" t="n"/>
+    <row r="62" ht="20" customHeight="1" s="6">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="27" t="n"/>
       <c r="D62" s="27" t="n"/>
@@ -2072,27 +2076,26 @@
       <c r="I62" s="27" t="n"/>
       <c r="J62" s="57" t="n"/>
     </row>
-    <row r="63" ht="16" customHeight="1" s="6">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>4．主語は「彼女」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B63" s="25" t="n"/>
-      <c r="C63" s="25" t="n"/>
-      <c r="D63" s="25" t="n"/>
-      <c r="E63" s="25" t="n"/>
-      <c r="F63" s="25" t="n"/>
-      <c r="G63" s="25" t="n"/>
-      <c r="H63" s="25" t="n"/>
-      <c r="I63" s="25" t="n"/>
-      <c r="J63" s="56" t="n"/>
-    </row>
-    <row r="64" ht="34" customHeight="1" s="6">
-      <c r="A64" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="63" ht="20" customHeight="1" s="6">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ基本形）：</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="n"/>
+      <c r="C63" s="27" t="n"/>
+      <c r="D63" s="27" t="n"/>
+      <c r="E63" s="27" t="n"/>
+      <c r="F63" s="27" t="n"/>
+      <c r="G63" s="27" t="n"/>
+      <c r="H63" s="27" t="n"/>
+      <c r="I63" s="27" t="n"/>
+      <c r="J63" s="57" t="n"/>
+    </row>
+    <row r="64" ht="20" customHeight="1" s="6">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ短縮形）：</t>
         </is>
       </c>
       <c r="B64" s="27" t="n"/>
@@ -2105,12 +2108,8 @@
       <c r="I64" s="27" t="n"/>
       <c r="J64" s="57" t="n"/>
     </row>
-    <row r="65" ht="17" customHeight="1" s="6">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>彼女は来週テニスをします。</t>
-        </is>
-      </c>
+    <row r="65" ht="6" customHeight="1" s="6">
+      <c r="A65" s="8" t="n"/>
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="27" t="n"/>
       <c r="D65" s="27" t="n"/>
@@ -2121,26 +2120,27 @@
       <c r="I65" s="27" t="n"/>
       <c r="J65" s="57" t="n"/>
     </row>
-    <row r="66" ht="20" customHeight="1" s="6">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>回答（will）：</t>
-        </is>
-      </c>
-      <c r="B66" s="27" t="n"/>
-      <c r="C66" s="27" t="n"/>
-      <c r="D66" s="27" t="n"/>
-      <c r="E66" s="27" t="n"/>
-      <c r="F66" s="27" t="n"/>
-      <c r="G66" s="27" t="n"/>
-      <c r="H66" s="27" t="n"/>
-      <c r="I66" s="27" t="n"/>
-      <c r="J66" s="57" t="n"/>
-    </row>
-    <row r="67" ht="20" customHeight="1" s="6">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>回答（言いかえ）：</t>
+    <row r="66" ht="18" customHeight="1" s="6">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>4．主語は「彼女」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="n"/>
+      <c r="C66" s="25" t="n"/>
+      <c r="D66" s="25" t="n"/>
+      <c r="E66" s="25" t="n"/>
+      <c r="F66" s="25" t="n"/>
+      <c r="G66" s="25" t="n"/>
+      <c r="H66" s="25" t="n"/>
+      <c r="I66" s="25" t="n"/>
+      <c r="J66" s="56" t="n"/>
+    </row>
+    <row r="67" ht="36" customHeight="1" s="6">
+      <c r="A67" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B67" s="27" t="n"/>
@@ -2153,10 +2153,10 @@
       <c r="I67" s="27" t="n"/>
       <c r="J67" s="57" t="n"/>
     </row>
-    <row r="68" ht="17" customHeight="1" s="6">
+    <row r="68" ht="18" customHeight="1" s="6">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>彼女は来週テニスをしません。</t>
+          <t>彼女は来週テニスをします。</t>
         </is>
       </c>
       <c r="B68" s="27" t="n"/>
@@ -2172,7 +2172,7 @@
     <row r="69" ht="20" customHeight="1" s="6">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（will）：</t>
         </is>
       </c>
       <c r="B69" s="27" t="n"/>
@@ -2188,7 +2188,7 @@
     <row r="70" ht="20" customHeight="1" s="6">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B70" s="27" t="n"/>
@@ -2201,10 +2201,10 @@
       <c r="I70" s="27" t="n"/>
       <c r="J70" s="57" t="n"/>
     </row>
-    <row r="71" ht="20" customHeight="1" s="6">
+    <row r="71" ht="18" customHeight="1" s="6">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>彼女は来週テニスをしません。</t>
         </is>
       </c>
       <c r="B71" s="27" t="n"/>
@@ -2217,10 +2217,10 @@
       <c r="I71" s="27" t="n"/>
       <c r="J71" s="57" t="n"/>
     </row>
-    <row r="72" ht="17" customHeight="1" s="6">
+    <row r="72" ht="20" customHeight="1" s="6">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>彼女は来週テニスをしますか。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B72" s="27" t="n"/>
@@ -2236,7 +2236,7 @@
     <row r="73" ht="20" customHeight="1" s="6">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B73" s="27" t="n"/>
@@ -2252,7 +2252,7 @@
     <row r="74" ht="20" customHeight="1" s="6">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ疑問文）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B74" s="27" t="n"/>
@@ -2265,10 +2265,10 @@
       <c r="I74" s="27" t="n"/>
       <c r="J74" s="57" t="n"/>
     </row>
-    <row r="75" ht="17" customHeight="1" s="6">
+    <row r="75" ht="18" customHeight="1" s="6">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>彼女は来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B75" s="27" t="n"/>
@@ -2284,7 +2284,7 @@
     <row r="76" ht="20" customHeight="1" s="6">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>回答（will返答）：</t>
+          <t>回答（will疑問文）：</t>
         </is>
       </c>
       <c r="B76" s="27" t="n"/>
@@ -2300,7 +2300,7 @@
     <row r="77" ht="20" customHeight="1" s="6">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>回答（言いかえ疑問文）：</t>
         </is>
       </c>
       <c r="B77" s="27" t="n"/>
@@ -2313,10 +2313,10 @@
       <c r="I77" s="27" t="n"/>
       <c r="J77" s="57" t="n"/>
     </row>
-    <row r="78" ht="17" customHeight="1" s="6">
+    <row r="78" ht="18" customHeight="1" s="6">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B78" s="27" t="n"/>
@@ -2332,7 +2332,7 @@
     <row r="79" ht="20" customHeight="1" s="6">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（will返答）：</t>
         </is>
       </c>
       <c r="B79" s="27" t="n"/>
@@ -2348,7 +2348,7 @@
     <row r="80" ht="20" customHeight="1" s="6">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B80" s="27" t="n"/>
@@ -2361,10 +2361,10 @@
       <c r="I80" s="27" t="n"/>
       <c r="J80" s="57" t="n"/>
     </row>
-    <row r="81" ht="20" customHeight="1" s="6">
+    <row r="81" ht="18" customHeight="1" s="6">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B81" s="27" t="n"/>
@@ -2377,8 +2377,12 @@
       <c r="I81" s="27" t="n"/>
       <c r="J81" s="57" t="n"/>
     </row>
-    <row r="82" ht="4" customHeight="1" s="6">
-      <c r="A82" s="8" t="n"/>
+    <row r="82" ht="20" customHeight="1" s="6">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="27" t="n"/>
       <c r="D82" s="27" t="n"/>
@@ -2389,28 +2393,26 @@
       <c r="I82" s="27" t="n"/>
       <c r="J82" s="57" t="n"/>
     </row>
-    <row r="83" ht="16" customHeight="1" s="6">
-      <c r="A83" s="9" t="inlineStr">
-        <is>
-          <t>5．主語は「私たち」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B83" s="25" t="n"/>
-      <c r="C83" s="25" t="n"/>
-      <c r="D83" s="25" t="n"/>
-      <c r="E83" s="25" t="n"/>
-      <c r="F83" s="25" t="n"/>
-      <c r="G83" s="25" t="n"/>
-      <c r="H83" s="25" t="n"/>
-      <c r="I83" s="25" t="n"/>
-      <c r="J83" s="56" t="n"/>
-    </row>
-    <row r="84" ht="40" customHeight="1" s="6">
-      <c r="A84" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。
-※相手が答える形なので、返答では I / we ではなく you を使います。</t>
+    <row r="83" ht="20" customHeight="1" s="6">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B83" s="27" t="n"/>
+      <c r="C83" s="27" t="n"/>
+      <c r="D83" s="27" t="n"/>
+      <c r="E83" s="27" t="n"/>
+      <c r="F83" s="27" t="n"/>
+      <c r="G83" s="27" t="n"/>
+      <c r="H83" s="27" t="n"/>
+      <c r="I83" s="27" t="n"/>
+      <c r="J83" s="57" t="n"/>
+    </row>
+    <row r="84" ht="20" customHeight="1" s="6">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ基本形）：</t>
         </is>
       </c>
       <c r="B84" s="27" t="n"/>
@@ -2423,10 +2425,10 @@
       <c r="I84" s="27" t="n"/>
       <c r="J84" s="57" t="n"/>
     </row>
-    <row r="85" ht="17" customHeight="1" s="6">
+    <row r="85" ht="20" customHeight="1" s="6">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>私たちは来週テニスをします。</t>
+          <t>回答（言いかえ短縮形）：</t>
         </is>
       </c>
       <c r="B85" s="27" t="n"/>
@@ -2439,12 +2441,8 @@
       <c r="I85" s="27" t="n"/>
       <c r="J85" s="57" t="n"/>
     </row>
-    <row r="86" ht="20" customHeight="1" s="6">
-      <c r="A86" s="11" t="inlineStr">
-        <is>
-          <t>回答（will）：</t>
-        </is>
-      </c>
+    <row r="86" ht="6" customHeight="1" s="6">
+      <c r="A86" s="8" t="n"/>
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="27" t="n"/>
       <c r="D86" s="27" t="n"/>
@@ -2455,26 +2453,28 @@
       <c r="I86" s="27" t="n"/>
       <c r="J86" s="57" t="n"/>
     </row>
-    <row r="87" ht="20" customHeight="1" s="6">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t>回答（言いかえ）：</t>
-        </is>
-      </c>
-      <c r="B87" s="27" t="n"/>
-      <c r="C87" s="27" t="n"/>
-      <c r="D87" s="27" t="n"/>
-      <c r="E87" s="27" t="n"/>
-      <c r="F87" s="27" t="n"/>
-      <c r="G87" s="27" t="n"/>
-      <c r="H87" s="27" t="n"/>
-      <c r="I87" s="27" t="n"/>
-      <c r="J87" s="57" t="n"/>
-    </row>
-    <row r="88" ht="17" customHeight="1" s="6">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>私たちは来週テニスをしません。</t>
+    <row r="87" ht="18" customHeight="1" s="6">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>5．主語は「私たち」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B87" s="25" t="n"/>
+      <c r="C87" s="25" t="n"/>
+      <c r="D87" s="25" t="n"/>
+      <c r="E87" s="25" t="n"/>
+      <c r="F87" s="25" t="n"/>
+      <c r="G87" s="25" t="n"/>
+      <c r="H87" s="25" t="n"/>
+      <c r="I87" s="25" t="n"/>
+      <c r="J87" s="56" t="n"/>
+    </row>
+    <row r="88" ht="42" customHeight="1" s="6">
+      <c r="A88" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。
+※相手が答える形なので、返答では I / we ではなく you を使います。</t>
         </is>
       </c>
       <c r="B88" s="27" t="n"/>
@@ -2487,10 +2487,10 @@
       <c r="I88" s="27" t="n"/>
       <c r="J88" s="57" t="n"/>
     </row>
-    <row r="89" ht="20" customHeight="1" s="6">
+    <row r="89" ht="18" customHeight="1" s="6">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>私たちは来週テニスをします。</t>
         </is>
       </c>
       <c r="B89" s="27" t="n"/>
@@ -2506,7 +2506,7 @@
     <row r="90" ht="20" customHeight="1" s="6">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（will）：</t>
         </is>
       </c>
       <c r="B90" s="27" t="n"/>
@@ -2535,10 +2535,10 @@
       <c r="I91" s="27" t="n"/>
       <c r="J91" s="57" t="n"/>
     </row>
-    <row r="92" ht="17" customHeight="1" s="6">
+    <row r="92" ht="18" customHeight="1" s="6">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>私たちは来週テニスをしますか。</t>
+          <t>私たちは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B92" s="27" t="n"/>
@@ -2554,7 +2554,7 @@
     <row r="93" ht="20" customHeight="1" s="6">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B93" s="27" t="n"/>
@@ -2570,7 +2570,7 @@
     <row r="94" ht="20" customHeight="1" s="6">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ疑問文）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B94" s="27" t="n"/>
@@ -2583,10 +2583,10 @@
       <c r="I94" s="27" t="n"/>
       <c r="J94" s="57" t="n"/>
     </row>
-    <row r="95" ht="17" customHeight="1" s="6">
+    <row r="95" ht="20" customHeight="1" s="6">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B95" s="27" t="n"/>
@@ -2599,10 +2599,10 @@
       <c r="I95" s="27" t="n"/>
       <c r="J95" s="57" t="n"/>
     </row>
-    <row r="96" ht="20" customHeight="1" s="6">
+    <row r="96" ht="18" customHeight="1" s="6">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>回答（will返答）：</t>
+          <t>私たちは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B96" s="27" t="n"/>
@@ -2618,7 +2618,7 @@
     <row r="97" ht="20" customHeight="1" s="6">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>回答（will疑問文）：</t>
         </is>
       </c>
       <c r="B97" s="27" t="n"/>
@@ -2631,10 +2631,10 @@
       <c r="I97" s="27" t="n"/>
       <c r="J97" s="57" t="n"/>
     </row>
-    <row r="98" ht="17" customHeight="1" s="6">
+    <row r="98" ht="20" customHeight="1" s="6">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>回答（言いかえ疑問文）：</t>
         </is>
       </c>
       <c r="B98" s="27" t="n"/>
@@ -2647,10 +2647,10 @@
       <c r="I98" s="27" t="n"/>
       <c r="J98" s="57" t="n"/>
     </row>
-    <row r="99" ht="20" customHeight="1" s="6">
+    <row r="99" ht="18" customHeight="1" s="6">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B99" s="27" t="n"/>
@@ -2666,7 +2666,7 @@
     <row r="100" ht="20" customHeight="1" s="6">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（will返答）：</t>
         </is>
       </c>
       <c r="B100" s="27" t="n"/>
@@ -2695,8 +2695,12 @@
       <c r="I101" s="27" t="n"/>
       <c r="J101" s="57" t="n"/>
     </row>
-    <row r="102" ht="4" customHeight="1" s="6">
-      <c r="A102" s="8" t="n"/>
+    <row r="102" ht="18" customHeight="1" s="6">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、しません。</t>
+        </is>
+      </c>
       <c r="B102" s="27" t="n"/>
       <c r="C102" s="27" t="n"/>
       <c r="D102" s="27" t="n"/>
@@ -2707,27 +2711,26 @@
       <c r="I102" s="27" t="n"/>
       <c r="J102" s="57" t="n"/>
     </row>
-    <row r="103" ht="16" customHeight="1" s="6">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>6．主語は「あなたたち」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B103" s="25" t="n"/>
-      <c r="C103" s="25" t="n"/>
-      <c r="D103" s="25" t="n"/>
-      <c r="E103" s="25" t="n"/>
-      <c r="F103" s="25" t="n"/>
-      <c r="G103" s="25" t="n"/>
-      <c r="H103" s="25" t="n"/>
-      <c r="I103" s="25" t="n"/>
-      <c r="J103" s="56" t="n"/>
-    </row>
-    <row r="104" ht="34" customHeight="1" s="6">
-      <c r="A104" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="103" ht="20" customHeight="1" s="6">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B103" s="27" t="n"/>
+      <c r="C103" s="27" t="n"/>
+      <c r="D103" s="27" t="n"/>
+      <c r="E103" s="27" t="n"/>
+      <c r="F103" s="27" t="n"/>
+      <c r="G103" s="27" t="n"/>
+      <c r="H103" s="27" t="n"/>
+      <c r="I103" s="27" t="n"/>
+      <c r="J103" s="57" t="n"/>
+    </row>
+    <row r="104" ht="20" customHeight="1" s="6">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B104" s="27" t="n"/>
@@ -2740,10 +2743,10 @@
       <c r="I104" s="27" t="n"/>
       <c r="J104" s="57" t="n"/>
     </row>
-    <row r="105" ht="17" customHeight="1" s="6">
+    <row r="105" ht="20" customHeight="1" s="6">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>あなたたちは来週テニスをします。</t>
+          <t>回答（言いかえ基本形）：</t>
         </is>
       </c>
       <c r="B105" s="27" t="n"/>
@@ -2759,7 +2762,7 @@
     <row r="106" ht="20" customHeight="1" s="6">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>回答（will）：</t>
+          <t>回答（言いかえ短縮形）：</t>
         </is>
       </c>
       <c r="B106" s="27" t="n"/>
@@ -2772,12 +2775,8 @@
       <c r="I106" s="27" t="n"/>
       <c r="J106" s="57" t="n"/>
     </row>
-    <row r="107" ht="20" customHeight="1" s="6">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t>回答（言いかえ）：</t>
-        </is>
-      </c>
+    <row r="107" ht="6" customHeight="1" s="6">
+      <c r="A107" s="8" t="n"/>
       <c r="B107" s="27" t="n"/>
       <c r="C107" s="27" t="n"/>
       <c r="D107" s="27" t="n"/>
@@ -2788,26 +2787,27 @@
       <c r="I107" s="27" t="n"/>
       <c r="J107" s="57" t="n"/>
     </row>
-    <row r="108" ht="17" customHeight="1" s="6">
-      <c r="A108" s="11" t="inlineStr">
-        <is>
-          <t>あなたたちは来週テニスをしません。</t>
-        </is>
-      </c>
-      <c r="B108" s="27" t="n"/>
-      <c r="C108" s="27" t="n"/>
-      <c r="D108" s="27" t="n"/>
-      <c r="E108" s="27" t="n"/>
-      <c r="F108" s="27" t="n"/>
-      <c r="G108" s="27" t="n"/>
-      <c r="H108" s="27" t="n"/>
-      <c r="I108" s="27" t="n"/>
-      <c r="J108" s="57" t="n"/>
-    </row>
-    <row r="109" ht="20" customHeight="1" s="6">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t>回答（基本形）：</t>
+    <row r="108" ht="18" customHeight="1" s="6">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>6．主語は「あなたたち」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B108" s="25" t="n"/>
+      <c r="C108" s="25" t="n"/>
+      <c r="D108" s="25" t="n"/>
+      <c r="E108" s="25" t="n"/>
+      <c r="F108" s="25" t="n"/>
+      <c r="G108" s="25" t="n"/>
+      <c r="H108" s="25" t="n"/>
+      <c r="I108" s="25" t="n"/>
+      <c r="J108" s="56" t="n"/>
+    </row>
+    <row r="109" ht="36" customHeight="1" s="6">
+      <c r="A109" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B109" s="27" t="n"/>
@@ -2820,10 +2820,10 @@
       <c r="I109" s="27" t="n"/>
       <c r="J109" s="57" t="n"/>
     </row>
-    <row r="110" ht="20" customHeight="1" s="6">
+    <row r="110" ht="18" customHeight="1" s="6">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>あなたたちは来週テニスをします。</t>
         </is>
       </c>
       <c r="B110" s="27" t="n"/>
@@ -2839,7 +2839,7 @@
     <row r="111" ht="20" customHeight="1" s="6">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（will）：</t>
         </is>
       </c>
       <c r="B111" s="27" t="n"/>
@@ -2852,10 +2852,10 @@
       <c r="I111" s="27" t="n"/>
       <c r="J111" s="57" t="n"/>
     </row>
-    <row r="112" ht="17" customHeight="1" s="6">
+    <row r="112" ht="20" customHeight="1" s="6">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>あなたたちは来週テニスをしますか。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B112" s="27" t="n"/>
@@ -2868,10 +2868,10 @@
       <c r="I112" s="27" t="n"/>
       <c r="J112" s="57" t="n"/>
     </row>
-    <row r="113" ht="20" customHeight="1" s="6">
+    <row r="113" ht="18" customHeight="1" s="6">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>あなたたちは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B113" s="27" t="n"/>
@@ -2887,7 +2887,7 @@
     <row r="114" ht="20" customHeight="1" s="6">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ疑問文）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B114" s="27" t="n"/>
@@ -2900,10 +2900,10 @@
       <c r="I114" s="27" t="n"/>
       <c r="J114" s="57" t="n"/>
     </row>
-    <row r="115" ht="17" customHeight="1" s="6">
+    <row r="115" ht="20" customHeight="1" s="6">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B115" s="27" t="n"/>
@@ -2919,7 +2919,7 @@
     <row r="116" ht="20" customHeight="1" s="6">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>回答（will返答）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B116" s="27" t="n"/>
@@ -2932,10 +2932,10 @@
       <c r="I116" s="27" t="n"/>
       <c r="J116" s="57" t="n"/>
     </row>
-    <row r="117" ht="20" customHeight="1" s="6">
+    <row r="117" ht="18" customHeight="1" s="6">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>あなたたちは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B117" s="27" t="n"/>
@@ -2948,10 +2948,10 @@
       <c r="I117" s="27" t="n"/>
       <c r="J117" s="57" t="n"/>
     </row>
-    <row r="118" ht="17" customHeight="1" s="6">
+    <row r="118" ht="20" customHeight="1" s="6">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>回答（will疑問文）：</t>
         </is>
       </c>
       <c r="B118" s="27" t="n"/>
@@ -2967,7 +2967,7 @@
     <row r="119" ht="20" customHeight="1" s="6">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（言いかえ疑問文）：</t>
         </is>
       </c>
       <c r="B119" s="27" t="n"/>
@@ -2980,10 +2980,10 @@
       <c r="I119" s="27" t="n"/>
       <c r="J119" s="57" t="n"/>
     </row>
-    <row r="120" ht="20" customHeight="1" s="6">
+    <row r="120" ht="18" customHeight="1" s="6">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B120" s="27" t="n"/>
@@ -2999,7 +2999,7 @@
     <row r="121" ht="20" customHeight="1" s="6">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>回答（will返答）：</t>
         </is>
       </c>
       <c r="B121" s="27" t="n"/>
@@ -3012,8 +3012,12 @@
       <c r="I121" s="27" t="n"/>
       <c r="J121" s="57" t="n"/>
     </row>
-    <row r="122" ht="4" customHeight="1" s="6">
-      <c r="A122" s="8" t="n"/>
+    <row r="122" ht="20" customHeight="1" s="6">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ返答）：</t>
+        </is>
+      </c>
       <c r="B122" s="27" t="n"/>
       <c r="C122" s="27" t="n"/>
       <c r="D122" s="27" t="n"/>
@@ -3024,27 +3028,26 @@
       <c r="I122" s="27" t="n"/>
       <c r="J122" s="57" t="n"/>
     </row>
-    <row r="123" ht="16" customHeight="1" s="6">
-      <c r="A123" s="9" t="inlineStr">
-        <is>
-          <t>7．主語は「彼ら」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B123" s="25" t="n"/>
-      <c r="C123" s="25" t="n"/>
-      <c r="D123" s="25" t="n"/>
-      <c r="E123" s="25" t="n"/>
-      <c r="F123" s="25" t="n"/>
-      <c r="G123" s="25" t="n"/>
-      <c r="H123" s="25" t="n"/>
-      <c r="I123" s="25" t="n"/>
-      <c r="J123" s="56" t="n"/>
-    </row>
-    <row r="124" ht="34" customHeight="1" s="6">
-      <c r="A124" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="123" ht="18" customHeight="1" s="6">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、しません。</t>
+        </is>
+      </c>
+      <c r="B123" s="27" t="n"/>
+      <c r="C123" s="27" t="n"/>
+      <c r="D123" s="27" t="n"/>
+      <c r="E123" s="27" t="n"/>
+      <c r="F123" s="27" t="n"/>
+      <c r="G123" s="27" t="n"/>
+      <c r="H123" s="27" t="n"/>
+      <c r="I123" s="27" t="n"/>
+      <c r="J123" s="57" t="n"/>
+    </row>
+    <row r="124" ht="20" customHeight="1" s="6">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B124" s="27" t="n"/>
@@ -3057,10 +3060,10 @@
       <c r="I124" s="27" t="n"/>
       <c r="J124" s="57" t="n"/>
     </row>
-    <row r="125" ht="17" customHeight="1" s="6">
+    <row r="125" ht="20" customHeight="1" s="6">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>彼らは来週テニスをします。</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B125" s="27" t="n"/>
@@ -3076,7 +3079,7 @@
     <row r="126" ht="20" customHeight="1" s="6">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>回答（will）：</t>
+          <t>回答（言いかえ基本形）：</t>
         </is>
       </c>
       <c r="B126" s="27" t="n"/>
@@ -3092,7 +3095,7 @@
     <row r="127" ht="20" customHeight="1" s="6">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（言いかえ短縮形）：</t>
         </is>
       </c>
       <c r="B127" s="27" t="n"/>
@@ -3105,12 +3108,8 @@
       <c r="I127" s="27" t="n"/>
       <c r="J127" s="57" t="n"/>
     </row>
-    <row r="128" ht="17" customHeight="1" s="6">
-      <c r="A128" s="11" t="inlineStr">
-        <is>
-          <t>彼らは来週テニスをしません。</t>
-        </is>
-      </c>
+    <row r="128" ht="6" customHeight="1" s="6">
+      <c r="A128" s="8" t="n"/>
       <c r="B128" s="27" t="n"/>
       <c r="C128" s="27" t="n"/>
       <c r="D128" s="27" t="n"/>
@@ -3121,26 +3120,27 @@
       <c r="I128" s="27" t="n"/>
       <c r="J128" s="57" t="n"/>
     </row>
-    <row r="129" ht="20" customHeight="1" s="6">
-      <c r="A129" s="11" t="inlineStr">
-        <is>
-          <t>回答（基本形）：</t>
-        </is>
-      </c>
-      <c r="B129" s="27" t="n"/>
-      <c r="C129" s="27" t="n"/>
-      <c r="D129" s="27" t="n"/>
-      <c r="E129" s="27" t="n"/>
-      <c r="F129" s="27" t="n"/>
-      <c r="G129" s="27" t="n"/>
-      <c r="H129" s="27" t="n"/>
-      <c r="I129" s="27" t="n"/>
-      <c r="J129" s="57" t="n"/>
-    </row>
-    <row r="130" ht="20" customHeight="1" s="6">
-      <c r="A130" s="11" t="inlineStr">
-        <is>
-          <t>回答（短縮形）：</t>
+    <row r="129" ht="18" customHeight="1" s="6">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>7．主語は「彼ら」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B129" s="25" t="n"/>
+      <c r="C129" s="25" t="n"/>
+      <c r="D129" s="25" t="n"/>
+      <c r="E129" s="25" t="n"/>
+      <c r="F129" s="25" t="n"/>
+      <c r="G129" s="25" t="n"/>
+      <c r="H129" s="25" t="n"/>
+      <c r="I129" s="25" t="n"/>
+      <c r="J129" s="56" t="n"/>
+    </row>
+    <row r="130" ht="36" customHeight="1" s="6">
+      <c r="A130" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B130" s="27" t="n"/>
@@ -3153,10 +3153,10 @@
       <c r="I130" s="27" t="n"/>
       <c r="J130" s="57" t="n"/>
     </row>
-    <row r="131" ht="20" customHeight="1" s="6">
+    <row r="131" ht="18" customHeight="1" s="6">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>彼らは来週テニスをします。</t>
         </is>
       </c>
       <c r="B131" s="27" t="n"/>
@@ -3169,10 +3169,10 @@
       <c r="I131" s="27" t="n"/>
       <c r="J131" s="57" t="n"/>
     </row>
-    <row r="132" ht="17" customHeight="1" s="6">
+    <row r="132" ht="20" customHeight="1" s="6">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>彼らは来週テニスをしますか。</t>
+          <t>回答（will）：</t>
         </is>
       </c>
       <c r="B132" s="27" t="n"/>
@@ -3188,7 +3188,7 @@
     <row r="133" ht="20" customHeight="1" s="6">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B133" s="27" t="n"/>
@@ -3201,10 +3201,10 @@
       <c r="I133" s="27" t="n"/>
       <c r="J133" s="57" t="n"/>
     </row>
-    <row r="134" ht="20" customHeight="1" s="6">
+    <row r="134" ht="18" customHeight="1" s="6">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ疑問文）：</t>
+          <t>彼らは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B134" s="27" t="n"/>
@@ -3217,10 +3217,10 @@
       <c r="I134" s="27" t="n"/>
       <c r="J134" s="57" t="n"/>
     </row>
-    <row r="135" ht="17" customHeight="1" s="6">
+    <row r="135" ht="20" customHeight="1" s="6">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B135" s="27" t="n"/>
@@ -3236,7 +3236,7 @@
     <row r="136" ht="20" customHeight="1" s="6">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>回答（will返答）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B136" s="27" t="n"/>
@@ -3252,7 +3252,7 @@
     <row r="137" ht="20" customHeight="1" s="6">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B137" s="27" t="n"/>
@@ -3265,10 +3265,10 @@
       <c r="I137" s="27" t="n"/>
       <c r="J137" s="57" t="n"/>
     </row>
-    <row r="138" ht="17" customHeight="1" s="6">
+    <row r="138" ht="18" customHeight="1" s="6">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>彼らは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B138" s="27" t="n"/>
@@ -3284,7 +3284,7 @@
     <row r="139" ht="20" customHeight="1" s="6">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（will疑問文）：</t>
         </is>
       </c>
       <c r="B139" s="27" t="n"/>
@@ -3300,7 +3300,7 @@
     <row r="140" ht="20" customHeight="1" s="6">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（言いかえ疑問文）：</t>
         </is>
       </c>
       <c r="B140" s="27" t="n"/>
@@ -3313,10 +3313,10 @@
       <c r="I140" s="27" t="n"/>
       <c r="J140" s="57" t="n"/>
     </row>
-    <row r="141" ht="20" customHeight="1" s="6">
+    <row r="141" ht="18" customHeight="1" s="6">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B141" s="27" t="n"/>
@@ -3329,8 +3329,12 @@
       <c r="I141" s="27" t="n"/>
       <c r="J141" s="57" t="n"/>
     </row>
-    <row r="142" ht="4" customHeight="1" s="6">
-      <c r="A142" s="8" t="n"/>
+    <row r="142" ht="20" customHeight="1" s="6">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>回答（will返答）：</t>
+        </is>
+      </c>
       <c r="B142" s="27" t="n"/>
       <c r="C142" s="27" t="n"/>
       <c r="D142" s="27" t="n"/>
@@ -3341,27 +3345,26 @@
       <c r="I142" s="27" t="n"/>
       <c r="J142" s="57" t="n"/>
     </row>
-    <row r="143" ht="16" customHeight="1" s="6">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>8．主語は「リョウタロウ」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B143" s="25" t="n"/>
-      <c r="C143" s="25" t="n"/>
-      <c r="D143" s="25" t="n"/>
-      <c r="E143" s="25" t="n"/>
-      <c r="F143" s="25" t="n"/>
-      <c r="G143" s="25" t="n"/>
-      <c r="H143" s="25" t="n"/>
-      <c r="I143" s="25" t="n"/>
-      <c r="J143" s="56" t="n"/>
-    </row>
-    <row r="144" ht="34" customHeight="1" s="6">
-      <c r="A144" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="143" ht="20" customHeight="1" s="6">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ返答）：</t>
+        </is>
+      </c>
+      <c r="B143" s="27" t="n"/>
+      <c r="C143" s="27" t="n"/>
+      <c r="D143" s="27" t="n"/>
+      <c r="E143" s="27" t="n"/>
+      <c r="F143" s="27" t="n"/>
+      <c r="G143" s="27" t="n"/>
+      <c r="H143" s="27" t="n"/>
+      <c r="I143" s="27" t="n"/>
+      <c r="J143" s="57" t="n"/>
+    </row>
+    <row r="144" ht="18" customHeight="1" s="6">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B144" s="27" t="n"/>
@@ -3374,10 +3377,10 @@
       <c r="I144" s="27" t="n"/>
       <c r="J144" s="57" t="n"/>
     </row>
-    <row r="145" ht="17" customHeight="1" s="6">
+    <row r="145" ht="20" customHeight="1" s="6">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは来週テニスをします。</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B145" s="27" t="n"/>
@@ -3393,7 +3396,7 @@
     <row r="146" ht="20" customHeight="1" s="6">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>回答（will）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B146" s="27" t="n"/>
@@ -3409,7 +3412,7 @@
     <row r="147" ht="20" customHeight="1" s="6">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（言いかえ基本形）：</t>
         </is>
       </c>
       <c r="B147" s="27" t="n"/>
@@ -3422,10 +3425,10 @@
       <c r="I147" s="27" t="n"/>
       <c r="J147" s="57" t="n"/>
     </row>
-    <row r="148" ht="17" customHeight="1" s="6">
+    <row r="148" ht="20" customHeight="1" s="6">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは来週テニスをしません。</t>
+          <t>回答（言いかえ短縮形）：</t>
         </is>
       </c>
       <c r="B148" s="27" t="n"/>
@@ -3438,12 +3441,8 @@
       <c r="I148" s="27" t="n"/>
       <c r="J148" s="57" t="n"/>
     </row>
-    <row r="149" ht="20" customHeight="1" s="6">
-      <c r="A149" s="11" t="inlineStr">
-        <is>
-          <t>回答（基本形）：</t>
-        </is>
-      </c>
+    <row r="149" ht="6" customHeight="1" s="6">
+      <c r="A149" s="8" t="n"/>
       <c r="B149" s="27" t="n"/>
       <c r="C149" s="27" t="n"/>
       <c r="D149" s="27" t="n"/>
@@ -3454,26 +3453,27 @@
       <c r="I149" s="27" t="n"/>
       <c r="J149" s="57" t="n"/>
     </row>
-    <row r="150" ht="20" customHeight="1" s="6">
-      <c r="A150" s="11" t="inlineStr">
-        <is>
-          <t>回答（短縮形）：</t>
-        </is>
-      </c>
-      <c r="B150" s="27" t="n"/>
-      <c r="C150" s="27" t="n"/>
-      <c r="D150" s="27" t="n"/>
-      <c r="E150" s="27" t="n"/>
-      <c r="F150" s="27" t="n"/>
-      <c r="G150" s="27" t="n"/>
-      <c r="H150" s="27" t="n"/>
-      <c r="I150" s="27" t="n"/>
-      <c r="J150" s="57" t="n"/>
-    </row>
-    <row r="151" ht="20" customHeight="1" s="6">
-      <c r="A151" s="11" t="inlineStr">
-        <is>
-          <t>回答（言いかえ）：</t>
+    <row r="150" ht="18" customHeight="1" s="6">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>8．主語は「リョウタロウ」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B150" s="25" t="n"/>
+      <c r="C150" s="25" t="n"/>
+      <c r="D150" s="25" t="n"/>
+      <c r="E150" s="25" t="n"/>
+      <c r="F150" s="25" t="n"/>
+      <c r="G150" s="25" t="n"/>
+      <c r="H150" s="25" t="n"/>
+      <c r="I150" s="25" t="n"/>
+      <c r="J150" s="56" t="n"/>
+    </row>
+    <row r="151" ht="36" customHeight="1" s="6">
+      <c r="A151" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B151" s="27" t="n"/>
@@ -3486,10 +3486,10 @@
       <c r="I151" s="27" t="n"/>
       <c r="J151" s="57" t="n"/>
     </row>
-    <row r="152" ht="17" customHeight="1" s="6">
+    <row r="152" ht="18" customHeight="1" s="6">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは来週テニスをしますか。</t>
+          <t>リョウタロウは来週テニスをします。</t>
         </is>
       </c>
       <c r="B152" s="27" t="n"/>
@@ -3505,7 +3505,7 @@
     <row r="153" ht="20" customHeight="1" s="6">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>回答（will）：</t>
         </is>
       </c>
       <c r="B153" s="27" t="n"/>
@@ -3521,7 +3521,7 @@
     <row r="154" ht="20" customHeight="1" s="6">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ疑問文）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B154" s="27" t="n"/>
@@ -3534,10 +3534,10 @@
       <c r="I154" s="27" t="n"/>
       <c r="J154" s="57" t="n"/>
     </row>
-    <row r="155" ht="17" customHeight="1" s="6">
+    <row r="155" ht="18" customHeight="1" s="6">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>リョウタロウは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B155" s="27" t="n"/>
@@ -3553,7 +3553,7 @@
     <row r="156" ht="20" customHeight="1" s="6">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>回答（will返答）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B156" s="27" t="n"/>
@@ -3569,7 +3569,7 @@
     <row r="157" ht="20" customHeight="1" s="6">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B157" s="27" t="n"/>
@@ -3582,10 +3582,10 @@
       <c r="I157" s="27" t="n"/>
       <c r="J157" s="57" t="n"/>
     </row>
-    <row r="158" ht="17" customHeight="1" s="6">
+    <row r="158" ht="20" customHeight="1" s="6">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B158" s="27" t="n"/>
@@ -3598,10 +3598,10 @@
       <c r="I158" s="27" t="n"/>
       <c r="J158" s="57" t="n"/>
     </row>
-    <row r="159" ht="20" customHeight="1" s="6">
+    <row r="159" ht="18" customHeight="1" s="6">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>リョウタロウは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B159" s="27" t="n"/>
@@ -3617,7 +3617,7 @@
     <row r="160" ht="20" customHeight="1" s="6">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>回答（will疑問文）：</t>
         </is>
       </c>
       <c r="B160" s="27" t="n"/>
@@ -3633,7 +3633,7 @@
     <row r="161" ht="20" customHeight="1" s="6">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>回答（言いかえ疑問文）：</t>
         </is>
       </c>
       <c r="B161" s="27" t="n"/>
@@ -3646,8 +3646,12 @@
       <c r="I161" s="27" t="n"/>
       <c r="J161" s="57" t="n"/>
     </row>
-    <row r="162" ht="4" customHeight="1" s="6">
-      <c r="A162" s="8" t="n"/>
+    <row r="162" ht="18" customHeight="1" s="6">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t>はい、します。</t>
+        </is>
+      </c>
       <c r="B162" s="27" t="n"/>
       <c r="C162" s="27" t="n"/>
       <c r="D162" s="27" t="n"/>
@@ -3658,27 +3662,26 @@
       <c r="I162" s="27" t="n"/>
       <c r="J162" s="57" t="n"/>
     </row>
-    <row r="163" ht="16" customHeight="1" s="6">
-      <c r="A163" s="9" t="inlineStr">
-        <is>
-          <t>9．主語は「チサコ」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B163" s="25" t="n"/>
-      <c r="C163" s="25" t="n"/>
-      <c r="D163" s="25" t="n"/>
-      <c r="E163" s="25" t="n"/>
-      <c r="F163" s="25" t="n"/>
-      <c r="G163" s="25" t="n"/>
-      <c r="H163" s="25" t="n"/>
-      <c r="I163" s="25" t="n"/>
-      <c r="J163" s="56" t="n"/>
-    </row>
-    <row r="164" ht="34" customHeight="1" s="6">
-      <c r="A164" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="163" ht="20" customHeight="1" s="6">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>回答（will返答）：</t>
+        </is>
+      </c>
+      <c r="B163" s="27" t="n"/>
+      <c r="C163" s="27" t="n"/>
+      <c r="D163" s="27" t="n"/>
+      <c r="E163" s="27" t="n"/>
+      <c r="F163" s="27" t="n"/>
+      <c r="G163" s="27" t="n"/>
+      <c r="H163" s="27" t="n"/>
+      <c r="I163" s="27" t="n"/>
+      <c r="J163" s="57" t="n"/>
+    </row>
+    <row r="164" ht="20" customHeight="1" s="6">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ返答）：</t>
         </is>
       </c>
       <c r="B164" s="27" t="n"/>
@@ -3691,10 +3694,10 @@
       <c r="I164" s="27" t="n"/>
       <c r="J164" s="57" t="n"/>
     </row>
-    <row r="165" ht="17" customHeight="1" s="6">
+    <row r="165" ht="18" customHeight="1" s="6">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>チサコは来週テニスをします。</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B165" s="27" t="n"/>
@@ -3710,7 +3713,7 @@
     <row r="166" ht="20" customHeight="1" s="6">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>回答（will）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B166" s="27" t="n"/>
@@ -3726,7 +3729,7 @@
     <row r="167" ht="20" customHeight="1" s="6">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ）：</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B167" s="27" t="n"/>
@@ -3739,10 +3742,10 @@
       <c r="I167" s="27" t="n"/>
       <c r="J167" s="57" t="n"/>
     </row>
-    <row r="168" ht="17" customHeight="1" s="6">
+    <row r="168" ht="20" customHeight="1" s="6">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>チサコは来週テニスをしません。</t>
+          <t>回答（言いかえ基本形）：</t>
         </is>
       </c>
       <c r="B168" s="27" t="n"/>
@@ -3758,7 +3761,7 @@
     <row r="169" ht="20" customHeight="1" s="6">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（言いかえ短縮形）：</t>
         </is>
       </c>
       <c r="B169" s="27" t="n"/>
@@ -3771,12 +3774,8 @@
       <c r="I169" s="27" t="n"/>
       <c r="J169" s="57" t="n"/>
     </row>
-    <row r="170" ht="20" customHeight="1" s="6">
-      <c r="A170" s="11" t="inlineStr">
-        <is>
-          <t>回答（短縮形）：</t>
-        </is>
-      </c>
+    <row r="170" ht="6" customHeight="1" s="6">
+      <c r="A170" s="8" t="n"/>
       <c r="B170" s="27" t="n"/>
       <c r="C170" s="27" t="n"/>
       <c r="D170" s="27" t="n"/>
@@ -3787,26 +3786,27 @@
       <c r="I170" s="27" t="n"/>
       <c r="J170" s="57" t="n"/>
     </row>
-    <row r="171" ht="20" customHeight="1" s="6">
-      <c r="A171" s="11" t="inlineStr">
-        <is>
-          <t>回答（言いかえ）：</t>
-        </is>
-      </c>
-      <c r="B171" s="27" t="n"/>
-      <c r="C171" s="27" t="n"/>
-      <c r="D171" s="27" t="n"/>
-      <c r="E171" s="27" t="n"/>
-      <c r="F171" s="27" t="n"/>
-      <c r="G171" s="27" t="n"/>
-      <c r="H171" s="27" t="n"/>
-      <c r="I171" s="27" t="n"/>
-      <c r="J171" s="57" t="n"/>
-    </row>
-    <row r="172" ht="17" customHeight="1" s="6">
-      <c r="A172" s="11" t="inlineStr">
-        <is>
-          <t>チサコは来週テニスをしますか。</t>
+    <row r="171" ht="18" customHeight="1" s="6">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>9．主語は「チサコ」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B171" s="25" t="n"/>
+      <c r="C171" s="25" t="n"/>
+      <c r="D171" s="25" t="n"/>
+      <c r="E171" s="25" t="n"/>
+      <c r="F171" s="25" t="n"/>
+      <c r="G171" s="25" t="n"/>
+      <c r="H171" s="25" t="n"/>
+      <c r="I171" s="25" t="n"/>
+      <c r="J171" s="56" t="n"/>
+    </row>
+    <row r="172" ht="36" customHeight="1" s="6">
+      <c r="A172" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B172" s="27" t="n"/>
@@ -3819,10 +3819,10 @@
       <c r="I172" s="27" t="n"/>
       <c r="J172" s="57" t="n"/>
     </row>
-    <row r="173" ht="20" customHeight="1" s="6">
+    <row r="173" ht="18" customHeight="1" s="6">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>回答（will疑問文）：</t>
+          <t>チサコは来週テニスをします。</t>
         </is>
       </c>
       <c r="B173" s="27" t="n"/>
@@ -3838,7 +3838,7 @@
     <row r="174" ht="20" customHeight="1" s="6">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ疑問文）：</t>
+          <t>回答（will）：</t>
         </is>
       </c>
       <c r="B174" s="27" t="n"/>
@@ -3851,10 +3851,10 @@
       <c r="I174" s="27" t="n"/>
       <c r="J174" s="57" t="n"/>
     </row>
-    <row r="175" ht="17" customHeight="1" s="6">
+    <row r="175" ht="20" customHeight="1" s="6">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B175" s="27" t="n"/>
@@ -3867,10 +3867,10 @@
       <c r="I175" s="27" t="n"/>
       <c r="J175" s="57" t="n"/>
     </row>
-    <row r="176" ht="20" customHeight="1" s="6">
+    <row r="176" ht="18" customHeight="1" s="6">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>回答（will返答）：</t>
+          <t>チサコは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B176" s="27" t="n"/>
@@ -3886,7 +3886,7 @@
     <row r="177" ht="20" customHeight="1" s="6">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>回答（基本形）：</t>
         </is>
       </c>
       <c r="B177" s="27" t="n"/>
@@ -3899,10 +3899,10 @@
       <c r="I177" s="27" t="n"/>
       <c r="J177" s="57" t="n"/>
     </row>
-    <row r="178" ht="17" customHeight="1" s="6">
+    <row r="178" ht="20" customHeight="1" s="6">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>回答（短縮形）：</t>
         </is>
       </c>
       <c r="B178" s="27" t="n"/>
@@ -3918,7 +3918,7 @@
     <row r="179" ht="20" customHeight="1" s="6">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>回答（基本形）：</t>
+          <t>回答（言いかえ）：</t>
         </is>
       </c>
       <c r="B179" s="27" t="n"/>
@@ -3931,10 +3931,10 @@
       <c r="I179" s="27" t="n"/>
       <c r="J179" s="57" t="n"/>
     </row>
-    <row r="180" ht="20" customHeight="1" s="6">
+    <row r="180" ht="18" customHeight="1" s="6">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>回答（短縮形）：</t>
+          <t>チサコは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B180" s="27" t="n"/>
@@ -3950,7 +3950,7 @@
     <row r="181" ht="20" customHeight="1" s="6">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>回答（言いかえ返答）：</t>
+          <t>回答（will疑問文）：</t>
         </is>
       </c>
       <c r="B181" s="27" t="n"/>
@@ -3963,8 +3963,12 @@
       <c r="I181" s="27" t="n"/>
       <c r="J181" s="57" t="n"/>
     </row>
-    <row r="182" ht="4" customHeight="1" s="6">
-      <c r="A182" s="8" t="n"/>
+    <row r="182" ht="20" customHeight="1" s="6">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ疑問文）：</t>
+        </is>
+      </c>
       <c r="B182" s="27" t="n"/>
       <c r="C182" s="27" t="n"/>
       <c r="D182" s="27" t="n"/>
@@ -3975,11 +3979,152 @@
       <c r="I182" s="27" t="n"/>
       <c r="J182" s="57" t="n"/>
     </row>
+    <row r="183" ht="18" customHeight="1" s="6">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>はい、します。</t>
+        </is>
+      </c>
+      <c r="B183" s="27" t="n"/>
+      <c r="C183" s="27" t="n"/>
+      <c r="D183" s="27" t="n"/>
+      <c r="E183" s="27" t="n"/>
+      <c r="F183" s="27" t="n"/>
+      <c r="G183" s="27" t="n"/>
+      <c r="H183" s="27" t="n"/>
+      <c r="I183" s="27" t="n"/>
+      <c r="J183" s="57" t="n"/>
+    </row>
+    <row r="184" ht="20" customHeight="1" s="6">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>回答（will返答）：</t>
+        </is>
+      </c>
+      <c r="B184" s="27" t="n"/>
+      <c r="C184" s="27" t="n"/>
+      <c r="D184" s="27" t="n"/>
+      <c r="E184" s="27" t="n"/>
+      <c r="F184" s="27" t="n"/>
+      <c r="G184" s="27" t="n"/>
+      <c r="H184" s="27" t="n"/>
+      <c r="I184" s="27" t="n"/>
+      <c r="J184" s="57" t="n"/>
+    </row>
+    <row r="185" ht="20" customHeight="1" s="6">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ返答）：</t>
+        </is>
+      </c>
+      <c r="B185" s="27" t="n"/>
+      <c r="C185" s="27" t="n"/>
+      <c r="D185" s="27" t="n"/>
+      <c r="E185" s="27" t="n"/>
+      <c r="F185" s="27" t="n"/>
+      <c r="G185" s="27" t="n"/>
+      <c r="H185" s="27" t="n"/>
+      <c r="I185" s="27" t="n"/>
+      <c r="J185" s="57" t="n"/>
+    </row>
+    <row r="186" ht="18" customHeight="1" s="6">
+      <c r="A186" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、しません。</t>
+        </is>
+      </c>
+      <c r="B186" s="27" t="n"/>
+      <c r="C186" s="27" t="n"/>
+      <c r="D186" s="27" t="n"/>
+      <c r="E186" s="27" t="n"/>
+      <c r="F186" s="27" t="n"/>
+      <c r="G186" s="27" t="n"/>
+      <c r="H186" s="27" t="n"/>
+      <c r="I186" s="27" t="n"/>
+      <c r="J186" s="57" t="n"/>
+    </row>
+    <row r="187" ht="20" customHeight="1" s="6">
+      <c r="A187" s="11" t="inlineStr">
+        <is>
+          <t>回答（基本形）：</t>
+        </is>
+      </c>
+      <c r="B187" s="27" t="n"/>
+      <c r="C187" s="27" t="n"/>
+      <c r="D187" s="27" t="n"/>
+      <c r="E187" s="27" t="n"/>
+      <c r="F187" s="27" t="n"/>
+      <c r="G187" s="27" t="n"/>
+      <c r="H187" s="27" t="n"/>
+      <c r="I187" s="27" t="n"/>
+      <c r="J187" s="57" t="n"/>
+    </row>
+    <row r="188" ht="20" customHeight="1" s="6">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t>回答（短縮形）：</t>
+        </is>
+      </c>
+      <c r="B188" s="27" t="n"/>
+      <c r="C188" s="27" t="n"/>
+      <c r="D188" s="27" t="n"/>
+      <c r="E188" s="27" t="n"/>
+      <c r="F188" s="27" t="n"/>
+      <c r="G188" s="27" t="n"/>
+      <c r="H188" s="27" t="n"/>
+      <c r="I188" s="27" t="n"/>
+      <c r="J188" s="57" t="n"/>
+    </row>
+    <row r="189" ht="20" customHeight="1" s="6">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ基本形）：</t>
+        </is>
+      </c>
+      <c r="B189" s="27" t="n"/>
+      <c r="C189" s="27" t="n"/>
+      <c r="D189" s="27" t="n"/>
+      <c r="E189" s="27" t="n"/>
+      <c r="F189" s="27" t="n"/>
+      <c r="G189" s="27" t="n"/>
+      <c r="H189" s="27" t="n"/>
+      <c r="I189" s="27" t="n"/>
+      <c r="J189" s="57" t="n"/>
+    </row>
+    <row r="190" ht="20" customHeight="1" s="6">
+      <c r="A190" s="11" t="inlineStr">
+        <is>
+          <t>回答（言いかえ短縮形）：</t>
+        </is>
+      </c>
+      <c r="B190" s="27" t="n"/>
+      <c r="C190" s="27" t="n"/>
+      <c r="D190" s="27" t="n"/>
+      <c r="E190" s="27" t="n"/>
+      <c r="F190" s="27" t="n"/>
+      <c r="G190" s="27" t="n"/>
+      <c r="H190" s="27" t="n"/>
+      <c r="I190" s="27" t="n"/>
+      <c r="J190" s="57" t="n"/>
+    </row>
+    <row r="191" ht="6" customHeight="1" s="6">
+      <c r="A191" s="8" t="n"/>
+      <c r="B191" s="27" t="n"/>
+      <c r="C191" s="27" t="n"/>
+      <c r="D191" s="27" t="n"/>
+      <c r="E191" s="27" t="n"/>
+      <c r="F191" s="27" t="n"/>
+      <c r="G191" s="27" t="n"/>
+      <c r="H191" s="27" t="n"/>
+      <c r="I191" s="27" t="n"/>
+      <c r="J191" s="57" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="182">
+  <mergeCells count="191">
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A181:J181"/>
     <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A184:J184"/>
     <mergeCell ref="A156:J156"/>
     <mergeCell ref="A43:J43"/>
     <mergeCell ref="A171:J171"/>
@@ -3991,8 +4136,8 @@
     <mergeCell ref="A93:J93"/>
     <mergeCell ref="A173:J173"/>
     <mergeCell ref="A130:J130"/>
+    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A77:J77"/>
-    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A148:J148"/>
     <mergeCell ref="A157:J157"/>
@@ -4004,6 +4149,7 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A69:J69"/>
     <mergeCell ref="A174:J174"/>
+    <mergeCell ref="A183:J183"/>
     <mergeCell ref="A66:J66"/>
     <mergeCell ref="A118:J118"/>
     <mergeCell ref="A75:J75"/>
@@ -4023,20 +4169,21 @@
     <mergeCell ref="A106:J106"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A96:J96"/>
     <mergeCell ref="A81:J81"/>
-    <mergeCell ref="A96:J96"/>
     <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A121:J121"/>
     <mergeCell ref="A147:J147"/>
-    <mergeCell ref="A121:J121"/>
     <mergeCell ref="A161:J161"/>
+    <mergeCell ref="A170:J170"/>
     <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A170:J170"/>
     <mergeCell ref="A44:J44"/>
     <mergeCell ref="A31:J31"/>
     <mergeCell ref="A58:J58"/>
     <mergeCell ref="A40:J40"/>
     <mergeCell ref="A67:J67"/>
     <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A186:J186"/>
     <mergeCell ref="A73:J73"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A82:J82"/>
@@ -4048,11 +4195,13 @@
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A172:J172"/>
     <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A187:J187"/>
     <mergeCell ref="A25:J25"/>
     <mergeCell ref="A108:J108"/>
     <mergeCell ref="A84:J84"/>
     <mergeCell ref="A149:J149"/>
     <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A189:J189"/>
     <mergeCell ref="A158:J158"/>
     <mergeCell ref="A50:J50"/>
     <mergeCell ref="A2:J2"/>
@@ -4071,12 +4220,13 @@
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A125:J125"/>
     <mergeCell ref="A72:J72"/>
-    <mergeCell ref="A134:J134"/>
+    <mergeCell ref="A190:J190"/>
     <mergeCell ref="A28:J28"/>
     <mergeCell ref="A112:J112"/>
+    <mergeCell ref="A134:J134"/>
     <mergeCell ref="A152:J152"/>
+    <mergeCell ref="A167:J167"/>
     <mergeCell ref="A127:J127"/>
-    <mergeCell ref="A167:J167"/>
     <mergeCell ref="A176:J176"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A114:J114"/>
@@ -4084,9 +4234,10 @@
     <mergeCell ref="A182:J182"/>
     <mergeCell ref="A64:J64"/>
     <mergeCell ref="A98:J98"/>
-    <mergeCell ref="A169:J169"/>
+    <mergeCell ref="A191:J191"/>
     <mergeCell ref="A51:J51"/>
     <mergeCell ref="A107:J107"/>
+    <mergeCell ref="A169:J169"/>
     <mergeCell ref="A178:J178"/>
     <mergeCell ref="A79:J79"/>
     <mergeCell ref="A61:J61"/>
@@ -4114,14 +4265,15 @@
     <mergeCell ref="A116:J116"/>
     <mergeCell ref="A85:J85"/>
     <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A188:J188"/>
     <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A100:J100"/>
     <mergeCell ref="A131:J131"/>
     <mergeCell ref="A126:J126"/>
-    <mergeCell ref="A100:J100"/>
+    <mergeCell ref="A109:J109"/>
+    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A35:J35"/>
     <mergeCell ref="A140:J140"/>
-    <mergeCell ref="A53:J53"/>
-    <mergeCell ref="A109:J109"/>
-    <mergeCell ref="A35:J35"/>
     <mergeCell ref="A180:J180"/>
     <mergeCell ref="A129:J129"/>
     <mergeCell ref="A10:J10"/>
@@ -4159,15 +4311,16 @@
     <mergeCell ref="A113:J113"/>
     <mergeCell ref="A179:J179"/>
     <mergeCell ref="A71:J71"/>
+    <mergeCell ref="A185:J185"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1" verticalDpi="0"/>
   <rowBreaks count="4" manualBreakCount="4">
-    <brk id="42" min="0" max="16383" man="1"/>
-    <brk id="82" min="0" max="16383" man="1"/>
-    <brk id="122" min="0" max="16383" man="1"/>
-    <brk id="162" min="0" max="16383" man="1"/>
+    <brk id="44" min="0" max="16383" man="1"/>
+    <brk id="86" min="0" max="16383" man="1"/>
+    <brk id="128" min="0" max="16383" man="1"/>
+    <brk id="170" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -4178,7 +4331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J182"/>
+  <dimension ref="A1:J191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="13" customWidth="1" style="6" min="1" max="1"/>
@@ -4209,7 +4362,7 @@
       <c r="I1" s="25" t="n"/>
       <c r="J1" s="56" t="n"/>
     </row>
-    <row r="2" ht="4" customHeight="1" s="6">
+    <row r="2" ht="6" customHeight="1" s="6">
       <c r="A2" s="8" t="n"/>
       <c r="B2" s="27" t="n"/>
       <c r="C2" s="27" t="n"/>
@@ -4221,7 +4374,7 @@
       <c r="I2" s="27" t="n"/>
       <c r="J2" s="57" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1" s="6">
+    <row r="3" ht="18" customHeight="1" s="6">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>1．主語は「私」で書いてください。</t>
@@ -4237,7 +4390,7 @@
       <c r="I3" s="25" t="n"/>
       <c r="J3" s="56" t="n"/>
     </row>
-    <row r="4" ht="40" customHeight="1" s="6">
+    <row r="4" ht="42" customHeight="1" s="6">
       <c r="A4" s="55" t="inlineStr">
         <is>
           <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
@@ -4255,7 +4408,7 @@
       <c r="I4" s="27" t="n"/>
       <c r="J4" s="57" t="n"/>
     </row>
-    <row r="5" ht="17" customHeight="1" s="6">
+    <row r="5" ht="18" customHeight="1" s="6">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>私は来週テニスをします。</t>
@@ -4303,7 +4456,7 @@
       <c r="I7" s="27" t="n"/>
       <c r="J7" s="57" t="n"/>
     </row>
-    <row r="8" ht="17" customHeight="1" s="6">
+    <row r="8" ht="18" customHeight="1" s="6">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>私は来週テニスをしません。</t>
@@ -4367,7 +4520,7 @@
       <c r="I11" s="27" t="n"/>
       <c r="J11" s="57" t="n"/>
     </row>
-    <row r="12" ht="17" customHeight="1" s="6">
+    <row r="12" ht="18" customHeight="1" s="6">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>私は来週テニスをしますか。</t>
@@ -4415,7 +4568,7 @@
       <c r="I14" s="27" t="n"/>
       <c r="J14" s="57" t="n"/>
     </row>
-    <row r="15" ht="17" customHeight="1" s="6">
+    <row r="15" ht="18" customHeight="1" s="6">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>はい、します。</t>
@@ -4463,7 +4616,7 @@
       <c r="I17" s="27" t="n"/>
       <c r="J17" s="57" t="n"/>
     </row>
-    <row r="18" ht="17" customHeight="1" s="6">
+    <row r="18" ht="18" customHeight="1" s="6">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>いいえ、しません。</t>
@@ -4514,7 +4667,7 @@
     <row r="21" ht="20" customHeight="1" s="6">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：No, you are not.</t>
+          <t>正解（言いかえ基本形）：No, you are not.</t>
         </is>
       </c>
       <c r="B21" s="27" t="n"/>
@@ -4527,8 +4680,12 @@
       <c r="I21" s="27" t="n"/>
       <c r="J21" s="57" t="n"/>
     </row>
-    <row r="22" ht="4" customHeight="1" s="6">
-      <c r="A22" s="8" t="n"/>
+    <row r="22" ht="20" customHeight="1" s="6">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ短縮形）：No, you aren't.</t>
+        </is>
+      </c>
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="27" t="n"/>
       <c r="D22" s="27" t="n"/>
@@ -4539,43 +4696,39 @@
       <c r="I22" s="27" t="n"/>
       <c r="J22" s="57" t="n"/>
     </row>
-    <row r="23" ht="16" customHeight="1" s="6">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="23" ht="6" customHeight="1" s="6">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="27" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="27" t="n"/>
+      <c r="G23" s="27" t="n"/>
+      <c r="H23" s="27" t="n"/>
+      <c r="I23" s="27" t="n"/>
+      <c r="J23" s="57" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="6">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>2．主語は「あなた」で書いてください。</t>
         </is>
       </c>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="25" t="n"/>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="25" t="n"/>
-      <c r="G23" s="25" t="n"/>
-      <c r="H23" s="25" t="n"/>
-      <c r="I23" s="25" t="n"/>
-      <c r="J23" s="56" t="n"/>
-    </row>
-    <row r="24" ht="34" customHeight="1" s="6">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
+      <c r="J24" s="56" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1" s="6">
+      <c r="A25" s="55" t="inlineStr">
         <is>
           <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
 ※否定の短縮形は will not → won't を使います。</t>
-        </is>
-      </c>
-      <c r="B24" s="27" t="n"/>
-      <c r="C24" s="27" t="n"/>
-      <c r="D24" s="27" t="n"/>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="27" t="n"/>
-      <c r="H24" s="27" t="n"/>
-      <c r="I24" s="27" t="n"/>
-      <c r="J24" s="57" t="n"/>
-    </row>
-    <row r="25" ht="17" customHeight="1" s="6">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>あなたは来週テニスをします。</t>
         </is>
       </c>
       <c r="B25" s="27" t="n"/>
@@ -4588,10 +4741,10 @@
       <c r="I25" s="27" t="n"/>
       <c r="J25" s="57" t="n"/>
     </row>
-    <row r="26" ht="20" customHeight="1" s="6">
+    <row r="26" ht="18" customHeight="1" s="6">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>正解（will）：You will play tennis next week.</t>
+          <t>あなたは来週テニスをします。</t>
         </is>
       </c>
       <c r="B26" s="27" t="n"/>
@@ -4607,7 +4760,7 @@
     <row r="27" ht="20" customHeight="1" s="6">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：You are going to play tennis next week.</t>
+          <t>正解（will）：You will play tennis next week.</t>
         </is>
       </c>
       <c r="B27" s="27" t="n"/>
@@ -4620,10 +4773,10 @@
       <c r="I27" s="27" t="n"/>
       <c r="J27" s="57" t="n"/>
     </row>
-    <row r="28" ht="17" customHeight="1" s="6">
+    <row r="28" ht="20" customHeight="1" s="6">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>あなたは来週テニスをしません。</t>
+          <t>正解（言いかえ）：You are going to play tennis next week.</t>
         </is>
       </c>
       <c r="B28" s="27" t="n"/>
@@ -4636,10 +4789,10 @@
       <c r="I28" s="27" t="n"/>
       <c r="J28" s="57" t="n"/>
     </row>
-    <row r="29" ht="20" customHeight="1" s="6">
+    <row r="29" ht="18" customHeight="1" s="6">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：You will not play tennis next week.</t>
+          <t>あなたは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B29" s="27" t="n"/>
@@ -4655,7 +4808,7 @@
     <row r="30" ht="20" customHeight="1" s="6">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：You won't play tennis next week.</t>
+          <t>正解（基本形）：You will not play tennis next week.</t>
         </is>
       </c>
       <c r="B30" s="27" t="n"/>
@@ -4671,7 +4824,7 @@
     <row r="31" ht="20" customHeight="1" s="6">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：You are not going to play tennis next week.</t>
+          <t>正解（短縮形）：You won't play tennis next week.</t>
         </is>
       </c>
       <c r="B31" s="27" t="n"/>
@@ -4684,10 +4837,10 @@
       <c r="I31" s="27" t="n"/>
       <c r="J31" s="57" t="n"/>
     </row>
-    <row r="32" ht="17" customHeight="1" s="6">
+    <row r="32" ht="20" customHeight="1" s="6">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>あなたは来週テニスをしますか。</t>
+          <t>正解（言いかえ）：You are not going to play tennis next week.</t>
         </is>
       </c>
       <c r="B32" s="27" t="n"/>
@@ -4700,10 +4853,10 @@
       <c r="I32" s="27" t="n"/>
       <c r="J32" s="57" t="n"/>
     </row>
-    <row r="33" ht="20" customHeight="1" s="6">
+    <row r="33" ht="18" customHeight="1" s="6">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will you play tennis next week?</t>
+          <t>あなたは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B33" s="27" t="n"/>
@@ -4719,7 +4872,7 @@
     <row r="34" ht="20" customHeight="1" s="6">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ疑問文）：Are you going to play tennis next week?</t>
+          <t>正解（will疑問文）：Will you play tennis next week?</t>
         </is>
       </c>
       <c r="B34" s="27" t="n"/>
@@ -4732,10 +4885,10 @@
       <c r="I34" s="27" t="n"/>
       <c r="J34" s="57" t="n"/>
     </row>
-    <row r="35" ht="17" customHeight="1" s="6">
+    <row r="35" ht="20" customHeight="1" s="6">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>正解（言いかえ疑問文）：Are you going to play tennis next week?</t>
         </is>
       </c>
       <c r="B35" s="27" t="n"/>
@@ -4748,10 +4901,10 @@
       <c r="I35" s="27" t="n"/>
       <c r="J35" s="57" t="n"/>
     </row>
-    <row r="36" ht="20" customHeight="1" s="6">
+    <row r="36" ht="18" customHeight="1" s="6">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>正解（will返答）：Yes, I will.</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B36" s="27" t="n"/>
@@ -4767,7 +4920,7 @@
     <row r="37" ht="20" customHeight="1" s="6">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：Yes, I am.</t>
+          <t>正解（will返答）：Yes, I will.</t>
         </is>
       </c>
       <c r="B37" s="27" t="n"/>
@@ -4780,10 +4933,10 @@
       <c r="I37" s="27" t="n"/>
       <c r="J37" s="57" t="n"/>
     </row>
-    <row r="38" ht="17" customHeight="1" s="6">
+    <row r="38" ht="20" customHeight="1" s="6">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>正解（言いかえ返答）：Yes, I am.</t>
         </is>
       </c>
       <c r="B38" s="27" t="n"/>
@@ -4796,10 +4949,10 @@
       <c r="I38" s="27" t="n"/>
       <c r="J38" s="57" t="n"/>
     </row>
-    <row r="39" ht="20" customHeight="1" s="6">
+    <row r="39" ht="18" customHeight="1" s="6">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, I will not.</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B39" s="27" t="n"/>
@@ -4815,7 +4968,7 @@
     <row r="40" ht="20" customHeight="1" s="6">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, I won't.</t>
+          <t>正解（基本形）：No, I will not.</t>
         </is>
       </c>
       <c r="B40" s="27" t="n"/>
@@ -4831,7 +4984,7 @@
     <row r="41" ht="20" customHeight="1" s="6">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：No, I am not.</t>
+          <t>正解（短縮形）：No, I won't.</t>
         </is>
       </c>
       <c r="B41" s="27" t="n"/>
@@ -4844,8 +4997,12 @@
       <c r="I41" s="27" t="n"/>
       <c r="J41" s="57" t="n"/>
     </row>
-    <row r="42" ht="4" customHeight="1" s="6">
-      <c r="A42" s="8" t="n"/>
+    <row r="42" ht="20" customHeight="1" s="6">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ基本形）：No, I am not.</t>
+        </is>
+      </c>
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="27" t="n"/>
       <c r="D42" s="27" t="n"/>
@@ -4856,29 +5013,24 @@
       <c r="I42" s="27" t="n"/>
       <c r="J42" s="57" t="n"/>
     </row>
-    <row r="43" ht="16" customHeight="1" s="6">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>3．主語は「彼」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="n"/>
-      <c r="C43" s="25" t="n"/>
-      <c r="D43" s="25" t="n"/>
-      <c r="E43" s="25" t="n"/>
-      <c r="F43" s="25" t="n"/>
-      <c r="G43" s="25" t="n"/>
-      <c r="H43" s="25" t="n"/>
-      <c r="I43" s="25" t="n"/>
-      <c r="J43" s="56" t="n"/>
-    </row>
-    <row r="44" ht="34" customHeight="1" s="6">
-      <c r="A44" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
-        </is>
-      </c>
+    <row r="43" ht="20" customHeight="1" s="6">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ短縮形）：No, I'm not.</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="n"/>
+      <c r="C43" s="27" t="n"/>
+      <c r="D43" s="27" t="n"/>
+      <c r="E43" s="27" t="n"/>
+      <c r="F43" s="27" t="n"/>
+      <c r="G43" s="27" t="n"/>
+      <c r="H43" s="27" t="n"/>
+      <c r="I43" s="27" t="n"/>
+      <c r="J43" s="57" t="n"/>
+    </row>
+    <row r="44" ht="6" customHeight="1" s="6">
+      <c r="A44" s="8" t="n"/>
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="27" t="n"/>
       <c r="D44" s="27" t="n"/>
@@ -4889,26 +5041,27 @@
       <c r="I44" s="27" t="n"/>
       <c r="J44" s="57" t="n"/>
     </row>
-    <row r="45" ht="17" customHeight="1" s="6">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>彼は来週テニスをします。</t>
-        </is>
-      </c>
-      <c r="B45" s="27" t="n"/>
-      <c r="C45" s="27" t="n"/>
-      <c r="D45" s="27" t="n"/>
-      <c r="E45" s="27" t="n"/>
-      <c r="F45" s="27" t="n"/>
-      <c r="G45" s="27" t="n"/>
-      <c r="H45" s="27" t="n"/>
-      <c r="I45" s="27" t="n"/>
-      <c r="J45" s="57" t="n"/>
-    </row>
-    <row r="46" ht="20" customHeight="1" s="6">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>正解（will）：He will play tennis next week.</t>
+    <row r="45" ht="18" customHeight="1" s="6">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>3．主語は「彼」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="n"/>
+      <c r="C45" s="25" t="n"/>
+      <c r="D45" s="25" t="n"/>
+      <c r="E45" s="25" t="n"/>
+      <c r="F45" s="25" t="n"/>
+      <c r="G45" s="25" t="n"/>
+      <c r="H45" s="25" t="n"/>
+      <c r="I45" s="25" t="n"/>
+      <c r="J45" s="56" t="n"/>
+    </row>
+    <row r="46" ht="36" customHeight="1" s="6">
+      <c r="A46" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B46" s="27" t="n"/>
@@ -4921,10 +5074,10 @@
       <c r="I46" s="27" t="n"/>
       <c r="J46" s="57" t="n"/>
     </row>
-    <row r="47" ht="20" customHeight="1" s="6">
+    <row r="47" ht="18" customHeight="1" s="6">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：He is going to play tennis next week.</t>
+          <t>彼は来週テニスをします。</t>
         </is>
       </c>
       <c r="B47" s="27" t="n"/>
@@ -4937,10 +5090,10 @@
       <c r="I47" s="27" t="n"/>
       <c r="J47" s="57" t="n"/>
     </row>
-    <row r="48" ht="17" customHeight="1" s="6">
+    <row r="48" ht="20" customHeight="1" s="6">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>彼は来週テニスをしません。</t>
+          <t>正解（will）：He will play tennis next week.</t>
         </is>
       </c>
       <c r="B48" s="27" t="n"/>
@@ -4956,7 +5109,7 @@
     <row r="49" ht="20" customHeight="1" s="6">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：He will not play tennis next week.</t>
+          <t>正解（言いかえ）：He is going to play tennis next week.</t>
         </is>
       </c>
       <c r="B49" s="27" t="n"/>
@@ -4969,10 +5122,10 @@
       <c r="I49" s="27" t="n"/>
       <c r="J49" s="57" t="n"/>
     </row>
-    <row r="50" ht="20" customHeight="1" s="6">
+    <row r="50" ht="18" customHeight="1" s="6">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：He won't play tennis next week.</t>
+          <t>彼は来週テニスをしません。</t>
         </is>
       </c>
       <c r="B50" s="27" t="n"/>
@@ -4988,7 +5141,7 @@
     <row r="51" ht="20" customHeight="1" s="6">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：He is not going to play tennis next week.</t>
+          <t>正解（基本形）：He will not play tennis next week.</t>
         </is>
       </c>
       <c r="B51" s="27" t="n"/>
@@ -5001,10 +5154,10 @@
       <c r="I51" s="27" t="n"/>
       <c r="J51" s="57" t="n"/>
     </row>
-    <row r="52" ht="17" customHeight="1" s="6">
+    <row r="52" ht="20" customHeight="1" s="6">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>彼は来週テニスをしますか。</t>
+          <t>正解（短縮形）：He won't play tennis next week.</t>
         </is>
       </c>
       <c r="B52" s="27" t="n"/>
@@ -5020,7 +5173,7 @@
     <row r="53" ht="20" customHeight="1" s="6">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will he play tennis next week?</t>
+          <t>正解（言いかえ）：He is not going to play tennis next week.</t>
         </is>
       </c>
       <c r="B53" s="27" t="n"/>
@@ -5033,10 +5186,10 @@
       <c r="I53" s="27" t="n"/>
       <c r="J53" s="57" t="n"/>
     </row>
-    <row r="54" ht="20" customHeight="1" s="6">
+    <row r="54" ht="18" customHeight="1" s="6">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ疑問文）：Is he going to play tennis next week?</t>
+          <t>彼は来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B54" s="27" t="n"/>
@@ -5049,10 +5202,10 @@
       <c r="I54" s="27" t="n"/>
       <c r="J54" s="57" t="n"/>
     </row>
-    <row r="55" ht="17" customHeight="1" s="6">
+    <row r="55" ht="20" customHeight="1" s="6">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>正解（will疑問文）：Will he play tennis next week?</t>
         </is>
       </c>
       <c r="B55" s="27" t="n"/>
@@ -5068,7 +5221,7 @@
     <row r="56" ht="20" customHeight="1" s="6">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>正解（will返答）：Yes, he will.</t>
+          <t>正解（言いかえ疑問文）：Is he going to play tennis next week?</t>
         </is>
       </c>
       <c r="B56" s="27" t="n"/>
@@ -5081,10 +5234,10 @@
       <c r="I56" s="27" t="n"/>
       <c r="J56" s="57" t="n"/>
     </row>
-    <row r="57" ht="20" customHeight="1" s="6">
+    <row r="57" ht="18" customHeight="1" s="6">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：Yes, he is.</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B57" s="27" t="n"/>
@@ -5097,10 +5250,10 @@
       <c r="I57" s="27" t="n"/>
       <c r="J57" s="57" t="n"/>
     </row>
-    <row r="58" ht="17" customHeight="1" s="6">
+    <row r="58" ht="20" customHeight="1" s="6">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>正解（will返答）：Yes, he will.</t>
         </is>
       </c>
       <c r="B58" s="27" t="n"/>
@@ -5116,7 +5269,7 @@
     <row r="59" ht="20" customHeight="1" s="6">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, he will not.</t>
+          <t>正解（言いかえ返答）：Yes, he is.</t>
         </is>
       </c>
       <c r="B59" s="27" t="n"/>
@@ -5129,10 +5282,10 @@
       <c r="I59" s="27" t="n"/>
       <c r="J59" s="57" t="n"/>
     </row>
-    <row r="60" ht="20" customHeight="1" s="6">
+    <row r="60" ht="18" customHeight="1" s="6">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, he won't.</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B60" s="27" t="n"/>
@@ -5148,7 +5301,7 @@
     <row r="61" ht="20" customHeight="1" s="6">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：No, he is not.</t>
+          <t>正解（基本形）：No, he will not.</t>
         </is>
       </c>
       <c r="B61" s="27" t="n"/>
@@ -5161,8 +5314,12 @@
       <c r="I61" s="27" t="n"/>
       <c r="J61" s="57" t="n"/>
     </row>
-    <row r="62" ht="4" customHeight="1" s="6">
-      <c r="A62" s="8" t="n"/>
+    <row r="62" ht="20" customHeight="1" s="6">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：No, he won't.</t>
+        </is>
+      </c>
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="27" t="n"/>
       <c r="D62" s="27" t="n"/>
@@ -5173,27 +5330,26 @@
       <c r="I62" s="27" t="n"/>
       <c r="J62" s="57" t="n"/>
     </row>
-    <row r="63" ht="16" customHeight="1" s="6">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>4．主語は「彼女」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B63" s="25" t="n"/>
-      <c r="C63" s="25" t="n"/>
-      <c r="D63" s="25" t="n"/>
-      <c r="E63" s="25" t="n"/>
-      <c r="F63" s="25" t="n"/>
-      <c r="G63" s="25" t="n"/>
-      <c r="H63" s="25" t="n"/>
-      <c r="I63" s="25" t="n"/>
-      <c r="J63" s="56" t="n"/>
-    </row>
-    <row r="64" ht="34" customHeight="1" s="6">
-      <c r="A64" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="63" ht="20" customHeight="1" s="6">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ基本形）：No, he is not.</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="n"/>
+      <c r="C63" s="27" t="n"/>
+      <c r="D63" s="27" t="n"/>
+      <c r="E63" s="27" t="n"/>
+      <c r="F63" s="27" t="n"/>
+      <c r="G63" s="27" t="n"/>
+      <c r="H63" s="27" t="n"/>
+      <c r="I63" s="27" t="n"/>
+      <c r="J63" s="57" t="n"/>
+    </row>
+    <row r="64" ht="20" customHeight="1" s="6">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ短縮形）：No, he isn't.</t>
         </is>
       </c>
       <c r="B64" s="27" t="n"/>
@@ -5206,12 +5362,8 @@
       <c r="I64" s="27" t="n"/>
       <c r="J64" s="57" t="n"/>
     </row>
-    <row r="65" ht="17" customHeight="1" s="6">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>彼女は来週テニスをします。</t>
-        </is>
-      </c>
+    <row r="65" ht="6" customHeight="1" s="6">
+      <c r="A65" s="8" t="n"/>
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="27" t="n"/>
       <c r="D65" s="27" t="n"/>
@@ -5222,26 +5374,27 @@
       <c r="I65" s="27" t="n"/>
       <c r="J65" s="57" t="n"/>
     </row>
-    <row r="66" ht="20" customHeight="1" s="6">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>正解（will）：She will play tennis next week.</t>
-        </is>
-      </c>
-      <c r="B66" s="27" t="n"/>
-      <c r="C66" s="27" t="n"/>
-      <c r="D66" s="27" t="n"/>
-      <c r="E66" s="27" t="n"/>
-      <c r="F66" s="27" t="n"/>
-      <c r="G66" s="27" t="n"/>
-      <c r="H66" s="27" t="n"/>
-      <c r="I66" s="27" t="n"/>
-      <c r="J66" s="57" t="n"/>
-    </row>
-    <row r="67" ht="20" customHeight="1" s="6">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>正解（言いかえ）：She is going to play tennis next week.</t>
+    <row r="66" ht="18" customHeight="1" s="6">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>4．主語は「彼女」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="n"/>
+      <c r="C66" s="25" t="n"/>
+      <c r="D66" s="25" t="n"/>
+      <c r="E66" s="25" t="n"/>
+      <c r="F66" s="25" t="n"/>
+      <c r="G66" s="25" t="n"/>
+      <c r="H66" s="25" t="n"/>
+      <c r="I66" s="25" t="n"/>
+      <c r="J66" s="56" t="n"/>
+    </row>
+    <row r="67" ht="36" customHeight="1" s="6">
+      <c r="A67" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B67" s="27" t="n"/>
@@ -5254,10 +5407,10 @@
       <c r="I67" s="27" t="n"/>
       <c r="J67" s="57" t="n"/>
     </row>
-    <row r="68" ht="17" customHeight="1" s="6">
+    <row r="68" ht="18" customHeight="1" s="6">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>彼女は来週テニスをしません。</t>
+          <t>彼女は来週テニスをします。</t>
         </is>
       </c>
       <c r="B68" s="27" t="n"/>
@@ -5273,7 +5426,7 @@
     <row r="69" ht="20" customHeight="1" s="6">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：She will not play tennis next week.</t>
+          <t>正解（will）：She will play tennis next week.</t>
         </is>
       </c>
       <c r="B69" s="27" t="n"/>
@@ -5289,7 +5442,7 @@
     <row r="70" ht="20" customHeight="1" s="6">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：She won't play tennis next week.</t>
+          <t>正解（言いかえ）：She is going to play tennis next week.</t>
         </is>
       </c>
       <c r="B70" s="27" t="n"/>
@@ -5302,10 +5455,10 @@
       <c r="I70" s="27" t="n"/>
       <c r="J70" s="57" t="n"/>
     </row>
-    <row r="71" ht="20" customHeight="1" s="6">
+    <row r="71" ht="18" customHeight="1" s="6">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：She is not going to play tennis next week.</t>
+          <t>彼女は来週テニスをしません。</t>
         </is>
       </c>
       <c r="B71" s="27" t="n"/>
@@ -5318,10 +5471,10 @@
       <c r="I71" s="27" t="n"/>
       <c r="J71" s="57" t="n"/>
     </row>
-    <row r="72" ht="17" customHeight="1" s="6">
+    <row r="72" ht="20" customHeight="1" s="6">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>彼女は来週テニスをしますか。</t>
+          <t>正解（基本形）：She will not play tennis next week.</t>
         </is>
       </c>
       <c r="B72" s="27" t="n"/>
@@ -5337,7 +5490,7 @@
     <row r="73" ht="20" customHeight="1" s="6">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will she play tennis next week?</t>
+          <t>正解（短縮形）：She won't play tennis next week.</t>
         </is>
       </c>
       <c r="B73" s="27" t="n"/>
@@ -5353,7 +5506,7 @@
     <row r="74" ht="20" customHeight="1" s="6">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ疑問文）：Is she going to play tennis next week?</t>
+          <t>正解（言いかえ）：She is not going to play tennis next week.</t>
         </is>
       </c>
       <c r="B74" s="27" t="n"/>
@@ -5366,10 +5519,10 @@
       <c r="I74" s="27" t="n"/>
       <c r="J74" s="57" t="n"/>
     </row>
-    <row r="75" ht="17" customHeight="1" s="6">
+    <row r="75" ht="18" customHeight="1" s="6">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>彼女は来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B75" s="27" t="n"/>
@@ -5385,7 +5538,7 @@
     <row r="76" ht="20" customHeight="1" s="6">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>正解（will返答）：Yes, she will.</t>
+          <t>正解（will疑問文）：Will she play tennis next week?</t>
         </is>
       </c>
       <c r="B76" s="27" t="n"/>
@@ -5401,7 +5554,7 @@
     <row r="77" ht="20" customHeight="1" s="6">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：Yes, she is.</t>
+          <t>正解（言いかえ疑問文）：Is she going to play tennis next week?</t>
         </is>
       </c>
       <c r="B77" s="27" t="n"/>
@@ -5414,10 +5567,10 @@
       <c r="I77" s="27" t="n"/>
       <c r="J77" s="57" t="n"/>
     </row>
-    <row r="78" ht="17" customHeight="1" s="6">
+    <row r="78" ht="18" customHeight="1" s="6">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B78" s="27" t="n"/>
@@ -5433,7 +5586,7 @@
     <row r="79" ht="20" customHeight="1" s="6">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, she will not.</t>
+          <t>正解（will返答）：Yes, she will.</t>
         </is>
       </c>
       <c r="B79" s="27" t="n"/>
@@ -5449,7 +5602,7 @@
     <row r="80" ht="20" customHeight="1" s="6">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, she won't.</t>
+          <t>正解（言いかえ返答）：Yes, she is.</t>
         </is>
       </c>
       <c r="B80" s="27" t="n"/>
@@ -5462,10 +5615,10 @@
       <c r="I80" s="27" t="n"/>
       <c r="J80" s="57" t="n"/>
     </row>
-    <row r="81" ht="20" customHeight="1" s="6">
+    <row r="81" ht="18" customHeight="1" s="6">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：No, she is not.</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B81" s="27" t="n"/>
@@ -5478,8 +5631,12 @@
       <c r="I81" s="27" t="n"/>
       <c r="J81" s="57" t="n"/>
     </row>
-    <row r="82" ht="4" customHeight="1" s="6">
-      <c r="A82" s="8" t="n"/>
+    <row r="82" ht="20" customHeight="1" s="6">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：No, she will not.</t>
+        </is>
+      </c>
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="27" t="n"/>
       <c r="D82" s="27" t="n"/>
@@ -5490,28 +5647,26 @@
       <c r="I82" s="27" t="n"/>
       <c r="J82" s="57" t="n"/>
     </row>
-    <row r="83" ht="16" customHeight="1" s="6">
-      <c r="A83" s="9" t="inlineStr">
-        <is>
-          <t>5．主語は「私たち」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B83" s="25" t="n"/>
-      <c r="C83" s="25" t="n"/>
-      <c r="D83" s="25" t="n"/>
-      <c r="E83" s="25" t="n"/>
-      <c r="F83" s="25" t="n"/>
-      <c r="G83" s="25" t="n"/>
-      <c r="H83" s="25" t="n"/>
-      <c r="I83" s="25" t="n"/>
-      <c r="J83" s="56" t="n"/>
-    </row>
-    <row r="84" ht="40" customHeight="1" s="6">
-      <c r="A84" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。
-※相手が答える形なので、返答では I / we ではなく you を使います。</t>
+    <row r="83" ht="20" customHeight="1" s="6">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：No, she won't.</t>
+        </is>
+      </c>
+      <c r="B83" s="27" t="n"/>
+      <c r="C83" s="27" t="n"/>
+      <c r="D83" s="27" t="n"/>
+      <c r="E83" s="27" t="n"/>
+      <c r="F83" s="27" t="n"/>
+      <c r="G83" s="27" t="n"/>
+      <c r="H83" s="27" t="n"/>
+      <c r="I83" s="27" t="n"/>
+      <c r="J83" s="57" t="n"/>
+    </row>
+    <row r="84" ht="20" customHeight="1" s="6">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ基本形）：No, she is not.</t>
         </is>
       </c>
       <c r="B84" s="27" t="n"/>
@@ -5524,10 +5679,10 @@
       <c r="I84" s="27" t="n"/>
       <c r="J84" s="57" t="n"/>
     </row>
-    <row r="85" ht="17" customHeight="1" s="6">
+    <row r="85" ht="20" customHeight="1" s="6">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>私たちは来週テニスをします。</t>
+          <t>正解（言いかえ短縮形）：No, she isn't.</t>
         </is>
       </c>
       <c r="B85" s="27" t="n"/>
@@ -5540,12 +5695,8 @@
       <c r="I85" s="27" t="n"/>
       <c r="J85" s="57" t="n"/>
     </row>
-    <row r="86" ht="20" customHeight="1" s="6">
-      <c r="A86" s="11" t="inlineStr">
-        <is>
-          <t>正解（will）：We will play tennis next week.</t>
-        </is>
-      </c>
+    <row r="86" ht="6" customHeight="1" s="6">
+      <c r="A86" s="8" t="n"/>
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="27" t="n"/>
       <c r="D86" s="27" t="n"/>
@@ -5556,26 +5707,28 @@
       <c r="I86" s="27" t="n"/>
       <c r="J86" s="57" t="n"/>
     </row>
-    <row r="87" ht="20" customHeight="1" s="6">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t>正解（言いかえ）：We are going to play tennis next week.</t>
-        </is>
-      </c>
-      <c r="B87" s="27" t="n"/>
-      <c r="C87" s="27" t="n"/>
-      <c r="D87" s="27" t="n"/>
-      <c r="E87" s="27" t="n"/>
-      <c r="F87" s="27" t="n"/>
-      <c r="G87" s="27" t="n"/>
-      <c r="H87" s="27" t="n"/>
-      <c r="I87" s="27" t="n"/>
-      <c r="J87" s="57" t="n"/>
-    </row>
-    <row r="88" ht="17" customHeight="1" s="6">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>私たちは来週テニスをしません。</t>
+    <row r="87" ht="18" customHeight="1" s="6">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>5．主語は「私たち」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B87" s="25" t="n"/>
+      <c r="C87" s="25" t="n"/>
+      <c r="D87" s="25" t="n"/>
+      <c r="E87" s="25" t="n"/>
+      <c r="F87" s="25" t="n"/>
+      <c r="G87" s="25" t="n"/>
+      <c r="H87" s="25" t="n"/>
+      <c r="I87" s="25" t="n"/>
+      <c r="J87" s="56" t="n"/>
+    </row>
+    <row r="88" ht="42" customHeight="1" s="6">
+      <c r="A88" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。
+※相手が答える形なので、返答では I / we ではなく you を使います。</t>
         </is>
       </c>
       <c r="B88" s="27" t="n"/>
@@ -5588,10 +5741,10 @@
       <c r="I88" s="27" t="n"/>
       <c r="J88" s="57" t="n"/>
     </row>
-    <row r="89" ht="20" customHeight="1" s="6">
+    <row r="89" ht="18" customHeight="1" s="6">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：We will not play tennis next week.</t>
+          <t>私たちは来週テニスをします。</t>
         </is>
       </c>
       <c r="B89" s="27" t="n"/>
@@ -5607,7 +5760,7 @@
     <row r="90" ht="20" customHeight="1" s="6">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：We won't play tennis next week.</t>
+          <t>正解（will）：We will play tennis next week.</t>
         </is>
       </c>
       <c r="B90" s="27" t="n"/>
@@ -5623,7 +5776,7 @@
     <row r="91" ht="20" customHeight="1" s="6">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：We are not going to play tennis next week.</t>
+          <t>正解（言いかえ）：We are going to play tennis next week.</t>
         </is>
       </c>
       <c r="B91" s="27" t="n"/>
@@ -5636,10 +5789,10 @@
       <c r="I91" s="27" t="n"/>
       <c r="J91" s="57" t="n"/>
     </row>
-    <row r="92" ht="17" customHeight="1" s="6">
+    <row r="92" ht="18" customHeight="1" s="6">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>私たちは来週テニスをしますか。</t>
+          <t>私たちは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B92" s="27" t="n"/>
@@ -5655,7 +5808,7 @@
     <row r="93" ht="20" customHeight="1" s="6">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will we play tennis next week?</t>
+          <t>正解（基本形）：We will not play tennis next week.</t>
         </is>
       </c>
       <c r="B93" s="27" t="n"/>
@@ -5671,7 +5824,7 @@
     <row r="94" ht="20" customHeight="1" s="6">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ疑問文）：Are we going to play tennis next week?</t>
+          <t>正解（短縮形）：We won't play tennis next week.</t>
         </is>
       </c>
       <c r="B94" s="27" t="n"/>
@@ -5684,10 +5837,10 @@
       <c r="I94" s="27" t="n"/>
       <c r="J94" s="57" t="n"/>
     </row>
-    <row r="95" ht="17" customHeight="1" s="6">
+    <row r="95" ht="20" customHeight="1" s="6">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>正解（言いかえ）：We are not going to play tennis next week.</t>
         </is>
       </c>
       <c r="B95" s="27" t="n"/>
@@ -5700,10 +5853,10 @@
       <c r="I95" s="27" t="n"/>
       <c r="J95" s="57" t="n"/>
     </row>
-    <row r="96" ht="20" customHeight="1" s="6">
+    <row r="96" ht="18" customHeight="1" s="6">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>正解（will返答）：Yes, you will.</t>
+          <t>私たちは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B96" s="27" t="n"/>
@@ -5719,7 +5872,7 @@
     <row r="97" ht="20" customHeight="1" s="6">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：Yes, you are.</t>
+          <t>正解（will疑問文）：Will we play tennis next week?</t>
         </is>
       </c>
       <c r="B97" s="27" t="n"/>
@@ -5732,10 +5885,10 @@
       <c r="I97" s="27" t="n"/>
       <c r="J97" s="57" t="n"/>
     </row>
-    <row r="98" ht="17" customHeight="1" s="6">
+    <row r="98" ht="20" customHeight="1" s="6">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>正解（言いかえ疑問文）：Are we going to play tennis next week?</t>
         </is>
       </c>
       <c r="B98" s="27" t="n"/>
@@ -5748,10 +5901,10 @@
       <c r="I98" s="27" t="n"/>
       <c r="J98" s="57" t="n"/>
     </row>
-    <row r="99" ht="20" customHeight="1" s="6">
+    <row r="99" ht="18" customHeight="1" s="6">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, you will not.</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B99" s="27" t="n"/>
@@ -5767,7 +5920,7 @@
     <row r="100" ht="20" customHeight="1" s="6">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, you won't.</t>
+          <t>正解（will返答）：Yes, you will.</t>
         </is>
       </c>
       <c r="B100" s="27" t="n"/>
@@ -5783,7 +5936,7 @@
     <row r="101" ht="20" customHeight="1" s="6">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：No, you are not.</t>
+          <t>正解（言いかえ返答）：Yes, you are.</t>
         </is>
       </c>
       <c r="B101" s="27" t="n"/>
@@ -5796,8 +5949,12 @@
       <c r="I101" s="27" t="n"/>
       <c r="J101" s="57" t="n"/>
     </row>
-    <row r="102" ht="4" customHeight="1" s="6">
-      <c r="A102" s="8" t="n"/>
+    <row r="102" ht="18" customHeight="1" s="6">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、しません。</t>
+        </is>
+      </c>
       <c r="B102" s="27" t="n"/>
       <c r="C102" s="27" t="n"/>
       <c r="D102" s="27" t="n"/>
@@ -5808,27 +5965,26 @@
       <c r="I102" s="27" t="n"/>
       <c r="J102" s="57" t="n"/>
     </row>
-    <row r="103" ht="16" customHeight="1" s="6">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>6．主語は「あなたたち」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B103" s="25" t="n"/>
-      <c r="C103" s="25" t="n"/>
-      <c r="D103" s="25" t="n"/>
-      <c r="E103" s="25" t="n"/>
-      <c r="F103" s="25" t="n"/>
-      <c r="G103" s="25" t="n"/>
-      <c r="H103" s="25" t="n"/>
-      <c r="I103" s="25" t="n"/>
-      <c r="J103" s="56" t="n"/>
-    </row>
-    <row r="104" ht="34" customHeight="1" s="6">
-      <c r="A104" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="103" ht="20" customHeight="1" s="6">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：No, you will not.</t>
+        </is>
+      </c>
+      <c r="B103" s="27" t="n"/>
+      <c r="C103" s="27" t="n"/>
+      <c r="D103" s="27" t="n"/>
+      <c r="E103" s="27" t="n"/>
+      <c r="F103" s="27" t="n"/>
+      <c r="G103" s="27" t="n"/>
+      <c r="H103" s="27" t="n"/>
+      <c r="I103" s="27" t="n"/>
+      <c r="J103" s="57" t="n"/>
+    </row>
+    <row r="104" ht="20" customHeight="1" s="6">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：No, you won't.</t>
         </is>
       </c>
       <c r="B104" s="27" t="n"/>
@@ -5841,10 +5997,10 @@
       <c r="I104" s="27" t="n"/>
       <c r="J104" s="57" t="n"/>
     </row>
-    <row r="105" ht="17" customHeight="1" s="6">
+    <row r="105" ht="20" customHeight="1" s="6">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>あなたたちは来週テニスをします。</t>
+          <t>正解（言いかえ基本形）：No, you are not.</t>
         </is>
       </c>
       <c r="B105" s="27" t="n"/>
@@ -5860,7 +6016,7 @@
     <row r="106" ht="20" customHeight="1" s="6">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>正解（will）：You will play tennis next week.</t>
+          <t>正解（言いかえ短縮形）：No, you aren't.</t>
         </is>
       </c>
       <c r="B106" s="27" t="n"/>
@@ -5873,12 +6029,8 @@
       <c r="I106" s="27" t="n"/>
       <c r="J106" s="57" t="n"/>
     </row>
-    <row r="107" ht="20" customHeight="1" s="6">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t>正解（言いかえ）：You are going to play tennis next week.</t>
-        </is>
-      </c>
+    <row r="107" ht="6" customHeight="1" s="6">
+      <c r="A107" s="8" t="n"/>
       <c r="B107" s="27" t="n"/>
       <c r="C107" s="27" t="n"/>
       <c r="D107" s="27" t="n"/>
@@ -5889,26 +6041,27 @@
       <c r="I107" s="27" t="n"/>
       <c r="J107" s="57" t="n"/>
     </row>
-    <row r="108" ht="17" customHeight="1" s="6">
-      <c r="A108" s="11" t="inlineStr">
-        <is>
-          <t>あなたたちは来週テニスをしません。</t>
-        </is>
-      </c>
-      <c r="B108" s="27" t="n"/>
-      <c r="C108" s="27" t="n"/>
-      <c r="D108" s="27" t="n"/>
-      <c r="E108" s="27" t="n"/>
-      <c r="F108" s="27" t="n"/>
-      <c r="G108" s="27" t="n"/>
-      <c r="H108" s="27" t="n"/>
-      <c r="I108" s="27" t="n"/>
-      <c r="J108" s="57" t="n"/>
-    </row>
-    <row r="109" ht="20" customHeight="1" s="6">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t>正解（基本形）：You will not play tennis next week.</t>
+    <row r="108" ht="18" customHeight="1" s="6">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>6．主語は「あなたたち」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B108" s="25" t="n"/>
+      <c r="C108" s="25" t="n"/>
+      <c r="D108" s="25" t="n"/>
+      <c r="E108" s="25" t="n"/>
+      <c r="F108" s="25" t="n"/>
+      <c r="G108" s="25" t="n"/>
+      <c r="H108" s="25" t="n"/>
+      <c r="I108" s="25" t="n"/>
+      <c r="J108" s="56" t="n"/>
+    </row>
+    <row r="109" ht="36" customHeight="1" s="6">
+      <c r="A109" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B109" s="27" t="n"/>
@@ -5921,10 +6074,10 @@
       <c r="I109" s="27" t="n"/>
       <c r="J109" s="57" t="n"/>
     </row>
-    <row r="110" ht="20" customHeight="1" s="6">
+    <row r="110" ht="18" customHeight="1" s="6">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：You won't play tennis next week.</t>
+          <t>あなたたちは来週テニスをします。</t>
         </is>
       </c>
       <c r="B110" s="27" t="n"/>
@@ -5940,7 +6093,7 @@
     <row r="111" ht="20" customHeight="1" s="6">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：You are not going to play tennis next week.</t>
+          <t>正解（will）：You will play tennis next week.</t>
         </is>
       </c>
       <c r="B111" s="27" t="n"/>
@@ -5953,10 +6106,10 @@
       <c r="I111" s="27" t="n"/>
       <c r="J111" s="57" t="n"/>
     </row>
-    <row r="112" ht="17" customHeight="1" s="6">
+    <row r="112" ht="20" customHeight="1" s="6">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>あなたたちは来週テニスをしますか。</t>
+          <t>正解（言いかえ）：You are going to play tennis next week.</t>
         </is>
       </c>
       <c r="B112" s="27" t="n"/>
@@ -5969,10 +6122,10 @@
       <c r="I112" s="27" t="n"/>
       <c r="J112" s="57" t="n"/>
     </row>
-    <row r="113" ht="20" customHeight="1" s="6">
+    <row r="113" ht="18" customHeight="1" s="6">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will you play tennis next week?</t>
+          <t>あなたたちは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B113" s="27" t="n"/>
@@ -5988,7 +6141,7 @@
     <row r="114" ht="20" customHeight="1" s="6">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ疑問文）：Are you going to play tennis next week?</t>
+          <t>正解（基本形）：You will not play tennis next week.</t>
         </is>
       </c>
       <c r="B114" s="27" t="n"/>
@@ -6001,10 +6154,10 @@
       <c r="I114" s="27" t="n"/>
       <c r="J114" s="57" t="n"/>
     </row>
-    <row r="115" ht="17" customHeight="1" s="6">
+    <row r="115" ht="20" customHeight="1" s="6">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>正解（短縮形）：You won't play tennis next week.</t>
         </is>
       </c>
       <c r="B115" s="27" t="n"/>
@@ -6020,7 +6173,7 @@
     <row r="116" ht="20" customHeight="1" s="6">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>正解（will返答）：Yes, we will.</t>
+          <t>正解（言いかえ）：You are not going to play tennis next week.</t>
         </is>
       </c>
       <c r="B116" s="27" t="n"/>
@@ -6033,10 +6186,10 @@
       <c r="I116" s="27" t="n"/>
       <c r="J116" s="57" t="n"/>
     </row>
-    <row r="117" ht="20" customHeight="1" s="6">
+    <row r="117" ht="18" customHeight="1" s="6">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：Yes, we are.</t>
+          <t>あなたたちは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B117" s="27" t="n"/>
@@ -6049,10 +6202,10 @@
       <c r="I117" s="27" t="n"/>
       <c r="J117" s="57" t="n"/>
     </row>
-    <row r="118" ht="17" customHeight="1" s="6">
+    <row r="118" ht="20" customHeight="1" s="6">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>正解（will疑問文）：Will you play tennis next week?</t>
         </is>
       </c>
       <c r="B118" s="27" t="n"/>
@@ -6068,7 +6221,7 @@
     <row r="119" ht="20" customHeight="1" s="6">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, we will not.</t>
+          <t>正解（言いかえ疑問文）：Are you going to play tennis next week?</t>
         </is>
       </c>
       <c r="B119" s="27" t="n"/>
@@ -6081,10 +6234,10 @@
       <c r="I119" s="27" t="n"/>
       <c r="J119" s="57" t="n"/>
     </row>
-    <row r="120" ht="20" customHeight="1" s="6">
+    <row r="120" ht="18" customHeight="1" s="6">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, we won't.</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B120" s="27" t="n"/>
@@ -6100,7 +6253,7 @@
     <row r="121" ht="20" customHeight="1" s="6">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：No, we are not.</t>
+          <t>正解（will返答）：Yes, we will.</t>
         </is>
       </c>
       <c r="B121" s="27" t="n"/>
@@ -6113,8 +6266,12 @@
       <c r="I121" s="27" t="n"/>
       <c r="J121" s="57" t="n"/>
     </row>
-    <row r="122" ht="4" customHeight="1" s="6">
-      <c r="A122" s="8" t="n"/>
+    <row r="122" ht="20" customHeight="1" s="6">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ返答）：Yes, we are.</t>
+        </is>
+      </c>
       <c r="B122" s="27" t="n"/>
       <c r="C122" s="27" t="n"/>
       <c r="D122" s="27" t="n"/>
@@ -6125,27 +6282,26 @@
       <c r="I122" s="27" t="n"/>
       <c r="J122" s="57" t="n"/>
     </row>
-    <row r="123" ht="16" customHeight="1" s="6">
-      <c r="A123" s="9" t="inlineStr">
-        <is>
-          <t>7．主語は「彼ら」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B123" s="25" t="n"/>
-      <c r="C123" s="25" t="n"/>
-      <c r="D123" s="25" t="n"/>
-      <c r="E123" s="25" t="n"/>
-      <c r="F123" s="25" t="n"/>
-      <c r="G123" s="25" t="n"/>
-      <c r="H123" s="25" t="n"/>
-      <c r="I123" s="25" t="n"/>
-      <c r="J123" s="56" t="n"/>
-    </row>
-    <row r="124" ht="34" customHeight="1" s="6">
-      <c r="A124" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="123" ht="18" customHeight="1" s="6">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、しません。</t>
+        </is>
+      </c>
+      <c r="B123" s="27" t="n"/>
+      <c r="C123" s="27" t="n"/>
+      <c r="D123" s="27" t="n"/>
+      <c r="E123" s="27" t="n"/>
+      <c r="F123" s="27" t="n"/>
+      <c r="G123" s="27" t="n"/>
+      <c r="H123" s="27" t="n"/>
+      <c r="I123" s="27" t="n"/>
+      <c r="J123" s="57" t="n"/>
+    </row>
+    <row r="124" ht="20" customHeight="1" s="6">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：No, we will not.</t>
         </is>
       </c>
       <c r="B124" s="27" t="n"/>
@@ -6158,10 +6314,10 @@
       <c r="I124" s="27" t="n"/>
       <c r="J124" s="57" t="n"/>
     </row>
-    <row r="125" ht="17" customHeight="1" s="6">
+    <row r="125" ht="20" customHeight="1" s="6">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>彼らは来週テニスをします。</t>
+          <t>正解（短縮形）：No, we won't.</t>
         </is>
       </c>
       <c r="B125" s="27" t="n"/>
@@ -6177,7 +6333,7 @@
     <row r="126" ht="20" customHeight="1" s="6">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>正解（will）：They will play tennis next week.</t>
+          <t>正解（言いかえ基本形）：No, we are not.</t>
         </is>
       </c>
       <c r="B126" s="27" t="n"/>
@@ -6193,7 +6349,7 @@
     <row r="127" ht="20" customHeight="1" s="6">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：They are going to play tennis next week.</t>
+          <t>正解（言いかえ短縮形）：No, we aren't.</t>
         </is>
       </c>
       <c r="B127" s="27" t="n"/>
@@ -6206,12 +6362,8 @@
       <c r="I127" s="27" t="n"/>
       <c r="J127" s="57" t="n"/>
     </row>
-    <row r="128" ht="17" customHeight="1" s="6">
-      <c r="A128" s="11" t="inlineStr">
-        <is>
-          <t>彼らは来週テニスをしません。</t>
-        </is>
-      </c>
+    <row r="128" ht="6" customHeight="1" s="6">
+      <c r="A128" s="8" t="n"/>
       <c r="B128" s="27" t="n"/>
       <c r="C128" s="27" t="n"/>
       <c r="D128" s="27" t="n"/>
@@ -6222,26 +6374,27 @@
       <c r="I128" s="27" t="n"/>
       <c r="J128" s="57" t="n"/>
     </row>
-    <row r="129" ht="20" customHeight="1" s="6">
-      <c r="A129" s="11" t="inlineStr">
-        <is>
-          <t>正解（基本形）：They will not play tennis next week.</t>
-        </is>
-      </c>
-      <c r="B129" s="27" t="n"/>
-      <c r="C129" s="27" t="n"/>
-      <c r="D129" s="27" t="n"/>
-      <c r="E129" s="27" t="n"/>
-      <c r="F129" s="27" t="n"/>
-      <c r="G129" s="27" t="n"/>
-      <c r="H129" s="27" t="n"/>
-      <c r="I129" s="27" t="n"/>
-      <c r="J129" s="57" t="n"/>
-    </row>
-    <row r="130" ht="20" customHeight="1" s="6">
-      <c r="A130" s="11" t="inlineStr">
-        <is>
-          <t>正解（短縮形）：They won't play tennis next week.</t>
+    <row r="129" ht="18" customHeight="1" s="6">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>7．主語は「彼ら」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B129" s="25" t="n"/>
+      <c r="C129" s="25" t="n"/>
+      <c r="D129" s="25" t="n"/>
+      <c r="E129" s="25" t="n"/>
+      <c r="F129" s="25" t="n"/>
+      <c r="G129" s="25" t="n"/>
+      <c r="H129" s="25" t="n"/>
+      <c r="I129" s="25" t="n"/>
+      <c r="J129" s="56" t="n"/>
+    </row>
+    <row r="130" ht="36" customHeight="1" s="6">
+      <c r="A130" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B130" s="27" t="n"/>
@@ -6254,10 +6407,10 @@
       <c r="I130" s="27" t="n"/>
       <c r="J130" s="57" t="n"/>
     </row>
-    <row r="131" ht="20" customHeight="1" s="6">
+    <row r="131" ht="18" customHeight="1" s="6">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：They are not going to play tennis next week.</t>
+          <t>彼らは来週テニスをします。</t>
         </is>
       </c>
       <c r="B131" s="27" t="n"/>
@@ -6270,10 +6423,10 @@
       <c r="I131" s="27" t="n"/>
       <c r="J131" s="57" t="n"/>
     </row>
-    <row r="132" ht="17" customHeight="1" s="6">
+    <row r="132" ht="20" customHeight="1" s="6">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>彼らは来週テニスをしますか。</t>
+          <t>正解（will）：They will play tennis next week.</t>
         </is>
       </c>
       <c r="B132" s="27" t="n"/>
@@ -6289,7 +6442,7 @@
     <row r="133" ht="20" customHeight="1" s="6">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will they play tennis next week?</t>
+          <t>正解（言いかえ）：They are going to play tennis next week.</t>
         </is>
       </c>
       <c r="B133" s="27" t="n"/>
@@ -6302,10 +6455,10 @@
       <c r="I133" s="27" t="n"/>
       <c r="J133" s="57" t="n"/>
     </row>
-    <row r="134" ht="20" customHeight="1" s="6">
+    <row r="134" ht="18" customHeight="1" s="6">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ疑問文）：Are they going to play tennis next week?</t>
+          <t>彼らは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B134" s="27" t="n"/>
@@ -6318,10 +6471,10 @@
       <c r="I134" s="27" t="n"/>
       <c r="J134" s="57" t="n"/>
     </row>
-    <row r="135" ht="17" customHeight="1" s="6">
+    <row r="135" ht="20" customHeight="1" s="6">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>正解（基本形）：They will not play tennis next week.</t>
         </is>
       </c>
       <c r="B135" s="27" t="n"/>
@@ -6337,7 +6490,7 @@
     <row r="136" ht="20" customHeight="1" s="6">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>正解（will返答）：Yes, they will.</t>
+          <t>正解（短縮形）：They won't play tennis next week.</t>
         </is>
       </c>
       <c r="B136" s="27" t="n"/>
@@ -6353,7 +6506,7 @@
     <row r="137" ht="20" customHeight="1" s="6">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：Yes, they are.</t>
+          <t>正解（言いかえ）：They are not going to play tennis next week.</t>
         </is>
       </c>
       <c r="B137" s="27" t="n"/>
@@ -6366,10 +6519,10 @@
       <c r="I137" s="27" t="n"/>
       <c r="J137" s="57" t="n"/>
     </row>
-    <row r="138" ht="17" customHeight="1" s="6">
+    <row r="138" ht="18" customHeight="1" s="6">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>彼らは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B138" s="27" t="n"/>
@@ -6385,7 +6538,7 @@
     <row r="139" ht="20" customHeight="1" s="6">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, they will not.</t>
+          <t>正解（will疑問文）：Will they play tennis next week?</t>
         </is>
       </c>
       <c r="B139" s="27" t="n"/>
@@ -6401,7 +6554,7 @@
     <row r="140" ht="20" customHeight="1" s="6">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, they won't.</t>
+          <t>正解（言いかえ疑問文）：Are they going to play tennis next week?</t>
         </is>
       </c>
       <c r="B140" s="27" t="n"/>
@@ -6414,10 +6567,10 @@
       <c r="I140" s="27" t="n"/>
       <c r="J140" s="57" t="n"/>
     </row>
-    <row r="141" ht="20" customHeight="1" s="6">
+    <row r="141" ht="18" customHeight="1" s="6">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：No, they are not.</t>
+          <t>はい、します。</t>
         </is>
       </c>
       <c r="B141" s="27" t="n"/>
@@ -6430,8 +6583,12 @@
       <c r="I141" s="27" t="n"/>
       <c r="J141" s="57" t="n"/>
     </row>
-    <row r="142" ht="4" customHeight="1" s="6">
-      <c r="A142" s="8" t="n"/>
+    <row r="142" ht="20" customHeight="1" s="6">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>正解（will返答）：Yes, they will.</t>
+        </is>
+      </c>
       <c r="B142" s="27" t="n"/>
       <c r="C142" s="27" t="n"/>
       <c r="D142" s="27" t="n"/>
@@ -6442,27 +6599,26 @@
       <c r="I142" s="27" t="n"/>
       <c r="J142" s="57" t="n"/>
     </row>
-    <row r="143" ht="16" customHeight="1" s="6">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>8．主語は「リョウタロウ」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B143" s="25" t="n"/>
-      <c r="C143" s="25" t="n"/>
-      <c r="D143" s="25" t="n"/>
-      <c r="E143" s="25" t="n"/>
-      <c r="F143" s="25" t="n"/>
-      <c r="G143" s="25" t="n"/>
-      <c r="H143" s="25" t="n"/>
-      <c r="I143" s="25" t="n"/>
-      <c r="J143" s="56" t="n"/>
-    </row>
-    <row r="144" ht="34" customHeight="1" s="6">
-      <c r="A144" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="143" ht="20" customHeight="1" s="6">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ返答）：Yes, they are.</t>
+        </is>
+      </c>
+      <c r="B143" s="27" t="n"/>
+      <c r="C143" s="27" t="n"/>
+      <c r="D143" s="27" t="n"/>
+      <c r="E143" s="27" t="n"/>
+      <c r="F143" s="27" t="n"/>
+      <c r="G143" s="27" t="n"/>
+      <c r="H143" s="27" t="n"/>
+      <c r="I143" s="27" t="n"/>
+      <c r="J143" s="57" t="n"/>
+    </row>
+    <row r="144" ht="18" customHeight="1" s="6">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B144" s="27" t="n"/>
@@ -6475,10 +6631,10 @@
       <c r="I144" s="27" t="n"/>
       <c r="J144" s="57" t="n"/>
     </row>
-    <row r="145" ht="17" customHeight="1" s="6">
+    <row r="145" ht="20" customHeight="1" s="6">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは来週テニスをします。</t>
+          <t>正解（基本形）：No, they will not.</t>
         </is>
       </c>
       <c r="B145" s="27" t="n"/>
@@ -6494,7 +6650,7 @@
     <row r="146" ht="20" customHeight="1" s="6">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>正解（will）：Ryoutarou will play tennis next week.</t>
+          <t>正解（短縮形）：No, they won't.</t>
         </is>
       </c>
       <c r="B146" s="27" t="n"/>
@@ -6510,7 +6666,7 @@
     <row r="147" ht="20" customHeight="1" s="6">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：Ryoutarou is going to play tennis next week.</t>
+          <t>正解（言いかえ基本形）：No, they are not.</t>
         </is>
       </c>
       <c r="B147" s="27" t="n"/>
@@ -6523,10 +6679,10 @@
       <c r="I147" s="27" t="n"/>
       <c r="J147" s="57" t="n"/>
     </row>
-    <row r="148" ht="17" customHeight="1" s="6">
+    <row r="148" ht="20" customHeight="1" s="6">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは来週テニスをしません。</t>
+          <t>正解（言いかえ短縮形）：No, they aren't.</t>
         </is>
       </c>
       <c r="B148" s="27" t="n"/>
@@ -6539,12 +6695,8 @@
       <c r="I148" s="27" t="n"/>
       <c r="J148" s="57" t="n"/>
     </row>
-    <row r="149" ht="20" customHeight="1" s="6">
-      <c r="A149" s="11" t="inlineStr">
-        <is>
-          <t>正解（基本形）：Ryoutarou will not play tennis next week.</t>
-        </is>
-      </c>
+    <row r="149" ht="6" customHeight="1" s="6">
+      <c r="A149" s="8" t="n"/>
       <c r="B149" s="27" t="n"/>
       <c r="C149" s="27" t="n"/>
       <c r="D149" s="27" t="n"/>
@@ -6555,26 +6707,27 @@
       <c r="I149" s="27" t="n"/>
       <c r="J149" s="57" t="n"/>
     </row>
-    <row r="150" ht="20" customHeight="1" s="6">
-      <c r="A150" s="11" t="inlineStr">
-        <is>
-          <t>正解（短縮形）：Ryoutarou won't play tennis next week.</t>
-        </is>
-      </c>
-      <c r="B150" s="27" t="n"/>
-      <c r="C150" s="27" t="n"/>
-      <c r="D150" s="27" t="n"/>
-      <c r="E150" s="27" t="n"/>
-      <c r="F150" s="27" t="n"/>
-      <c r="G150" s="27" t="n"/>
-      <c r="H150" s="27" t="n"/>
-      <c r="I150" s="27" t="n"/>
-      <c r="J150" s="57" t="n"/>
-    </row>
-    <row r="151" ht="20" customHeight="1" s="6">
-      <c r="A151" s="11" t="inlineStr">
-        <is>
-          <t>正解（言いかえ）：Ryoutarou is not going to play tennis next week.</t>
+    <row r="150" ht="18" customHeight="1" s="6">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>8．主語は「リョウタロウ」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B150" s="25" t="n"/>
+      <c r="C150" s="25" t="n"/>
+      <c r="D150" s="25" t="n"/>
+      <c r="E150" s="25" t="n"/>
+      <c r="F150" s="25" t="n"/>
+      <c r="G150" s="25" t="n"/>
+      <c r="H150" s="25" t="n"/>
+      <c r="I150" s="25" t="n"/>
+      <c r="J150" s="56" t="n"/>
+    </row>
+    <row r="151" ht="36" customHeight="1" s="6">
+      <c r="A151" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B151" s="27" t="n"/>
@@ -6587,10 +6740,10 @@
       <c r="I151" s="27" t="n"/>
       <c r="J151" s="57" t="n"/>
     </row>
-    <row r="152" ht="17" customHeight="1" s="6">
+    <row r="152" ht="18" customHeight="1" s="6">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>リョウタロウは来週テニスをしますか。</t>
+          <t>リョウタロウは来週テニスをします。</t>
         </is>
       </c>
       <c r="B152" s="27" t="n"/>
@@ -6606,7 +6759,7 @@
     <row r="153" ht="20" customHeight="1" s="6">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will Ryoutarou play tennis next week?</t>
+          <t>正解（will）：Ryoutarou will play tennis next week.</t>
         </is>
       </c>
       <c r="B153" s="27" t="n"/>
@@ -6622,7 +6775,7 @@
     <row r="154" ht="20" customHeight="1" s="6">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ疑問文）：Is Ryoutarou going to play tennis next week?</t>
+          <t>正解（言いかえ）：Ryoutarou is going to play tennis next week.</t>
         </is>
       </c>
       <c r="B154" s="27" t="n"/>
@@ -6635,10 +6788,10 @@
       <c r="I154" s="27" t="n"/>
       <c r="J154" s="57" t="n"/>
     </row>
-    <row r="155" ht="17" customHeight="1" s="6">
+    <row r="155" ht="18" customHeight="1" s="6">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>リョウタロウは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B155" s="27" t="n"/>
@@ -6654,7 +6807,7 @@
     <row r="156" ht="20" customHeight="1" s="6">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>正解（will返答）：Yes, he will.</t>
+          <t>正解（基本形）：Ryoutarou will not play tennis next week.</t>
         </is>
       </c>
       <c r="B156" s="27" t="n"/>
@@ -6670,7 +6823,7 @@
     <row r="157" ht="20" customHeight="1" s="6">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：Yes, he is.</t>
+          <t>正解（短縮形）：Ryoutarou won't play tennis next week.</t>
         </is>
       </c>
       <c r="B157" s="27" t="n"/>
@@ -6683,10 +6836,10 @@
       <c r="I157" s="27" t="n"/>
       <c r="J157" s="57" t="n"/>
     </row>
-    <row r="158" ht="17" customHeight="1" s="6">
+    <row r="158" ht="20" customHeight="1" s="6">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>正解（言いかえ）：Ryoutarou is not going to play tennis next week.</t>
         </is>
       </c>
       <c r="B158" s="27" t="n"/>
@@ -6699,10 +6852,10 @@
       <c r="I158" s="27" t="n"/>
       <c r="J158" s="57" t="n"/>
     </row>
-    <row r="159" ht="20" customHeight="1" s="6">
+    <row r="159" ht="18" customHeight="1" s="6">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, he will not.</t>
+          <t>リョウタロウは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B159" s="27" t="n"/>
@@ -6718,7 +6871,7 @@
     <row r="160" ht="20" customHeight="1" s="6">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, he won't.</t>
+          <t>正解（will疑問文）：Will Ryoutarou play tennis next week?</t>
         </is>
       </c>
       <c r="B160" s="27" t="n"/>
@@ -6734,7 +6887,7 @@
     <row r="161" ht="20" customHeight="1" s="6">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：No, he is not.</t>
+          <t>正解（言いかえ疑問文）：Is Ryoutarou going to play tennis next week?</t>
         </is>
       </c>
       <c r="B161" s="27" t="n"/>
@@ -6747,8 +6900,12 @@
       <c r="I161" s="27" t="n"/>
       <c r="J161" s="57" t="n"/>
     </row>
-    <row r="162" ht="4" customHeight="1" s="6">
-      <c r="A162" s="8" t="n"/>
+    <row r="162" ht="18" customHeight="1" s="6">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t>はい、します。</t>
+        </is>
+      </c>
       <c r="B162" s="27" t="n"/>
       <c r="C162" s="27" t="n"/>
       <c r="D162" s="27" t="n"/>
@@ -6759,27 +6916,26 @@
       <c r="I162" s="27" t="n"/>
       <c r="J162" s="57" t="n"/>
     </row>
-    <row r="163" ht="16" customHeight="1" s="6">
-      <c r="A163" s="9" t="inlineStr">
-        <is>
-          <t>9．主語は「チサコ」で書いてください。</t>
-        </is>
-      </c>
-      <c r="B163" s="25" t="n"/>
-      <c r="C163" s="25" t="n"/>
-      <c r="D163" s="25" t="n"/>
-      <c r="E163" s="25" t="n"/>
-      <c r="F163" s="25" t="n"/>
-      <c r="G163" s="25" t="n"/>
-      <c r="H163" s="25" t="n"/>
-      <c r="I163" s="25" t="n"/>
-      <c r="J163" s="56" t="n"/>
-    </row>
-    <row r="164" ht="34" customHeight="1" s="6">
-      <c r="A164" s="55" t="inlineStr">
-        <is>
-          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
-※否定の短縮形は will not → won't を使います。</t>
+    <row r="163" ht="20" customHeight="1" s="6">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>正解（will返答）：Yes, he will.</t>
+        </is>
+      </c>
+      <c r="B163" s="27" t="n"/>
+      <c r="C163" s="27" t="n"/>
+      <c r="D163" s="27" t="n"/>
+      <c r="E163" s="27" t="n"/>
+      <c r="F163" s="27" t="n"/>
+      <c r="G163" s="27" t="n"/>
+      <c r="H163" s="27" t="n"/>
+      <c r="I163" s="27" t="n"/>
+      <c r="J163" s="57" t="n"/>
+    </row>
+    <row r="164" ht="20" customHeight="1" s="6">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ返答）：Yes, he is.</t>
         </is>
       </c>
       <c r="B164" s="27" t="n"/>
@@ -6792,10 +6948,10 @@
       <c r="I164" s="27" t="n"/>
       <c r="J164" s="57" t="n"/>
     </row>
-    <row r="165" ht="17" customHeight="1" s="6">
+    <row r="165" ht="18" customHeight="1" s="6">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>チサコは来週テニスをします。</t>
+          <t>いいえ、しません。</t>
         </is>
       </c>
       <c r="B165" s="27" t="n"/>
@@ -6811,7 +6967,7 @@
     <row r="166" ht="20" customHeight="1" s="6">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>正解（will）：Chisako will play tennis next week.</t>
+          <t>正解（基本形）：No, he will not.</t>
         </is>
       </c>
       <c r="B166" s="27" t="n"/>
@@ -6827,7 +6983,7 @@
     <row r="167" ht="20" customHeight="1" s="6">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ）：Chisako is going to play tennis next week.</t>
+          <t>正解（短縮形）：No, he won't.</t>
         </is>
       </c>
       <c r="B167" s="27" t="n"/>
@@ -6840,10 +6996,10 @@
       <c r="I167" s="27" t="n"/>
       <c r="J167" s="57" t="n"/>
     </row>
-    <row r="168" ht="17" customHeight="1" s="6">
+    <row r="168" ht="20" customHeight="1" s="6">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>チサコは来週テニスをしません。</t>
+          <t>正解（言いかえ基本形）：No, he is not.</t>
         </is>
       </c>
       <c r="B168" s="27" t="n"/>
@@ -6859,7 +7015,7 @@
     <row r="169" ht="20" customHeight="1" s="6">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：Chisako will not play tennis next week.</t>
+          <t>正解（言いかえ短縮形）：No, he isn't.</t>
         </is>
       </c>
       <c r="B169" s="27" t="n"/>
@@ -6872,12 +7028,8 @@
       <c r="I169" s="27" t="n"/>
       <c r="J169" s="57" t="n"/>
     </row>
-    <row r="170" ht="20" customHeight="1" s="6">
-      <c r="A170" s="11" t="inlineStr">
-        <is>
-          <t>正解（短縮形）：Chisako won't play tennis next week.</t>
-        </is>
-      </c>
+    <row r="170" ht="6" customHeight="1" s="6">
+      <c r="A170" s="8" t="n"/>
       <c r="B170" s="27" t="n"/>
       <c r="C170" s="27" t="n"/>
       <c r="D170" s="27" t="n"/>
@@ -6888,26 +7040,27 @@
       <c r="I170" s="27" t="n"/>
       <c r="J170" s="57" t="n"/>
     </row>
-    <row r="171" ht="20" customHeight="1" s="6">
-      <c r="A171" s="11" t="inlineStr">
-        <is>
-          <t>正解（言いかえ）：Chisako is not going to play tennis next week.</t>
-        </is>
-      </c>
-      <c r="B171" s="27" t="n"/>
-      <c r="C171" s="27" t="n"/>
-      <c r="D171" s="27" t="n"/>
-      <c r="E171" s="27" t="n"/>
-      <c r="F171" s="27" t="n"/>
-      <c r="G171" s="27" t="n"/>
-      <c r="H171" s="27" t="n"/>
-      <c r="I171" s="27" t="n"/>
-      <c r="J171" s="57" t="n"/>
-    </row>
-    <row r="172" ht="17" customHeight="1" s="6">
-      <c r="A172" s="11" t="inlineStr">
-        <is>
-          <t>チサコは来週テニスをしますか。</t>
+    <row r="171" ht="18" customHeight="1" s="6">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>9．主語は「チサコ」で書いてください。</t>
+        </is>
+      </c>
+      <c r="B171" s="25" t="n"/>
+      <c r="C171" s="25" t="n"/>
+      <c r="D171" s="25" t="n"/>
+      <c r="E171" s="25" t="n"/>
+      <c r="F171" s="25" t="n"/>
+      <c r="G171" s="25" t="n"/>
+      <c r="H171" s="25" t="n"/>
+      <c r="I171" s="25" t="n"/>
+      <c r="J171" s="56" t="n"/>
+    </row>
+    <row r="172" ht="36" customHeight="1" s="6">
+      <c r="A172" s="55" t="inlineStr">
+        <is>
+          <t>※未来の文は will + 動詞の原形、言いかえは am / are / is going to + 動詞の原形を使います。
+※否定の短縮形は will not → won't を使います。</t>
         </is>
       </c>
       <c r="B172" s="27" t="n"/>
@@ -6920,10 +7073,10 @@
       <c r="I172" s="27" t="n"/>
       <c r="J172" s="57" t="n"/>
     </row>
-    <row r="173" ht="20" customHeight="1" s="6">
+    <row r="173" ht="18" customHeight="1" s="6">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>正解（will疑問文）：Will Chisako play tennis next week?</t>
+          <t>チサコは来週テニスをします。</t>
         </is>
       </c>
       <c r="B173" s="27" t="n"/>
@@ -6939,7 +7092,7 @@
     <row r="174" ht="20" customHeight="1" s="6">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ疑問文）：Is Chisako going to play tennis next week?</t>
+          <t>正解（will）：Chisako will play tennis next week.</t>
         </is>
       </c>
       <c r="B174" s="27" t="n"/>
@@ -6952,10 +7105,10 @@
       <c r="I174" s="27" t="n"/>
       <c r="J174" s="57" t="n"/>
     </row>
-    <row r="175" ht="17" customHeight="1" s="6">
+    <row r="175" ht="20" customHeight="1" s="6">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>はい、します。</t>
+          <t>正解（言いかえ）：Chisako is going to play tennis next week.</t>
         </is>
       </c>
       <c r="B175" s="27" t="n"/>
@@ -6968,10 +7121,10 @@
       <c r="I175" s="27" t="n"/>
       <c r="J175" s="57" t="n"/>
     </row>
-    <row r="176" ht="20" customHeight="1" s="6">
+    <row r="176" ht="18" customHeight="1" s="6">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>正解（will返答）：Yes, she will.</t>
+          <t>チサコは来週テニスをしません。</t>
         </is>
       </c>
       <c r="B176" s="27" t="n"/>
@@ -6987,7 +7140,7 @@
     <row r="177" ht="20" customHeight="1" s="6">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：Yes, she is.</t>
+          <t>正解（基本形）：Chisako will not play tennis next week.</t>
         </is>
       </c>
       <c r="B177" s="27" t="n"/>
@@ -7000,10 +7153,10 @@
       <c r="I177" s="27" t="n"/>
       <c r="J177" s="57" t="n"/>
     </row>
-    <row r="178" ht="17" customHeight="1" s="6">
+    <row r="178" ht="20" customHeight="1" s="6">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>いいえ、しません。</t>
+          <t>正解（短縮形）：Chisako won't play tennis next week.</t>
         </is>
       </c>
       <c r="B178" s="27" t="n"/>
@@ -7019,7 +7172,7 @@
     <row r="179" ht="20" customHeight="1" s="6">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, she will not.</t>
+          <t>正解（言いかえ）：Chisako is not going to play tennis next week.</t>
         </is>
       </c>
       <c r="B179" s="27" t="n"/>
@@ -7032,10 +7185,10 @@
       <c r="I179" s="27" t="n"/>
       <c r="J179" s="57" t="n"/>
     </row>
-    <row r="180" ht="20" customHeight="1" s="6">
+    <row r="180" ht="18" customHeight="1" s="6">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, she won't.</t>
+          <t>チサコは来週テニスをしますか。</t>
         </is>
       </c>
       <c r="B180" s="27" t="n"/>
@@ -7051,7 +7204,7 @@
     <row r="181" ht="20" customHeight="1" s="6">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>正解（言いかえ返答）：No, she is not.</t>
+          <t>正解（will疑問文）：Will Chisako play tennis next week?</t>
         </is>
       </c>
       <c r="B181" s="27" t="n"/>
@@ -7064,8 +7217,12 @@
       <c r="I181" s="27" t="n"/>
       <c r="J181" s="57" t="n"/>
     </row>
-    <row r="182" ht="4" customHeight="1" s="6">
-      <c r="A182" s="8" t="n"/>
+    <row r="182" ht="20" customHeight="1" s="6">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ疑問文）：Is Chisako going to play tennis next week?</t>
+        </is>
+      </c>
       <c r="B182" s="27" t="n"/>
       <c r="C182" s="27" t="n"/>
       <c r="D182" s="27" t="n"/>
@@ -7076,11 +7233,152 @@
       <c r="I182" s="27" t="n"/>
       <c r="J182" s="57" t="n"/>
     </row>
+    <row r="183" ht="18" customHeight="1" s="6">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>はい、します。</t>
+        </is>
+      </c>
+      <c r="B183" s="27" t="n"/>
+      <c r="C183" s="27" t="n"/>
+      <c r="D183" s="27" t="n"/>
+      <c r="E183" s="27" t="n"/>
+      <c r="F183" s="27" t="n"/>
+      <c r="G183" s="27" t="n"/>
+      <c r="H183" s="27" t="n"/>
+      <c r="I183" s="27" t="n"/>
+      <c r="J183" s="57" t="n"/>
+    </row>
+    <row r="184" ht="20" customHeight="1" s="6">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>正解（will返答）：Yes, she will.</t>
+        </is>
+      </c>
+      <c r="B184" s="27" t="n"/>
+      <c r="C184" s="27" t="n"/>
+      <c r="D184" s="27" t="n"/>
+      <c r="E184" s="27" t="n"/>
+      <c r="F184" s="27" t="n"/>
+      <c r="G184" s="27" t="n"/>
+      <c r="H184" s="27" t="n"/>
+      <c r="I184" s="27" t="n"/>
+      <c r="J184" s="57" t="n"/>
+    </row>
+    <row r="185" ht="20" customHeight="1" s="6">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ返答）：Yes, she is.</t>
+        </is>
+      </c>
+      <c r="B185" s="27" t="n"/>
+      <c r="C185" s="27" t="n"/>
+      <c r="D185" s="27" t="n"/>
+      <c r="E185" s="27" t="n"/>
+      <c r="F185" s="27" t="n"/>
+      <c r="G185" s="27" t="n"/>
+      <c r="H185" s="27" t="n"/>
+      <c r="I185" s="27" t="n"/>
+      <c r="J185" s="57" t="n"/>
+    </row>
+    <row r="186" ht="18" customHeight="1" s="6">
+      <c r="A186" s="11" t="inlineStr">
+        <is>
+          <t>いいえ、しません。</t>
+        </is>
+      </c>
+      <c r="B186" s="27" t="n"/>
+      <c r="C186" s="27" t="n"/>
+      <c r="D186" s="27" t="n"/>
+      <c r="E186" s="27" t="n"/>
+      <c r="F186" s="27" t="n"/>
+      <c r="G186" s="27" t="n"/>
+      <c r="H186" s="27" t="n"/>
+      <c r="I186" s="27" t="n"/>
+      <c r="J186" s="57" t="n"/>
+    </row>
+    <row r="187" ht="20" customHeight="1" s="6">
+      <c r="A187" s="11" t="inlineStr">
+        <is>
+          <t>正解（基本形）：No, she will not.</t>
+        </is>
+      </c>
+      <c r="B187" s="27" t="n"/>
+      <c r="C187" s="27" t="n"/>
+      <c r="D187" s="27" t="n"/>
+      <c r="E187" s="27" t="n"/>
+      <c r="F187" s="27" t="n"/>
+      <c r="G187" s="27" t="n"/>
+      <c r="H187" s="27" t="n"/>
+      <c r="I187" s="27" t="n"/>
+      <c r="J187" s="57" t="n"/>
+    </row>
+    <row r="188" ht="20" customHeight="1" s="6">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t>正解（短縮形）：No, she won't.</t>
+        </is>
+      </c>
+      <c r="B188" s="27" t="n"/>
+      <c r="C188" s="27" t="n"/>
+      <c r="D188" s="27" t="n"/>
+      <c r="E188" s="27" t="n"/>
+      <c r="F188" s="27" t="n"/>
+      <c r="G188" s="27" t="n"/>
+      <c r="H188" s="27" t="n"/>
+      <c r="I188" s="27" t="n"/>
+      <c r="J188" s="57" t="n"/>
+    </row>
+    <row r="189" ht="20" customHeight="1" s="6">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ基本形）：No, she is not.</t>
+        </is>
+      </c>
+      <c r="B189" s="27" t="n"/>
+      <c r="C189" s="27" t="n"/>
+      <c r="D189" s="27" t="n"/>
+      <c r="E189" s="27" t="n"/>
+      <c r="F189" s="27" t="n"/>
+      <c r="G189" s="27" t="n"/>
+      <c r="H189" s="27" t="n"/>
+      <c r="I189" s="27" t="n"/>
+      <c r="J189" s="57" t="n"/>
+    </row>
+    <row r="190" ht="20" customHeight="1" s="6">
+      <c r="A190" s="11" t="inlineStr">
+        <is>
+          <t>正解（言いかえ短縮形）：No, she isn't.</t>
+        </is>
+      </c>
+      <c r="B190" s="27" t="n"/>
+      <c r="C190" s="27" t="n"/>
+      <c r="D190" s="27" t="n"/>
+      <c r="E190" s="27" t="n"/>
+      <c r="F190" s="27" t="n"/>
+      <c r="G190" s="27" t="n"/>
+      <c r="H190" s="27" t="n"/>
+      <c r="I190" s="27" t="n"/>
+      <c r="J190" s="57" t="n"/>
+    </row>
+    <row r="191" ht="6" customHeight="1" s="6">
+      <c r="A191" s="8" t="n"/>
+      <c r="B191" s="27" t="n"/>
+      <c r="C191" s="27" t="n"/>
+      <c r="D191" s="27" t="n"/>
+      <c r="E191" s="27" t="n"/>
+      <c r="F191" s="27" t="n"/>
+      <c r="G191" s="27" t="n"/>
+      <c r="H191" s="27" t="n"/>
+      <c r="I191" s="27" t="n"/>
+      <c r="J191" s="57" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="182">
+  <mergeCells count="191">
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A181:J181"/>
     <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A184:J184"/>
     <mergeCell ref="A156:J156"/>
     <mergeCell ref="A43:J43"/>
     <mergeCell ref="A171:J171"/>
@@ -7092,8 +7390,8 @@
     <mergeCell ref="A93:J93"/>
     <mergeCell ref="A173:J173"/>
     <mergeCell ref="A130:J130"/>
+    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A77:J77"/>
-    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A148:J148"/>
     <mergeCell ref="A157:J157"/>
@@ -7105,6 +7403,7 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A69:J69"/>
     <mergeCell ref="A174:J174"/>
+    <mergeCell ref="A183:J183"/>
     <mergeCell ref="A66:J66"/>
     <mergeCell ref="A118:J118"/>
     <mergeCell ref="A75:J75"/>
@@ -7124,20 +7423,21 @@
     <mergeCell ref="A106:J106"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A96:J96"/>
     <mergeCell ref="A81:J81"/>
-    <mergeCell ref="A96:J96"/>
     <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A121:J121"/>
     <mergeCell ref="A147:J147"/>
-    <mergeCell ref="A121:J121"/>
     <mergeCell ref="A161:J161"/>
+    <mergeCell ref="A170:J170"/>
     <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A170:J170"/>
     <mergeCell ref="A44:J44"/>
     <mergeCell ref="A31:J31"/>
     <mergeCell ref="A58:J58"/>
     <mergeCell ref="A40:J40"/>
     <mergeCell ref="A67:J67"/>
     <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A186:J186"/>
     <mergeCell ref="A73:J73"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A82:J82"/>
@@ -7149,11 +7449,13 @@
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A172:J172"/>
     <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A187:J187"/>
     <mergeCell ref="A25:J25"/>
     <mergeCell ref="A108:J108"/>
     <mergeCell ref="A84:J84"/>
     <mergeCell ref="A149:J149"/>
     <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A189:J189"/>
     <mergeCell ref="A158:J158"/>
     <mergeCell ref="A50:J50"/>
     <mergeCell ref="A2:J2"/>
@@ -7172,12 +7474,13 @@
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A125:J125"/>
     <mergeCell ref="A72:J72"/>
-    <mergeCell ref="A134:J134"/>
+    <mergeCell ref="A190:J190"/>
     <mergeCell ref="A28:J28"/>
     <mergeCell ref="A112:J112"/>
+    <mergeCell ref="A134:J134"/>
     <mergeCell ref="A152:J152"/>
+    <mergeCell ref="A167:J167"/>
     <mergeCell ref="A127:J127"/>
-    <mergeCell ref="A167:J167"/>
     <mergeCell ref="A176:J176"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A114:J114"/>
@@ -7185,9 +7488,10 @@
     <mergeCell ref="A182:J182"/>
     <mergeCell ref="A64:J64"/>
     <mergeCell ref="A98:J98"/>
-    <mergeCell ref="A169:J169"/>
+    <mergeCell ref="A191:J191"/>
     <mergeCell ref="A51:J51"/>
     <mergeCell ref="A107:J107"/>
+    <mergeCell ref="A169:J169"/>
     <mergeCell ref="A178:J178"/>
     <mergeCell ref="A79:J79"/>
     <mergeCell ref="A61:J61"/>
@@ -7215,14 +7519,15 @@
     <mergeCell ref="A116:J116"/>
     <mergeCell ref="A85:J85"/>
     <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A188:J188"/>
     <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A100:J100"/>
     <mergeCell ref="A131:J131"/>
     <mergeCell ref="A126:J126"/>
-    <mergeCell ref="A100:J100"/>
+    <mergeCell ref="A109:J109"/>
+    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A35:J35"/>
     <mergeCell ref="A140:J140"/>
-    <mergeCell ref="A53:J53"/>
-    <mergeCell ref="A109:J109"/>
-    <mergeCell ref="A35:J35"/>
     <mergeCell ref="A180:J180"/>
     <mergeCell ref="A129:J129"/>
     <mergeCell ref="A10:J10"/>
@@ -7260,15 +7565,16 @@
     <mergeCell ref="A113:J113"/>
     <mergeCell ref="A179:J179"/>
     <mergeCell ref="A71:J71"/>
+    <mergeCell ref="A185:J185"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1" verticalDpi="0"/>
   <rowBreaks count="4" manualBreakCount="4">
-    <brk id="42" min="0" max="16383" man="1"/>
-    <brk id="82" min="0" max="16383" man="1"/>
-    <brk id="122" min="0" max="16383" man="1"/>
-    <brk id="162" min="0" max="16383" man="1"/>
+    <brk id="44" min="0" max="16383" man="1"/>
+    <brk id="86" min="0" max="16383" man="1"/>
+    <brk id="128" min="0" max="16383" man="1"/>
+    <brk id="170" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>